--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125393618</v>
+        <v>125392596</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>813976</v>
+        <v>813911</v>
       </c>
       <c r="R7" t="n">
-        <v>7355749</v>
+        <v>7355874</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125393613</v>
+        <v>125393618</v>
       </c>
       <c r="B8" t="n">
-        <v>78834</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>813953</v>
+        <v>813976</v>
       </c>
       <c r="R8" t="n">
-        <v>7355711</v>
+        <v>7355749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125394416</v>
+        <v>125393613</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>78834</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>814013</v>
+        <v>813953</v>
       </c>
       <c r="R9" t="n">
-        <v>7355681</v>
+        <v>7355711</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,11 +1467,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1484,19 +1479,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125401313</v>
+        <v>125394416</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1536,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>813998</v>
+        <v>814013</v>
       </c>
       <c r="R10" t="n">
-        <v>7355672</v>
+        <v>7355681</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1591,22 +1586,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125401292</v>
+        <v>125392505</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>92293</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>813980</v>
+        <v>813992</v>
       </c>
       <c r="R11" t="n">
-        <v>7355837</v>
+        <v>7355418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1681,11 +1676,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1698,22 +1688,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125392596</v>
+        <v>125392499</v>
       </c>
       <c r="B12" t="n">
-        <v>92293</v>
+        <v>92490</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>813911</v>
+        <v>814055</v>
       </c>
       <c r="R12" t="n">
-        <v>7355874</v>
+        <v>7355488</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1786,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,22 +1795,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125392505</v>
+        <v>125401313</v>
       </c>
       <c r="B13" t="n">
-        <v>92293</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,13 +1847,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>813992</v>
+        <v>813998</v>
       </c>
       <c r="R13" t="n">
-        <v>7355418</v>
+        <v>7355672</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1888,6 +1883,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,22 +1902,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125392499</v>
+        <v>125401317</v>
       </c>
       <c r="B14" t="n">
-        <v>92490</v>
+        <v>78455</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,13 +1954,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>814055</v>
+        <v>813998</v>
       </c>
       <c r="R14" t="n">
-        <v>7355488</v>
+        <v>7355852</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1990,11 +1990,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,22 +2004,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125401317</v>
+        <v>125401292</v>
       </c>
       <c r="B15" t="n">
-        <v>78455</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>813998</v>
+        <v>813980</v>
       </c>
       <c r="R15" t="n">
-        <v>7355852</v>
+        <v>7355837</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2097,6 +2092,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,12 +2111,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -5387,10 +5387,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125392274</v>
+        <v>125401322</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5399,25 +5399,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>814062</v>
+        <v>813963</v>
       </c>
       <c r="R48" t="n">
-        <v>7355640</v>
+        <v>7355778</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5477,22 +5477,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125401322</v>
+        <v>125392274</v>
       </c>
       <c r="B49" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5501,25 +5501,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>813963</v>
+        <v>814062</v>
       </c>
       <c r="R49" t="n">
-        <v>7355778</v>
+        <v>7355640</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5579,12 +5579,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6101,7 +6101,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125394417</v>
+        <v>125401297</v>
       </c>
       <c r="B55" t="n">
         <v>92293</v>
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>813952</v>
+        <v>813885</v>
       </c>
       <c r="R55" t="n">
-        <v>7355835</v>
+        <v>7355896</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6191,19 +6191,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125401297</v>
+        <v>125394417</v>
       </c>
       <c r="B56" t="n">
         <v>92293</v>
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>813885</v>
+        <v>813952</v>
       </c>
       <c r="R56" t="n">
-        <v>7355896</v>
+        <v>7355835</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6293,22 +6293,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125401314</v>
+        <v>125392590</v>
       </c>
       <c r="B57" t="n">
-        <v>78547</v>
+        <v>90977</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6317,25 +6317,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6345,10 +6345,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>813899</v>
+        <v>813970</v>
       </c>
       <c r="R57" t="n">
-        <v>7355975</v>
+        <v>7355771</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6395,22 +6395,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125392590</v>
+        <v>125394420</v>
       </c>
       <c r="B58" t="n">
-        <v>90977</v>
+        <v>92293</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6423,21 +6423,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6447,13 +6447,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>813970</v>
+        <v>813977</v>
       </c>
       <c r="R58" t="n">
-        <v>7355771</v>
+        <v>7355690</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6497,22 +6497,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125394420</v>
+        <v>125401314</v>
       </c>
       <c r="B59" t="n">
-        <v>92293</v>
+        <v>78547</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6521,25 +6521,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6549,13 +6549,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>813977</v>
+        <v>813899</v>
       </c>
       <c r="R59" t="n">
-        <v>7355690</v>
+        <v>7355975</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6599,12 +6599,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6815,10 +6815,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125393628</v>
+        <v>125392595</v>
       </c>
       <c r="B62" t="n">
-        <v>78194</v>
+        <v>92293</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6827,25 +6827,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6855,13 +6855,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>813979</v>
+        <v>813850</v>
       </c>
       <c r="R62" t="n">
-        <v>7355768</v>
+        <v>7355937</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6905,22 +6905,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125392595</v>
+        <v>125393628</v>
       </c>
       <c r="B63" t="n">
-        <v>92293</v>
+        <v>78194</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6929,25 +6929,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6957,13 +6957,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>813850</v>
+        <v>813979</v>
       </c>
       <c r="R63" t="n">
-        <v>7355937</v>
+        <v>7355768</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7007,12 +7007,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -9164,6 +9164,955 @@
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>125417988</v>
+      </c>
+      <c r="B85" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Bergträskryggen, Nb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>814016</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7355686</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>125417990</v>
+      </c>
+      <c r="B86" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Bergträskryggen, Nb</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>814036</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7355516</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>125417989</v>
+      </c>
+      <c r="B87" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Bergträskryggen, Nb</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>814054</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7355732</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>125433170</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Bergträskryggen, Nb</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>813923</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7355691</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>125417991</v>
+      </c>
+      <c r="B89" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Bergträskryggen, Nb</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>813973</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7355786</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>125433174</v>
+      </c>
+      <c r="B90" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Bergträskryggen, Nb</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>813928</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7355688</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>125433171</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Bergträskryggen, Nb</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>814007</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7355824</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>125433172</v>
+      </c>
+      <c r="B92" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Bergträskryggen, Nb</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>813909</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7355667</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>125433173</v>
+      </c>
+      <c r="B93" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Bergträskryggen, Nb</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>813919</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7355726</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125392267</v>
+        <v>125401318</v>
       </c>
       <c r="B2" t="n">
-        <v>90051</v>
+        <v>78455</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>814049</v>
+        <v>814001</v>
       </c>
       <c r="R2" t="n">
-        <v>7355602</v>
+        <v>7355662</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125392503</v>
+        <v>125393621</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>814058</v>
+        <v>813934</v>
       </c>
       <c r="R3" t="n">
-        <v>7355447</v>
+        <v>7355844</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125401298</v>
+        <v>125392504</v>
       </c>
       <c r="B4" t="n">
         <v>92293</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>813922</v>
+        <v>813963</v>
       </c>
       <c r="R4" t="n">
-        <v>7355853</v>
+        <v>7355408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125401310</v>
+        <v>125393618</v>
       </c>
       <c r="B5" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>814093</v>
+        <v>813976</v>
       </c>
       <c r="R5" t="n">
-        <v>7355601</v>
+        <v>7355749</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125401318</v>
+        <v>125392505</v>
       </c>
       <c r="B6" t="n">
-        <v>78455</v>
+        <v>92293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>814001</v>
+        <v>813992</v>
       </c>
       <c r="R6" t="n">
-        <v>7355662</v>
+        <v>7355418</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125392596</v>
+        <v>125393623</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>78455</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>813911</v>
+        <v>814062</v>
       </c>
       <c r="R7" t="n">
-        <v>7355874</v>
+        <v>7355547</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125393618</v>
+        <v>125392272</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>91172</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>813976</v>
+        <v>814011</v>
       </c>
       <c r="R8" t="n">
-        <v>7355749</v>
+        <v>7355730</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125393613</v>
+        <v>125394417</v>
       </c>
       <c r="B9" t="n">
-        <v>78834</v>
+        <v>92293</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>813953</v>
+        <v>813952</v>
       </c>
       <c r="R9" t="n">
-        <v>7355711</v>
+        <v>7355835</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125394416</v>
+        <v>125392494</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>90051</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>814013</v>
+        <v>814004</v>
       </c>
       <c r="R10" t="n">
-        <v>7355681</v>
+        <v>7355434</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1569,11 +1569,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1586,19 +1581,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125392505</v>
+        <v>125392275</v>
       </c>
       <c r="B11" t="n">
         <v>92293</v>
@@ -1638,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>813992</v>
+        <v>814068</v>
       </c>
       <c r="R11" t="n">
-        <v>7355418</v>
+        <v>7355802</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1688,22 +1683,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125392499</v>
+        <v>125401323</v>
       </c>
       <c r="B12" t="n">
-        <v>92490</v>
+        <v>92293</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,13 +1735,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>814055</v>
+        <v>813969</v>
       </c>
       <c r="R12" t="n">
-        <v>7355488</v>
+        <v>7355700</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1776,11 +1771,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,22 +1785,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125401313</v>
+        <v>125401297</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>92293</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>813998</v>
+        <v>813885</v>
       </c>
       <c r="R13" t="n">
-        <v>7355672</v>
+        <v>7355896</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1883,11 +1873,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,22 +1887,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125401317</v>
+        <v>125401301</v>
       </c>
       <c r="B14" t="n">
-        <v>78455</v>
+        <v>92287</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,13 +1939,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>813998</v>
+        <v>814046</v>
       </c>
       <c r="R14" t="n">
-        <v>7355852</v>
+        <v>7355641</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2004,22 +1989,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125401292</v>
+        <v>125392590</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>90977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,13 +2041,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>813980</v>
+        <v>813970</v>
       </c>
       <c r="R15" t="n">
-        <v>7355837</v>
+        <v>7355771</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2092,11 +2077,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2111,22 +2091,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125392497</v>
+        <v>125392508</v>
       </c>
       <c r="B16" t="n">
-        <v>92285</v>
+        <v>77738</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>6487</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>814027</v>
+        <v>814001</v>
       </c>
       <c r="R16" t="n">
-        <v>7355486</v>
+        <v>7355442</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125392502</v>
+        <v>125403784</v>
       </c>
       <c r="B17" t="n">
-        <v>91264</v>
+        <v>92293</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,13 +2245,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>813982</v>
+        <v>813985</v>
       </c>
       <c r="R17" t="n">
-        <v>7355407</v>
+        <v>7355756</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2315,19 +2295,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125392592</v>
+        <v>125392271</v>
       </c>
       <c r="B18" t="n">
         <v>78547</v>
@@ -2367,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>813924</v>
+        <v>813991</v>
       </c>
       <c r="R18" t="n">
-        <v>7355940</v>
+        <v>7355833</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2417,22 +2397,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125393615</v>
+        <v>125392267</v>
       </c>
       <c r="B19" t="n">
-        <v>78547</v>
+        <v>90051</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,13 +2449,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>814053</v>
+        <v>814049</v>
       </c>
       <c r="R19" t="n">
-        <v>7355646</v>
+        <v>7355602</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2519,22 +2499,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125393611</v>
+        <v>125401288</v>
       </c>
       <c r="B20" t="n">
-        <v>79399</v>
+        <v>90934</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>3242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>814063</v>
+        <v>813970</v>
       </c>
       <c r="R20" t="n">
-        <v>7355649</v>
+        <v>7355705</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2621,19 +2601,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125393602</v>
+        <v>125393609</v>
       </c>
       <c r="B21" t="n">
         <v>79428</v>
@@ -2673,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>814085</v>
+        <v>814066</v>
       </c>
       <c r="R21" t="n">
-        <v>7355609</v>
+        <v>7355537</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125393607</v>
+        <v>125393602</v>
       </c>
       <c r="B22" t="n">
         <v>79428</v>
@@ -2775,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>813971</v>
+        <v>814085</v>
       </c>
       <c r="R22" t="n">
-        <v>7355703</v>
+        <v>7355609</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125401325</v>
+        <v>125392507</v>
       </c>
       <c r="B23" t="n">
-        <v>78194</v>
+        <v>92293</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,25 +2829,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,13 +2857,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>814093</v>
+        <v>814049</v>
       </c>
       <c r="R23" t="n">
-        <v>7355602</v>
+        <v>7355489</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2927,22 +2907,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125393614</v>
+        <v>125393608</v>
       </c>
       <c r="B24" t="n">
-        <v>78834</v>
+        <v>79428</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,25 +2931,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>814021</v>
+        <v>814054</v>
       </c>
       <c r="R24" t="n">
-        <v>7355670</v>
+        <v>7355641</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125393609</v>
+        <v>125393607</v>
       </c>
       <c r="B25" t="n">
         <v>79428</v>
@@ -3081,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>814066</v>
+        <v>813971</v>
       </c>
       <c r="R25" t="n">
-        <v>7355537</v>
+        <v>7355703</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125394419</v>
+        <v>125393603</v>
       </c>
       <c r="B26" t="n">
-        <v>92293</v>
+        <v>79428</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,25 +3135,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>813962</v>
+        <v>813848</v>
       </c>
       <c r="R26" t="n">
-        <v>7355721</v>
+        <v>7355853</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,19 +3213,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125392504</v>
+        <v>125401321</v>
       </c>
       <c r="B27" t="n">
         <v>92293</v>
@@ -3285,13 +3265,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>813963</v>
+        <v>813851</v>
       </c>
       <c r="R27" t="n">
-        <v>7355408</v>
+        <v>7355951</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3335,22 +3315,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125401324</v>
+        <v>125392591</v>
       </c>
       <c r="B28" t="n">
-        <v>92287</v>
+        <v>79428</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3363,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>813960</v>
+        <v>813924</v>
       </c>
       <c r="R28" t="n">
-        <v>7355731</v>
+        <v>7355940</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3437,22 +3417,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125393626</v>
+        <v>125393606</v>
       </c>
       <c r="B29" t="n">
-        <v>78194</v>
+        <v>79428</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>813874</v>
+        <v>813976</v>
       </c>
       <c r="R29" t="n">
-        <v>7355877</v>
+        <v>7355749</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125392495</v>
+        <v>125392597</v>
       </c>
       <c r="B30" t="n">
-        <v>56722</v>
+        <v>92293</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3567,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3591,13 +3571,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>814057</v>
+        <v>814123</v>
       </c>
       <c r="R30" t="n">
-        <v>7355446</v>
+        <v>7355495</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3641,19 +3621,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125392507</v>
+        <v>125392503</v>
       </c>
       <c r="B31" t="n">
         <v>92293</v>
@@ -3693,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>814049</v>
+        <v>814058</v>
       </c>
       <c r="R31" t="n">
-        <v>7355489</v>
+        <v>7355447</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,7 +3735,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125401321</v>
+        <v>125392596</v>
       </c>
       <c r="B32" t="n">
         <v>92293</v>
@@ -3795,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>813851</v>
+        <v>813911</v>
       </c>
       <c r="R32" t="n">
-        <v>7355951</v>
+        <v>7355874</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3845,22 +3825,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125392272</v>
+        <v>125401311</v>
       </c>
       <c r="B33" t="n">
-        <v>91172</v>
+        <v>79428</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3869,25 +3849,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3897,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>814011</v>
+        <v>813899</v>
       </c>
       <c r="R33" t="n">
-        <v>7355730</v>
+        <v>7355971</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3947,22 +3927,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125393621</v>
+        <v>125392499</v>
       </c>
       <c r="B34" t="n">
-        <v>78546</v>
+        <v>92490</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3975,21 +3955,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3999,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>813934</v>
+        <v>814055</v>
       </c>
       <c r="R34" t="n">
-        <v>7355844</v>
+        <v>7355488</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4037,6 +4017,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4049,22 +4034,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125393608</v>
+        <v>125394416</v>
       </c>
       <c r="B35" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4073,25 +4058,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4101,10 +4086,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>814054</v>
+        <v>814013</v>
       </c>
       <c r="R35" t="n">
-        <v>7355641</v>
+        <v>7355681</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4139,6 +4124,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4151,22 +4141,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125392494</v>
+        <v>125401317</v>
       </c>
       <c r="B36" t="n">
-        <v>90051</v>
+        <v>78455</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,21 +4169,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4203,13 +4193,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>814004</v>
+        <v>813998</v>
       </c>
       <c r="R36" t="n">
-        <v>7355434</v>
+        <v>7355852</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4253,22 +4243,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125393620</v>
+        <v>125392496</v>
       </c>
       <c r="B37" t="n">
-        <v>80763</v>
+        <v>56722</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4277,25 +4267,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1049</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>813875</v>
+        <v>814003</v>
       </c>
       <c r="R37" t="n">
-        <v>7355877</v>
+        <v>7355454</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4355,22 +4345,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125393610</v>
+        <v>125401296</v>
       </c>
       <c r="B38" t="n">
-        <v>79399</v>
+        <v>92293</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4379,25 +4369,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4407,10 +4397,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>813948</v>
+        <v>813777</v>
       </c>
       <c r="R38" t="n">
-        <v>7355861</v>
+        <v>7355862</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4445,6 +4435,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Häxring</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4457,19 +4452,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125392275</v>
+        <v>125392595</v>
       </c>
       <c r="B39" t="n">
         <v>92293</v>
@@ -4509,10 +4504,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>814068</v>
+        <v>813850</v>
       </c>
       <c r="R39" t="n">
-        <v>7355802</v>
+        <v>7355937</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4559,22 +4554,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125393605</v>
+        <v>125393619</v>
       </c>
       <c r="B40" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,21 +4582,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4611,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>813983</v>
+        <v>814069</v>
       </c>
       <c r="R40" t="n">
-        <v>7355808</v>
+        <v>7355541</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,10 +4668,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125393622</v>
+        <v>125392268</v>
       </c>
       <c r="B41" t="n">
-        <v>78546</v>
+        <v>92490</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4689,21 +4684,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4713,13 +4708,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>814058</v>
+        <v>814049</v>
       </c>
       <c r="R41" t="n">
-        <v>7355641</v>
+        <v>7355786</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4763,22 +4758,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125392506</v>
+        <v>125393620</v>
       </c>
       <c r="B42" t="n">
-        <v>92293</v>
+        <v>80763</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4787,25 +4782,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4815,10 +4810,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>813996</v>
+        <v>813875</v>
       </c>
       <c r="R42" t="n">
-        <v>7355461</v>
+        <v>7355877</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4865,22 +4860,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125392597</v>
+        <v>125392497</v>
       </c>
       <c r="B43" t="n">
-        <v>92293</v>
+        <v>92285</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4889,25 +4884,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4917,13 +4912,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>814123</v>
+        <v>814027</v>
       </c>
       <c r="R43" t="n">
-        <v>7355495</v>
+        <v>7355486</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4967,22 +4962,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125393629</v>
+        <v>125401298</v>
       </c>
       <c r="B44" t="n">
-        <v>78194</v>
+        <v>92293</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4991,25 +4986,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5019,10 +5014,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>814063</v>
+        <v>813922</v>
       </c>
       <c r="R44" t="n">
-        <v>7355649</v>
+        <v>7355853</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5069,19 +5064,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125393619</v>
+        <v>125393615</v>
       </c>
       <c r="B45" t="n">
         <v>78547</v>
@@ -5121,10 +5116,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>814069</v>
+        <v>814053</v>
       </c>
       <c r="R45" t="n">
-        <v>7355541</v>
+        <v>7355646</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5183,10 +5178,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125401301</v>
+        <v>125393616</v>
       </c>
       <c r="B46" t="n">
-        <v>92287</v>
+        <v>78547</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,21 +5194,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5223,10 +5218,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>814046</v>
+        <v>813859</v>
       </c>
       <c r="R46" t="n">
-        <v>7355641</v>
+        <v>7355858</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5273,22 +5268,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125401299</v>
+        <v>125401314</v>
       </c>
       <c r="B47" t="n">
-        <v>92293</v>
+        <v>78547</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5297,25 +5292,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5325,13 +5320,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>814052</v>
+        <v>813899</v>
       </c>
       <c r="R47" t="n">
-        <v>7355644</v>
+        <v>7355975</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5375,19 +5370,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125401322</v>
+        <v>125403785</v>
       </c>
       <c r="B48" t="n">
         <v>92293</v>
@@ -5427,10 +5422,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>813963</v>
+        <v>814010</v>
       </c>
       <c r="R48" t="n">
-        <v>7355778</v>
+        <v>7355734</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5477,22 +5472,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125392274</v>
+        <v>125393624</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5501,25 +5496,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5529,13 +5524,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>814062</v>
+        <v>813879</v>
       </c>
       <c r="R49" t="n">
-        <v>7355640</v>
+        <v>7355876</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5579,22 +5574,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125401311</v>
+        <v>125392506</v>
       </c>
       <c r="B50" t="n">
-        <v>79428</v>
+        <v>92293</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5603,25 +5598,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5631,13 +5626,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>813899</v>
+        <v>813996</v>
       </c>
       <c r="R50" t="n">
-        <v>7355971</v>
+        <v>7355461</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5681,22 +5676,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125393603</v>
+        <v>125401313</v>
       </c>
       <c r="B51" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5705,25 +5700,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5733,13 +5728,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>813848</v>
+        <v>813998</v>
       </c>
       <c r="R51" t="n">
-        <v>7355853</v>
+        <v>7355672</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5769,6 +5764,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5783,22 +5783,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125392271</v>
+        <v>125393611</v>
       </c>
       <c r="B52" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5811,21 +5811,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5835,13 +5835,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>813991</v>
+        <v>814063</v>
       </c>
       <c r="R52" t="n">
-        <v>7355833</v>
+        <v>7355649</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5885,22 +5885,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125401289</v>
+        <v>125394420</v>
       </c>
       <c r="B53" t="n">
-        <v>90977</v>
+        <v>92293</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,21 +5913,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>813966</v>
+        <v>813977</v>
       </c>
       <c r="R53" t="n">
-        <v>7355769</v>
+        <v>7355690</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5987,22 +5987,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125401315</v>
+        <v>125401292</v>
       </c>
       <c r="B54" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6011,25 +6011,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6039,13 +6039,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>813936</v>
+        <v>813980</v>
       </c>
       <c r="R54" t="n">
-        <v>7355848</v>
+        <v>7355837</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6075,6 +6075,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6089,19 +6094,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125401297</v>
+        <v>125401322</v>
       </c>
       <c r="B55" t="n">
         <v>92293</v>
@@ -6141,13 +6146,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>813885</v>
+        <v>813963</v>
       </c>
       <c r="R55" t="n">
-        <v>7355896</v>
+        <v>7355778</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6191,22 +6196,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125394417</v>
+        <v>125393622</v>
       </c>
       <c r="B56" t="n">
-        <v>92293</v>
+        <v>78546</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6215,25 +6220,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6243,10 +6248,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>813952</v>
+        <v>814058</v>
       </c>
       <c r="R56" t="n">
-        <v>7355835</v>
+        <v>7355641</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6293,22 +6298,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125392590</v>
+        <v>125393613</v>
       </c>
       <c r="B57" t="n">
-        <v>90977</v>
+        <v>78834</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6321,21 +6326,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6345,13 +6350,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>813970</v>
+        <v>813953</v>
       </c>
       <c r="R57" t="n">
-        <v>7355771</v>
+        <v>7355711</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6395,22 +6400,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125394420</v>
+        <v>125393617</v>
       </c>
       <c r="B58" t="n">
-        <v>92293</v>
+        <v>78547</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6419,25 +6424,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6447,10 +6452,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>813977</v>
+        <v>813999</v>
       </c>
       <c r="R58" t="n">
-        <v>7355690</v>
+        <v>7355845</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6497,22 +6502,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125401314</v>
+        <v>125403783</v>
       </c>
       <c r="B59" t="n">
-        <v>78547</v>
+        <v>92293</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6521,25 +6526,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6549,10 +6554,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>813899</v>
+        <v>813951</v>
       </c>
       <c r="R59" t="n">
-        <v>7355975</v>
+        <v>7355737</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6599,22 +6604,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125403783</v>
+        <v>125393625</v>
       </c>
       <c r="B60" t="n">
-        <v>92293</v>
+        <v>77738</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6623,25 +6628,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6651,13 +6656,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>813951</v>
+        <v>813993</v>
       </c>
       <c r="R60" t="n">
-        <v>7355737</v>
+        <v>7355850</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6701,22 +6706,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125403784</v>
+        <v>125392592</v>
       </c>
       <c r="B61" t="n">
-        <v>92293</v>
+        <v>78547</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6725,25 +6730,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6753,10 +6758,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>813985</v>
+        <v>813924</v>
       </c>
       <c r="R61" t="n">
-        <v>7355756</v>
+        <v>7355940</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6803,22 +6808,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125392595</v>
+        <v>125392502</v>
       </c>
       <c r="B62" t="n">
-        <v>92293</v>
+        <v>91264</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6827,25 +6832,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6855,13 +6860,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>813850</v>
+        <v>813982</v>
       </c>
       <c r="R62" t="n">
-        <v>7355937</v>
+        <v>7355407</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6905,22 +6910,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125393628</v>
+        <v>125401289</v>
       </c>
       <c r="B63" t="n">
-        <v>78194</v>
+        <v>90977</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6929,25 +6934,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6957,10 +6962,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>813979</v>
+        <v>813966</v>
       </c>
       <c r="R63" t="n">
-        <v>7355768</v>
+        <v>7355769</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7007,22 +7012,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125401312</v>
+        <v>125401319</v>
       </c>
       <c r="B64" t="n">
-        <v>79428</v>
+        <v>92293</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7031,25 +7036,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7059,7 +7064,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>813943</v>
+        <v>813998</v>
       </c>
       <c r="R64" t="n">
         <v>7355850</v>
@@ -7121,10 +7126,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125401319</v>
+        <v>125393629</v>
       </c>
       <c r="B65" t="n">
-        <v>92293</v>
+        <v>78194</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7133,25 +7138,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7161,13 +7166,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>813998</v>
+        <v>814063</v>
       </c>
       <c r="R65" t="n">
-        <v>7355850</v>
+        <v>7355649</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7211,22 +7216,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125393625</v>
+        <v>125393605</v>
       </c>
       <c r="B66" t="n">
-        <v>77738</v>
+        <v>79428</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7239,21 +7244,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7263,10 +7268,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>813993</v>
+        <v>813983</v>
       </c>
       <c r="R66" t="n">
-        <v>7355850</v>
+        <v>7355808</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7325,10 +7330,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125393617</v>
+        <v>125394419</v>
       </c>
       <c r="B67" t="n">
-        <v>78547</v>
+        <v>92293</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7337,25 +7342,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7365,10 +7370,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>813999</v>
+        <v>813962</v>
       </c>
       <c r="R67" t="n">
-        <v>7355845</v>
+        <v>7355721</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7415,22 +7420,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125393623</v>
+        <v>125393628</v>
       </c>
       <c r="B68" t="n">
-        <v>78455</v>
+        <v>78194</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7443,21 +7448,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7467,10 +7472,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>814062</v>
+        <v>813979</v>
       </c>
       <c r="R68" t="n">
-        <v>7355547</v>
+        <v>7355768</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7529,10 +7534,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125401296</v>
+        <v>125401312</v>
       </c>
       <c r="B69" t="n">
-        <v>92293</v>
+        <v>79428</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7541,25 +7546,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7569,13 +7574,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>813777</v>
+        <v>813943</v>
       </c>
       <c r="R69" t="n">
-        <v>7355862</v>
+        <v>7355850</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7605,11 +7610,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Häxring</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7624,22 +7624,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125403785</v>
+        <v>125393614</v>
       </c>
       <c r="B70" t="n">
-        <v>92293</v>
+        <v>78834</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7652,21 +7652,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7676,13 +7676,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>814010</v>
+        <v>814021</v>
       </c>
       <c r="R70" t="n">
-        <v>7355734</v>
+        <v>7355670</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7726,22 +7726,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125393627</v>
+        <v>125392594</v>
       </c>
       <c r="B71" t="n">
-        <v>78194</v>
+        <v>92293</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7750,25 +7750,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7778,13 +7778,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>813993</v>
+        <v>814057</v>
       </c>
       <c r="R71" t="n">
-        <v>7355850</v>
+        <v>7355682</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7828,22 +7828,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125401323</v>
+        <v>125392498</v>
       </c>
       <c r="B72" t="n">
-        <v>92293</v>
+        <v>78834</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7856,21 +7856,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>813969</v>
+        <v>814002</v>
       </c>
       <c r="R72" t="n">
-        <v>7355700</v>
+        <v>7355412</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7930,22 +7930,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125392268</v>
+        <v>125393626</v>
       </c>
       <c r="B73" t="n">
-        <v>92490</v>
+        <v>78194</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7958,21 +7958,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7982,13 +7982,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>814049</v>
+        <v>813874</v>
       </c>
       <c r="R73" t="n">
-        <v>7355786</v>
+        <v>7355877</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8032,22 +8032,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125393616</v>
+        <v>125393627</v>
       </c>
       <c r="B74" t="n">
-        <v>78547</v>
+        <v>78194</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8060,21 +8060,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>813859</v>
+        <v>813993</v>
       </c>
       <c r="R74" t="n">
-        <v>7355858</v>
+        <v>7355850</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8146,10 +8146,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125392508</v>
+        <v>125392274</v>
       </c>
       <c r="B75" t="n">
-        <v>77738</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8162,21 +8162,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8186,13 +8186,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>814001</v>
+        <v>814062</v>
       </c>
       <c r="R75" t="n">
-        <v>7355442</v>
+        <v>7355640</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8236,22 +8236,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125401303</v>
+        <v>125392495</v>
       </c>
       <c r="B76" t="n">
-        <v>78194</v>
+        <v>56722</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8260,25 +8260,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>813955</v>
+        <v>814057</v>
       </c>
       <c r="R76" t="n">
-        <v>7355863</v>
+        <v>7355446</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8338,22 +8338,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125401288</v>
+        <v>125401310</v>
       </c>
       <c r="B77" t="n">
-        <v>90934</v>
+        <v>79428</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8366,21 +8366,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8390,13 +8390,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>813970</v>
+        <v>814093</v>
       </c>
       <c r="R77" t="n">
-        <v>7355705</v>
+        <v>7355601</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8440,12 +8440,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8554,10 +8554,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125393624</v>
+        <v>125401303</v>
       </c>
       <c r="B79" t="n">
-        <v>92293</v>
+        <v>78194</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8566,25 +8566,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8594,10 +8594,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>813879</v>
+        <v>813955</v>
       </c>
       <c r="R79" t="n">
-        <v>7355876</v>
+        <v>7355863</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8644,22 +8644,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125392594</v>
+        <v>125401325</v>
       </c>
       <c r="B80" t="n">
-        <v>92293</v>
+        <v>78194</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8668,25 +8668,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8696,10 +8696,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>814057</v>
+        <v>814093</v>
       </c>
       <c r="R80" t="n">
-        <v>7355682</v>
+        <v>7355602</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8746,22 +8746,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125392591</v>
+        <v>125393610</v>
       </c>
       <c r="B81" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8774,21 +8774,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8798,13 +8798,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>813924</v>
+        <v>813948</v>
       </c>
       <c r="R81" t="n">
-        <v>7355940</v>
+        <v>7355861</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8848,22 +8848,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125393606</v>
+        <v>125401315</v>
       </c>
       <c r="B82" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8876,21 +8876,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8900,13 +8900,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>813976</v>
+        <v>813936</v>
       </c>
       <c r="R82" t="n">
-        <v>7355749</v>
+        <v>7355848</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8950,22 +8950,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125392498</v>
+        <v>125401324</v>
       </c>
       <c r="B83" t="n">
-        <v>78834</v>
+        <v>92287</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8974,25 +8974,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9002,13 +9002,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>814002</v>
+        <v>813960</v>
       </c>
       <c r="R83" t="n">
-        <v>7355412</v>
+        <v>7355731</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9052,22 +9052,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125392496</v>
+        <v>125401299</v>
       </c>
       <c r="B84" t="n">
-        <v>56722</v>
+        <v>92293</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9080,21 +9080,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>814003</v>
+        <v>814052</v>
       </c>
       <c r="R84" t="n">
-        <v>7355454</v>
+        <v>7355644</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9154,22 +9154,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125417988</v>
+        <v>125433174</v>
       </c>
       <c r="B85" t="n">
-        <v>56722</v>
+        <v>92293</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9182,42 +9182,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Bergträskryggen, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>814016</v>
+        <v>813928</v>
       </c>
       <c r="R85" t="n">
-        <v>7355686</v>
+        <v>7355688</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9258,25 +9250,26 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125417990</v>
+        <v>125417988</v>
       </c>
       <c r="B86" t="n">
         <v>56722</v>
@@ -9314,7 +9307,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9324,10 +9317,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>814036</v>
+        <v>814016</v>
       </c>
       <c r="R86" t="n">
-        <v>7355516</v>
+        <v>7355686</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9360,11 +9353,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9391,10 +9379,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125417989</v>
+        <v>125433171</v>
       </c>
       <c r="B87" t="n">
-        <v>56722</v>
+        <v>79399</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9403,46 +9391,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Bergträskryggen, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>814054</v>
+        <v>814007</v>
       </c>
       <c r="R87" t="n">
-        <v>7355732</v>
+        <v>7355824</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9489,22 +9469,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125433170</v>
+        <v>125433172</v>
       </c>
       <c r="B88" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9517,21 +9497,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9541,10 +9521,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>813923</v>
+        <v>813909</v>
       </c>
       <c r="R88" t="n">
-        <v>7355691</v>
+        <v>7355667</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9603,10 +9583,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125417991</v>
+        <v>125417989</v>
       </c>
       <c r="B89" t="n">
-        <v>92293</v>
+        <v>56722</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9619,34 +9599,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Bergträskryggen, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>813973</v>
+        <v>814054</v>
       </c>
       <c r="R89" t="n">
-        <v>7355786</v>
+        <v>7355732</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9705,7 +9693,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125433174</v>
+        <v>125417991</v>
       </c>
       <c r="B90" t="n">
         <v>92293</v>
@@ -9745,10 +9733,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>813928</v>
+        <v>813973</v>
       </c>
       <c r="R90" t="n">
-        <v>7355688</v>
+        <v>7355786</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9789,29 +9777,28 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125433171</v>
+        <v>125433170</v>
       </c>
       <c r="B91" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9824,21 +9811,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9848,10 +9835,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>814007</v>
+        <v>813923</v>
       </c>
       <c r="R91" t="n">
-        <v>7355824</v>
+        <v>7355691</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9910,10 +9897,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125433172</v>
+        <v>125417990</v>
       </c>
       <c r="B92" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9922,38 +9909,46 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bergträskryggen, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>813909</v>
+        <v>814036</v>
       </c>
       <c r="R92" t="n">
-        <v>7355667</v>
+        <v>7355516</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9988,6 +9983,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -10000,12 +10000,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10113,6 +10113,210 @@
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>125395032</v>
+      </c>
+      <c r="B94" t="n">
+        <v>90934</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Bergträskryggen, Nb</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>813965</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7355712</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>125395033</v>
+      </c>
+      <c r="B95" t="n">
+        <v>91264</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>65</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Bergträskryggen, Nb</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>814076</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7355650</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125401318</v>
+        <v>125401301</v>
       </c>
       <c r="B2" t="n">
-        <v>78455</v>
+        <v>92442</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>814001</v>
+        <v>814046</v>
       </c>
       <c r="R2" t="n">
-        <v>7355662</v>
+        <v>7355641</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125393621</v>
+        <v>125401325</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>78331</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>813934</v>
+        <v>814093</v>
       </c>
       <c r="R3" t="n">
-        <v>7355844</v>
+        <v>7355602</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125392504</v>
+        <v>125392591</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>79565</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>813963</v>
+        <v>813924</v>
       </c>
       <c r="R4" t="n">
-        <v>7355408</v>
+        <v>7355940</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125393618</v>
+        <v>125394417</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>92448</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>813976</v>
+        <v>813952</v>
       </c>
       <c r="R5" t="n">
-        <v>7355749</v>
+        <v>7355835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125392505</v>
+        <v>125393627</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>78331</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>813992</v>
+        <v>813993</v>
       </c>
       <c r="R6" t="n">
-        <v>7355418</v>
+        <v>7355850</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125393623</v>
+        <v>125393624</v>
       </c>
       <c r="B7" t="n">
-        <v>78455</v>
+        <v>92448</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>814062</v>
+        <v>813879</v>
       </c>
       <c r="R7" t="n">
-        <v>7355547</v>
+        <v>7355876</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125392272</v>
+        <v>125392494</v>
       </c>
       <c r="B8" t="n">
-        <v>91172</v>
+        <v>90204</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>814011</v>
+        <v>814004</v>
       </c>
       <c r="R8" t="n">
-        <v>7355730</v>
+        <v>7355434</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125394417</v>
+        <v>125403785</v>
       </c>
       <c r="B9" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>813952</v>
+        <v>814010</v>
       </c>
       <c r="R9" t="n">
-        <v>7355835</v>
+        <v>7355734</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125392494</v>
+        <v>125393616</v>
       </c>
       <c r="B10" t="n">
-        <v>90051</v>
+        <v>78684</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>814004</v>
+        <v>813859</v>
       </c>
       <c r="R10" t="n">
-        <v>7355434</v>
+        <v>7355858</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,22 +1581,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125392275</v>
+        <v>125392501</v>
       </c>
       <c r="B11" t="n">
-        <v>92293</v>
+        <v>91784</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5454</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>814068</v>
+        <v>814052</v>
       </c>
       <c r="R11" t="n">
-        <v>7355802</v>
+        <v>7355484</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1683,22 +1683,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125401323</v>
+        <v>125392594</v>
       </c>
       <c r="B12" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>813969</v>
+        <v>814057</v>
       </c>
       <c r="R12" t="n">
-        <v>7355700</v>
+        <v>7355682</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1785,22 +1785,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125401297</v>
+        <v>125401313</v>
       </c>
       <c r="B13" t="n">
-        <v>92293</v>
+        <v>56836</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>813885</v>
+        <v>813998</v>
       </c>
       <c r="R13" t="n">
-        <v>7355896</v>
+        <v>7355672</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1873,6 +1873,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,22 +1892,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125401301</v>
+        <v>125392268</v>
       </c>
       <c r="B14" t="n">
-        <v>92287</v>
+        <v>92646</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>814046</v>
+        <v>814049</v>
       </c>
       <c r="R14" t="n">
-        <v>7355641</v>
+        <v>7355786</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1989,22 +1994,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125392590</v>
+        <v>125392504</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>92448</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>813970</v>
+        <v>813963</v>
       </c>
       <c r="R15" t="n">
-        <v>7355771</v>
+        <v>7355408</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2091,22 +2096,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125392508</v>
+        <v>125393614</v>
       </c>
       <c r="B16" t="n">
-        <v>77738</v>
+        <v>78971</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6487</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>814001</v>
+        <v>814021</v>
       </c>
       <c r="R16" t="n">
-        <v>7355442</v>
+        <v>7355670</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,22 +2198,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125403784</v>
+        <v>125393609</v>
       </c>
       <c r="B17" t="n">
-        <v>92293</v>
+        <v>79565</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,13 +2250,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>813985</v>
+        <v>814066</v>
       </c>
       <c r="R17" t="n">
-        <v>7355756</v>
+        <v>7355537</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2295,22 +2300,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125392271</v>
+        <v>125392507</v>
       </c>
       <c r="B18" t="n">
-        <v>78547</v>
+        <v>92448</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>813991</v>
+        <v>814049</v>
       </c>
       <c r="R18" t="n">
-        <v>7355833</v>
+        <v>7355489</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2397,22 +2402,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125392267</v>
+        <v>125392275</v>
       </c>
       <c r="B19" t="n">
-        <v>90051</v>
+        <v>92448</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>814049</v>
+        <v>814068</v>
       </c>
       <c r="R19" t="n">
-        <v>7355602</v>
+        <v>7355802</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2511,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125401288</v>
+        <v>125403783</v>
       </c>
       <c r="B20" t="n">
-        <v>90934</v>
+        <v>92448</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,13 +2556,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>813970</v>
+        <v>813951</v>
       </c>
       <c r="R20" t="n">
-        <v>7355705</v>
+        <v>7355737</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2601,22 +2606,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125393609</v>
+        <v>125401321</v>
       </c>
       <c r="B21" t="n">
-        <v>79428</v>
+        <v>92448</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,13 +2658,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>814066</v>
+        <v>813851</v>
       </c>
       <c r="R21" t="n">
-        <v>7355537</v>
+        <v>7355951</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2703,22 +2708,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125393602</v>
+        <v>125403784</v>
       </c>
       <c r="B22" t="n">
-        <v>79428</v>
+        <v>92448</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2727,25 +2732,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,13 +2760,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>814085</v>
+        <v>813985</v>
       </c>
       <c r="R22" t="n">
-        <v>7355609</v>
+        <v>7355756</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2805,22 +2810,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125392507</v>
+        <v>125392272</v>
       </c>
       <c r="B23" t="n">
-        <v>92293</v>
+        <v>91326</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2829,25 +2834,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,13 +2862,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>814049</v>
+        <v>814011</v>
       </c>
       <c r="R23" t="n">
-        <v>7355489</v>
+        <v>7355730</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2907,22 +2912,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125393608</v>
+        <v>125392267</v>
       </c>
       <c r="B24" t="n">
-        <v>79428</v>
+        <v>90204</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,13 +2964,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>814054</v>
+        <v>814049</v>
       </c>
       <c r="R24" t="n">
-        <v>7355641</v>
+        <v>7355602</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3009,22 +3014,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125393607</v>
+        <v>125401299</v>
       </c>
       <c r="B25" t="n">
-        <v>79428</v>
+        <v>92448</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3033,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>813971</v>
+        <v>814052</v>
       </c>
       <c r="R25" t="n">
-        <v>7355703</v>
+        <v>7355644</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3111,22 +3116,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125393603</v>
+        <v>125393605</v>
       </c>
       <c r="B26" t="n">
-        <v>79428</v>
+        <v>79565</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3163,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>813848</v>
+        <v>813983</v>
       </c>
       <c r="R26" t="n">
-        <v>7355853</v>
+        <v>7355808</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125401321</v>
+        <v>125393626</v>
       </c>
       <c r="B27" t="n">
-        <v>92293</v>
+        <v>78331</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3237,25 +3242,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,13 +3270,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>813851</v>
+        <v>813874</v>
       </c>
       <c r="R27" t="n">
-        <v>7355951</v>
+        <v>7355877</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3315,22 +3320,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125392591</v>
+        <v>125393613</v>
       </c>
       <c r="B28" t="n">
-        <v>79428</v>
+        <v>78971</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3339,25 +3344,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,13 +3372,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>813924</v>
+        <v>813953</v>
       </c>
       <c r="R28" t="n">
-        <v>7355940</v>
+        <v>7355711</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3417,22 +3422,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125393606</v>
+        <v>125392590</v>
       </c>
       <c r="B29" t="n">
-        <v>79428</v>
+        <v>91131</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3441,25 +3446,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,13 +3474,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>813976</v>
+        <v>813970</v>
       </c>
       <c r="R29" t="n">
-        <v>7355749</v>
+        <v>7355771</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3519,22 +3524,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125392597</v>
+        <v>125401312</v>
       </c>
       <c r="B30" t="n">
-        <v>92293</v>
+        <v>79565</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3543,25 +3548,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3576,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>814123</v>
+        <v>813943</v>
       </c>
       <c r="R30" t="n">
-        <v>7355495</v>
+        <v>7355850</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3621,22 +3626,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125392503</v>
+        <v>125394416</v>
       </c>
       <c r="B31" t="n">
-        <v>92293</v>
+        <v>56836</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3654,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3678,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>814058</v>
+        <v>814013</v>
       </c>
       <c r="R31" t="n">
-        <v>7355447</v>
+        <v>7355681</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3711,6 +3716,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3723,22 +3733,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125392596</v>
+        <v>125393625</v>
       </c>
       <c r="B32" t="n">
-        <v>92293</v>
+        <v>77874</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3747,25 +3757,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,13 +3785,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>813911</v>
+        <v>813993</v>
       </c>
       <c r="R32" t="n">
-        <v>7355874</v>
+        <v>7355850</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3825,22 +3835,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125401311</v>
+        <v>125393603</v>
       </c>
       <c r="B33" t="n">
-        <v>79428</v>
+        <v>79565</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3877,13 +3887,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>813899</v>
+        <v>813848</v>
       </c>
       <c r="R33" t="n">
-        <v>7355971</v>
+        <v>7355853</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3927,22 +3937,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125392499</v>
+        <v>125392502</v>
       </c>
       <c r="B34" t="n">
-        <v>92490</v>
+        <v>91424</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3951,25 +3961,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>814055</v>
+        <v>813982</v>
       </c>
       <c r="R34" t="n">
-        <v>7355488</v>
+        <v>7355407</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4015,11 +4025,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4046,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125394416</v>
+        <v>125401314</v>
       </c>
       <c r="B35" t="n">
-        <v>56722</v>
+        <v>78684</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4058,25 +4063,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4086,13 +4091,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>814013</v>
+        <v>813899</v>
       </c>
       <c r="R35" t="n">
-        <v>7355681</v>
+        <v>7355975</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4122,11 +4127,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4141,22 +4141,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125401317</v>
+        <v>125393606</v>
       </c>
       <c r="B36" t="n">
-        <v>78455</v>
+        <v>79565</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4169,21 +4169,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4193,13 +4193,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>813998</v>
+        <v>813976</v>
       </c>
       <c r="R36" t="n">
-        <v>7355852</v>
+        <v>7355749</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4243,22 +4243,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125392496</v>
+        <v>125392597</v>
       </c>
       <c r="B37" t="n">
-        <v>56722</v>
+        <v>92448</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4271,21 +4271,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4295,13 +4295,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>814003</v>
+        <v>814123</v>
       </c>
       <c r="R37" t="n">
-        <v>7355454</v>
+        <v>7355495</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4345,22 +4345,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125401296</v>
+        <v>125393617</v>
       </c>
       <c r="B38" t="n">
-        <v>92293</v>
+        <v>78684</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4369,25 +4369,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>813777</v>
+        <v>813999</v>
       </c>
       <c r="R38" t="n">
-        <v>7355862</v>
+        <v>7355845</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4435,11 +4435,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Häxring</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4452,22 +4447,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125392595</v>
+        <v>125392499</v>
       </c>
       <c r="B39" t="n">
-        <v>92293</v>
+        <v>92646</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4476,25 +4471,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4504,13 +4499,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>813850</v>
+        <v>814055</v>
       </c>
       <c r="R39" t="n">
-        <v>7355937</v>
+        <v>7355488</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4540,6 +4535,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4554,22 +4554,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125393619</v>
+        <v>125401288</v>
       </c>
       <c r="B40" t="n">
-        <v>78547</v>
+        <v>91088</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4582,21 +4582,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>814069</v>
+        <v>813970</v>
       </c>
       <c r="R40" t="n">
-        <v>7355541</v>
+        <v>7355705</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4656,22 +4656,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125392268</v>
+        <v>125392595</v>
       </c>
       <c r="B41" t="n">
-        <v>92490</v>
+        <v>92448</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4680,25 +4680,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>814049</v>
+        <v>813850</v>
       </c>
       <c r="R41" t="n">
-        <v>7355786</v>
+        <v>7355937</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4758,12 +4758,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4773,7 +4773,7 @@
         <v>125393620</v>
       </c>
       <c r="B42" t="n">
-        <v>80763</v>
+        <v>80900</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4872,10 +4872,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125392497</v>
+        <v>125392506</v>
       </c>
       <c r="B43" t="n">
-        <v>92285</v>
+        <v>92448</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4884,25 +4884,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>814027</v>
+        <v>813996</v>
       </c>
       <c r="R43" t="n">
-        <v>7355486</v>
+        <v>7355461</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125401298</v>
+        <v>125392508</v>
       </c>
       <c r="B44" t="n">
-        <v>92293</v>
+        <v>77874</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4986,25 +4986,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5014,10 +5014,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>813922</v>
+        <v>814001</v>
       </c>
       <c r="R44" t="n">
-        <v>7355853</v>
+        <v>7355442</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5064,22 +5064,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125393615</v>
+        <v>125392596</v>
       </c>
       <c r="B45" t="n">
-        <v>78547</v>
+        <v>92448</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5088,25 +5088,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5116,13 +5116,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>814053</v>
+        <v>813911</v>
       </c>
       <c r="R45" t="n">
-        <v>7355646</v>
+        <v>7355874</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5166,22 +5166,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125393616</v>
+        <v>125393611</v>
       </c>
       <c r="B46" t="n">
-        <v>78547</v>
+        <v>79536</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5194,21 +5194,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>813859</v>
+        <v>814063</v>
       </c>
       <c r="R46" t="n">
-        <v>7355858</v>
+        <v>7355649</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5280,10 +5280,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125401314</v>
+        <v>125392592</v>
       </c>
       <c r="B47" t="n">
-        <v>78547</v>
+        <v>78684</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5320,10 +5320,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>813899</v>
+        <v>813924</v>
       </c>
       <c r="R47" t="n">
-        <v>7355975</v>
+        <v>7355940</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5370,22 +5370,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125403785</v>
+        <v>125401310</v>
       </c>
       <c r="B48" t="n">
-        <v>92293</v>
+        <v>79565</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5394,25 +5394,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>814010</v>
+        <v>814093</v>
       </c>
       <c r="R48" t="n">
-        <v>7355734</v>
+        <v>7355601</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5472,22 +5472,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125393624</v>
+        <v>125401324</v>
       </c>
       <c r="B49" t="n">
-        <v>92293</v>
+        <v>92442</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5496,25 +5496,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5524,13 +5524,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>813879</v>
+        <v>813960</v>
       </c>
       <c r="R49" t="n">
-        <v>7355876</v>
+        <v>7355731</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5574,22 +5574,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125392506</v>
+        <v>125401319</v>
       </c>
       <c r="B50" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5626,13 +5626,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>813996</v>
+        <v>813998</v>
       </c>
       <c r="R50" t="n">
-        <v>7355461</v>
+        <v>7355850</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5676,22 +5676,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125401313</v>
+        <v>125401315</v>
       </c>
       <c r="B51" t="n">
-        <v>56722</v>
+        <v>78684</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5700,25 +5700,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>813998</v>
+        <v>813936</v>
       </c>
       <c r="R51" t="n">
-        <v>7355672</v>
+        <v>7355848</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5764,11 +5764,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5795,10 +5790,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125393611</v>
+        <v>125393629</v>
       </c>
       <c r="B52" t="n">
-        <v>79399</v>
+        <v>78331</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5811,21 +5806,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5897,10 +5892,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125394420</v>
+        <v>125393621</v>
       </c>
       <c r="B53" t="n">
-        <v>92293</v>
+        <v>78683</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5909,25 +5904,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5937,10 +5932,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>813977</v>
+        <v>813934</v>
       </c>
       <c r="R53" t="n">
-        <v>7355690</v>
+        <v>7355844</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5987,22 +5982,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125401292</v>
+        <v>125393622</v>
       </c>
       <c r="B54" t="n">
-        <v>56722</v>
+        <v>78683</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6011,25 +6006,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6039,10 +6034,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>813980</v>
+        <v>814058</v>
       </c>
       <c r="R54" t="n">
-        <v>7355837</v>
+        <v>7355641</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6077,11 +6072,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6094,22 +6084,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125401322</v>
+        <v>125393607</v>
       </c>
       <c r="B55" t="n">
-        <v>92293</v>
+        <v>79565</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6118,25 +6108,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6146,13 +6136,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>813963</v>
+        <v>813971</v>
       </c>
       <c r="R55" t="n">
-        <v>7355778</v>
+        <v>7355703</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6196,22 +6186,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125393622</v>
+        <v>125392271</v>
       </c>
       <c r="B56" t="n">
-        <v>78546</v>
+        <v>78684</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6224,21 +6214,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6248,13 +6238,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>814058</v>
+        <v>813991</v>
       </c>
       <c r="R56" t="n">
-        <v>7355641</v>
+        <v>7355833</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6298,22 +6288,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125393613</v>
+        <v>125401317</v>
       </c>
       <c r="B57" t="n">
-        <v>78834</v>
+        <v>78592</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6322,25 +6312,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6350,13 +6340,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>813953</v>
+        <v>813998</v>
       </c>
       <c r="R57" t="n">
-        <v>7355711</v>
+        <v>7355852</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6400,22 +6390,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125393617</v>
+        <v>125392496</v>
       </c>
       <c r="B58" t="n">
-        <v>78547</v>
+        <v>56836</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6424,25 +6414,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6452,10 +6442,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>813999</v>
+        <v>814003</v>
       </c>
       <c r="R58" t="n">
-        <v>7355845</v>
+        <v>7355454</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6502,22 +6492,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125403783</v>
+        <v>125392495</v>
       </c>
       <c r="B59" t="n">
-        <v>92293</v>
+        <v>56836</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6530,21 +6520,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6554,13 +6544,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>813951</v>
+        <v>814057</v>
       </c>
       <c r="R59" t="n">
-        <v>7355737</v>
+        <v>7355446</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6604,22 +6594,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125393625</v>
+        <v>125401289</v>
       </c>
       <c r="B60" t="n">
-        <v>77738</v>
+        <v>91131</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6628,25 +6618,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6487</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6656,10 +6646,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>813993</v>
+        <v>813966</v>
       </c>
       <c r="R60" t="n">
-        <v>7355850</v>
+        <v>7355769</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6706,22 +6696,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125392592</v>
+        <v>125393602</v>
       </c>
       <c r="B61" t="n">
-        <v>78547</v>
+        <v>79565</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6734,21 +6724,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6758,13 +6748,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>813924</v>
+        <v>814085</v>
       </c>
       <c r="R61" t="n">
-        <v>7355940</v>
+        <v>7355609</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6808,22 +6798,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125392502</v>
+        <v>125394419</v>
       </c>
       <c r="B62" t="n">
-        <v>91264</v>
+        <v>92448</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6832,25 +6822,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6860,10 +6850,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>813982</v>
+        <v>813962</v>
       </c>
       <c r="R62" t="n">
-        <v>7355407</v>
+        <v>7355721</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6910,22 +6900,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125401289</v>
+        <v>125393619</v>
       </c>
       <c r="B63" t="n">
-        <v>90977</v>
+        <v>78684</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6934,25 +6924,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6962,10 +6952,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>813966</v>
+        <v>814069</v>
       </c>
       <c r="R63" t="n">
-        <v>7355769</v>
+        <v>7355541</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7012,22 +7002,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125401319</v>
+        <v>125401297</v>
       </c>
       <c r="B64" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7064,13 +7054,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>813998</v>
+        <v>813885</v>
       </c>
       <c r="R64" t="n">
-        <v>7355850</v>
+        <v>7355896</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7114,22 +7104,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125393629</v>
+        <v>125401318</v>
       </c>
       <c r="B65" t="n">
-        <v>78194</v>
+        <v>78592</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7142,21 +7132,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7166,13 +7156,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>814063</v>
+        <v>814001</v>
       </c>
       <c r="R65" t="n">
-        <v>7355649</v>
+        <v>7355662</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7216,22 +7206,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125393605</v>
+        <v>125393610</v>
       </c>
       <c r="B66" t="n">
-        <v>79428</v>
+        <v>79536</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7244,21 +7234,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7268,10 +7258,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>813983</v>
+        <v>813948</v>
       </c>
       <c r="R66" t="n">
-        <v>7355808</v>
+        <v>7355861</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7330,10 +7320,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125394419</v>
+        <v>125392498</v>
       </c>
       <c r="B67" t="n">
-        <v>92293</v>
+        <v>78971</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7346,21 +7336,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7370,10 +7360,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>813962</v>
+        <v>814002</v>
       </c>
       <c r="R67" t="n">
-        <v>7355721</v>
+        <v>7355412</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7420,22 +7410,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125393628</v>
+        <v>125392274</v>
       </c>
       <c r="B68" t="n">
-        <v>78194</v>
+        <v>78947</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7448,21 +7438,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7472,13 +7462,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>813979</v>
+        <v>814062</v>
       </c>
       <c r="R68" t="n">
-        <v>7355768</v>
+        <v>7355640</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7522,22 +7512,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125401312</v>
+        <v>125393628</v>
       </c>
       <c r="B69" t="n">
-        <v>79428</v>
+        <v>78331</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7550,21 +7540,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7574,13 +7564,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>813943</v>
+        <v>813979</v>
       </c>
       <c r="R69" t="n">
-        <v>7355850</v>
+        <v>7355768</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7624,22 +7614,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125393614</v>
+        <v>125393615</v>
       </c>
       <c r="B70" t="n">
-        <v>78834</v>
+        <v>78684</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7648,25 +7638,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7676,10 +7666,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>814021</v>
+        <v>814053</v>
       </c>
       <c r="R70" t="n">
-        <v>7355670</v>
+        <v>7355646</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7738,10 +7728,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125392594</v>
+        <v>125401323</v>
       </c>
       <c r="B71" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7778,10 +7768,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>814057</v>
+        <v>813969</v>
       </c>
       <c r="R71" t="n">
-        <v>7355682</v>
+        <v>7355700</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7828,22 +7818,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125392498</v>
+        <v>125401296</v>
       </c>
       <c r="B72" t="n">
-        <v>78834</v>
+        <v>92448</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7856,21 +7846,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7880,10 +7870,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>814002</v>
+        <v>813777</v>
       </c>
       <c r="R72" t="n">
-        <v>7355412</v>
+        <v>7355862</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7918,6 +7908,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Häxring</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -7930,22 +7925,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125393626</v>
+        <v>125393618</v>
       </c>
       <c r="B73" t="n">
-        <v>78194</v>
+        <v>78684</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7958,21 +7953,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7982,10 +7977,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>813874</v>
+        <v>813976</v>
       </c>
       <c r="R73" t="n">
-        <v>7355877</v>
+        <v>7355749</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8044,10 +8039,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125393627</v>
+        <v>125393623</v>
       </c>
       <c r="B74" t="n">
-        <v>78194</v>
+        <v>78592</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8060,21 +8055,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8084,10 +8079,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>813993</v>
+        <v>814062</v>
       </c>
       <c r="R74" t="n">
-        <v>7355850</v>
+        <v>7355547</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8146,10 +8141,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125392274</v>
+        <v>125392505</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>92448</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8158,25 +8153,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8186,13 +8181,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>814062</v>
+        <v>813992</v>
       </c>
       <c r="R75" t="n">
-        <v>7355640</v>
+        <v>7355418</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8236,22 +8231,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125392495</v>
+        <v>125401303</v>
       </c>
       <c r="B76" t="n">
-        <v>56722</v>
+        <v>78331</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8260,25 +8255,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8288,10 +8283,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>814057</v>
+        <v>813955</v>
       </c>
       <c r="R76" t="n">
-        <v>7355446</v>
+        <v>7355863</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8338,22 +8333,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125401310</v>
+        <v>125394420</v>
       </c>
       <c r="B77" t="n">
-        <v>79428</v>
+        <v>92448</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8362,25 +8357,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8390,13 +8385,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>814093</v>
+        <v>813977</v>
       </c>
       <c r="R77" t="n">
-        <v>7355601</v>
+        <v>7355690</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8440,22 +8435,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125392501</v>
+        <v>125401311</v>
       </c>
       <c r="B78" t="n">
-        <v>91624</v>
+        <v>79565</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8468,21 +8463,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5454</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8492,13 +8487,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>814052</v>
+        <v>813899</v>
       </c>
       <c r="R78" t="n">
-        <v>7355484</v>
+        <v>7355971</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8542,22 +8537,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125401303</v>
+        <v>125401322</v>
       </c>
       <c r="B79" t="n">
-        <v>78194</v>
+        <v>92448</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8566,25 +8561,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8594,13 +8589,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>813955</v>
+        <v>813963</v>
       </c>
       <c r="R79" t="n">
-        <v>7355863</v>
+        <v>7355778</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8644,22 +8639,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125401325</v>
+        <v>125401298</v>
       </c>
       <c r="B80" t="n">
-        <v>78194</v>
+        <v>92448</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8668,25 +8663,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8696,13 +8691,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>814093</v>
+        <v>813922</v>
       </c>
       <c r="R80" t="n">
-        <v>7355602</v>
+        <v>7355853</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8746,22 +8741,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125393610</v>
+        <v>125401292</v>
       </c>
       <c r="B81" t="n">
-        <v>79399</v>
+        <v>56836</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8770,25 +8765,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8798,10 +8793,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>813948</v>
+        <v>813980</v>
       </c>
       <c r="R81" t="n">
-        <v>7355861</v>
+        <v>7355837</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8836,6 +8831,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -8848,22 +8848,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125401315</v>
+        <v>125393608</v>
       </c>
       <c r="B82" t="n">
-        <v>78547</v>
+        <v>79565</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8876,21 +8876,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8900,13 +8900,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>813936</v>
+        <v>814054</v>
       </c>
       <c r="R82" t="n">
-        <v>7355848</v>
+        <v>7355641</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8950,22 +8950,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125401324</v>
+        <v>125392503</v>
       </c>
       <c r="B83" t="n">
-        <v>92287</v>
+        <v>92448</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8974,25 +8974,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9002,13 +9002,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>813960</v>
+        <v>814058</v>
       </c>
       <c r="R83" t="n">
-        <v>7355731</v>
+        <v>7355447</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9052,22 +9052,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125401299</v>
+        <v>125392497</v>
       </c>
       <c r="B84" t="n">
-        <v>92293</v>
+        <v>92440</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9076,25 +9076,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>814052</v>
+        <v>814027</v>
       </c>
       <c r="R84" t="n">
-        <v>7355644</v>
+        <v>7355486</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9154,22 +9154,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125433174</v>
+        <v>125417990</v>
       </c>
       <c r="B85" t="n">
-        <v>92293</v>
+        <v>56836</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9182,34 +9182,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Bergträskryggen, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>813928</v>
+        <v>814036</v>
       </c>
       <c r="R85" t="n">
-        <v>7355688</v>
+        <v>7355516</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9244,35 +9252,39 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125417988</v>
+        <v>125433170</v>
       </c>
       <c r="B86" t="n">
-        <v>56722</v>
+        <v>79565</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9281,46 +9293,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bergträskryggen, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>814016</v>
+        <v>813923</v>
       </c>
       <c r="R86" t="n">
-        <v>7355686</v>
+        <v>7355691</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9367,22 +9371,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125433171</v>
+        <v>125433173</v>
       </c>
       <c r="B87" t="n">
-        <v>79399</v>
+        <v>92448</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9391,25 +9395,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9419,10 +9423,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>814007</v>
+        <v>813919</v>
       </c>
       <c r="R87" t="n">
-        <v>7355824</v>
+        <v>7355726</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9463,6 +9467,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9481,10 +9486,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125433172</v>
+        <v>125433174</v>
       </c>
       <c r="B88" t="n">
-        <v>78547</v>
+        <v>92448</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9493,25 +9498,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9521,10 +9526,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>813909</v>
+        <v>813928</v>
       </c>
       <c r="R88" t="n">
-        <v>7355667</v>
+        <v>7355688</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9565,6 +9570,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9583,10 +9589,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125417989</v>
+        <v>125433171</v>
       </c>
       <c r="B89" t="n">
-        <v>56722</v>
+        <v>79536</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9595,46 +9601,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Bergträskryggen, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>814054</v>
+        <v>814007</v>
       </c>
       <c r="R89" t="n">
-        <v>7355732</v>
+        <v>7355824</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9681,12 +9679,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9696,7 +9694,7 @@
         <v>125417991</v>
       </c>
       <c r="B90" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9795,10 +9793,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125433170</v>
+        <v>125433172</v>
       </c>
       <c r="B91" t="n">
-        <v>79428</v>
+        <v>78684</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9811,21 +9809,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9835,10 +9833,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>813923</v>
+        <v>813909</v>
       </c>
       <c r="R91" t="n">
-        <v>7355691</v>
+        <v>7355667</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9897,10 +9895,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125417990</v>
+        <v>125417989</v>
       </c>
       <c r="B92" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9945,10 +9943,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>814036</v>
+        <v>814054</v>
       </c>
       <c r="R92" t="n">
-        <v>7355516</v>
+        <v>7355732</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9981,11 +9979,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10012,10 +10005,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125433173</v>
+        <v>125417988</v>
       </c>
       <c r="B93" t="n">
-        <v>92293</v>
+        <v>56836</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10028,34 +10021,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Bergträskryggen, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>813919</v>
+        <v>814016</v>
       </c>
       <c r="R93" t="n">
-        <v>7355726</v>
+        <v>7355686</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10096,19 +10097,18 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10118,7 +10118,7 @@
         <v>125395032</v>
       </c>
       <c r="B94" t="n">
-        <v>90934</v>
+        <v>91088</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>125395033</v>
       </c>
       <c r="B95" t="n">
-        <v>91264</v>
+        <v>91424</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125401301</v>
+        <v>125394417</v>
       </c>
       <c r="B2" t="n">
-        <v>92442</v>
+        <v>92448</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>814046</v>
+        <v>813952</v>
       </c>
       <c r="R2" t="n">
-        <v>7355641</v>
+        <v>7355835</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125401325</v>
+        <v>125401301</v>
       </c>
       <c r="B3" t="n">
-        <v>78331</v>
+        <v>92442</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>814093</v>
+        <v>814046</v>
       </c>
       <c r="R3" t="n">
-        <v>7355602</v>
+        <v>7355641</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125394417</v>
+        <v>125401325</v>
       </c>
       <c r="B5" t="n">
-        <v>92448</v>
+        <v>78331</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>813952</v>
+        <v>814093</v>
       </c>
       <c r="R5" t="n">
-        <v>7355835</v>
+        <v>7355602</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125394416</v>
+        <v>125392502</v>
       </c>
       <c r="B31" t="n">
-        <v>56836</v>
+        <v>91424</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3650,25 +3650,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>65</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>814013</v>
+        <v>813982</v>
       </c>
       <c r="R31" t="n">
-        <v>7355681</v>
+        <v>7355407</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3716,11 +3716,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3733,22 +3728,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125393625</v>
+        <v>125394416</v>
       </c>
       <c r="B32" t="n">
-        <v>77874</v>
+        <v>56836</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3757,25 +3752,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3780,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>813993</v>
+        <v>814013</v>
       </c>
       <c r="R32" t="n">
-        <v>7355850</v>
+        <v>7355681</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3823,6 +3818,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3835,22 +3835,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125393603</v>
+        <v>125393625</v>
       </c>
       <c r="B33" t="n">
-        <v>79565</v>
+        <v>77874</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>813848</v>
+        <v>813993</v>
       </c>
       <c r="R33" t="n">
-        <v>7355853</v>
+        <v>7355850</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125392502</v>
+        <v>125393603</v>
       </c>
       <c r="B34" t="n">
-        <v>91424</v>
+        <v>79565</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3961,25 +3961,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>813982</v>
+        <v>813848</v>
       </c>
       <c r="R34" t="n">
-        <v>7355407</v>
+        <v>7355853</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4039,12 +4039,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125401288</v>
+        <v>125392595</v>
       </c>
       <c r="B40" t="n">
-        <v>91088</v>
+        <v>92448</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4578,25 +4578,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4606,13 +4606,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>813970</v>
+        <v>813850</v>
       </c>
       <c r="R40" t="n">
-        <v>7355705</v>
+        <v>7355937</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4656,22 +4656,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125392595</v>
+        <v>125401288</v>
       </c>
       <c r="B41" t="n">
-        <v>92448</v>
+        <v>91088</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4680,25 +4680,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4708,13 +4708,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>813850</v>
+        <v>813970</v>
       </c>
       <c r="R41" t="n">
-        <v>7355937</v>
+        <v>7355705</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4758,12 +4758,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125393629</v>
+        <v>125392496</v>
       </c>
       <c r="B52" t="n">
-        <v>78331</v>
+        <v>56836</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5802,25 +5802,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>814063</v>
+        <v>814003</v>
       </c>
       <c r="R52" t="n">
-        <v>7355649</v>
+        <v>7355454</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5880,22 +5880,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125393621</v>
+        <v>125392495</v>
       </c>
       <c r="B53" t="n">
-        <v>78683</v>
+        <v>56836</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5904,25 +5904,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>813934</v>
+        <v>814057</v>
       </c>
       <c r="R53" t="n">
-        <v>7355844</v>
+        <v>7355446</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5982,22 +5982,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125393622</v>
+        <v>125393629</v>
       </c>
       <c r="B54" t="n">
-        <v>78683</v>
+        <v>78331</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6010,21 +6010,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6034,10 +6034,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>814058</v>
+        <v>814063</v>
       </c>
       <c r="R54" t="n">
-        <v>7355641</v>
+        <v>7355649</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6096,10 +6096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125393607</v>
+        <v>125393621</v>
       </c>
       <c r="B55" t="n">
-        <v>79565</v>
+        <v>78683</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6112,21 +6112,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>813971</v>
+        <v>813934</v>
       </c>
       <c r="R55" t="n">
-        <v>7355703</v>
+        <v>7355844</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6198,10 +6198,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125392271</v>
+        <v>125393622</v>
       </c>
       <c r="B56" t="n">
-        <v>78684</v>
+        <v>78683</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6214,21 +6214,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6238,13 +6238,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>813991</v>
+        <v>814058</v>
       </c>
       <c r="R56" t="n">
-        <v>7355833</v>
+        <v>7355641</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6288,22 +6288,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125401317</v>
+        <v>125393607</v>
       </c>
       <c r="B57" t="n">
-        <v>78592</v>
+        <v>79565</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6316,21 +6316,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>813998</v>
+        <v>813971</v>
       </c>
       <c r="R57" t="n">
-        <v>7355852</v>
+        <v>7355703</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6390,22 +6390,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125392496</v>
+        <v>125392271</v>
       </c>
       <c r="B58" t="n">
-        <v>56836</v>
+        <v>78684</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6414,25 +6414,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6442,13 +6442,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>814003</v>
+        <v>813991</v>
       </c>
       <c r="R58" t="n">
-        <v>7355454</v>
+        <v>7355833</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6492,22 +6492,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125392495</v>
+        <v>125401289</v>
       </c>
       <c r="B59" t="n">
-        <v>56836</v>
+        <v>91131</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6520,21 +6520,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>814057</v>
+        <v>813966</v>
       </c>
       <c r="R59" t="n">
-        <v>7355446</v>
+        <v>7355769</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6594,22 +6594,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125401289</v>
+        <v>125401317</v>
       </c>
       <c r="B60" t="n">
-        <v>91131</v>
+        <v>78592</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6618,25 +6618,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6646,13 +6646,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>813966</v>
+        <v>813998</v>
       </c>
       <c r="R60" t="n">
-        <v>7355769</v>
+        <v>7355852</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6696,12 +6696,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125394419</v>
+        <v>125401318</v>
       </c>
       <c r="B62" t="n">
-        <v>92448</v>
+        <v>78592</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6822,25 +6822,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6850,13 +6850,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>813962</v>
+        <v>814001</v>
       </c>
       <c r="R62" t="n">
-        <v>7355721</v>
+        <v>7355662</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6900,22 +6900,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125393619</v>
+        <v>125394419</v>
       </c>
       <c r="B63" t="n">
-        <v>78684</v>
+        <v>92448</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6924,25 +6924,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>814069</v>
+        <v>813962</v>
       </c>
       <c r="R63" t="n">
-        <v>7355541</v>
+        <v>7355721</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7002,22 +7002,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125401297</v>
+        <v>125393619</v>
       </c>
       <c r="B64" t="n">
-        <v>92448</v>
+        <v>78684</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7026,25 +7026,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7054,10 +7054,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>813885</v>
+        <v>814069</v>
       </c>
       <c r="R64" t="n">
-        <v>7355896</v>
+        <v>7355541</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7104,22 +7104,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125401318</v>
+        <v>125401297</v>
       </c>
       <c r="B65" t="n">
-        <v>78592</v>
+        <v>92448</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7128,25 +7128,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7156,13 +7156,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>814001</v>
+        <v>813885</v>
       </c>
       <c r="R65" t="n">
-        <v>7355662</v>
+        <v>7355896</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7206,12 +7206,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8345,10 +8345,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125394420</v>
+        <v>125401311</v>
       </c>
       <c r="B77" t="n">
-        <v>92448</v>
+        <v>79565</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8357,25 +8357,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8385,13 +8385,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>813977</v>
+        <v>813899</v>
       </c>
       <c r="R77" t="n">
-        <v>7355690</v>
+        <v>7355971</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8435,22 +8435,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125401311</v>
+        <v>125394420</v>
       </c>
       <c r="B78" t="n">
-        <v>79565</v>
+        <v>92448</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8459,25 +8459,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8487,13 +8487,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>813899</v>
+        <v>813977</v>
       </c>
       <c r="R78" t="n">
-        <v>7355971</v>
+        <v>7355690</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8537,22 +8537,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125401322</v>
+        <v>125393608</v>
       </c>
       <c r="B79" t="n">
-        <v>92448</v>
+        <v>79565</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8561,25 +8561,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8589,13 +8589,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>813963</v>
+        <v>814054</v>
       </c>
       <c r="R79" t="n">
-        <v>7355778</v>
+        <v>7355641</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8639,19 +8639,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125401298</v>
+        <v>125401322</v>
       </c>
       <c r="B80" t="n">
         <v>92448</v>
@@ -8691,13 +8691,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>813922</v>
+        <v>813963</v>
       </c>
       <c r="R80" t="n">
-        <v>7355853</v>
+        <v>7355778</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8741,22 +8741,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125401292</v>
+        <v>125401298</v>
       </c>
       <c r="B81" t="n">
-        <v>56836</v>
+        <v>92448</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8769,21 +8769,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8793,10 +8793,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>813980</v>
+        <v>813922</v>
       </c>
       <c r="R81" t="n">
-        <v>7355837</v>
+        <v>7355853</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8829,11 +8829,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8860,10 +8855,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125393608</v>
+        <v>125401292</v>
       </c>
       <c r="B82" t="n">
-        <v>79565</v>
+        <v>56836</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8872,25 +8867,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8900,10 +8895,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>814054</v>
+        <v>813980</v>
       </c>
       <c r="R82" t="n">
-        <v>7355641</v>
+        <v>7355837</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8938,6 +8933,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -8950,12 +8950,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9589,10 +9589,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125433171</v>
+        <v>125417991</v>
       </c>
       <c r="B89" t="n">
-        <v>79536</v>
+        <v>92448</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9601,25 +9601,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9629,10 +9629,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>814007</v>
+        <v>813973</v>
       </c>
       <c r="R89" t="n">
-        <v>7355824</v>
+        <v>7355786</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9679,22 +9679,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125417991</v>
+        <v>125433171</v>
       </c>
       <c r="B90" t="n">
-        <v>92448</v>
+        <v>79536</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9703,25 +9703,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9731,10 +9731,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>813973</v>
+        <v>814007</v>
       </c>
       <c r="R90" t="n">
-        <v>7355786</v>
+        <v>7355824</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9781,12 +9781,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125394417</v>
+        <v>125394419</v>
       </c>
       <c r="B2" t="n">
         <v>92448</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>813952</v>
+        <v>813962</v>
       </c>
       <c r="R2" t="n">
-        <v>7355835</v>
+        <v>7355721</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125401301</v>
+        <v>125392508</v>
       </c>
       <c r="B3" t="n">
-        <v>92442</v>
+        <v>77874</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>6487</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>814046</v>
+        <v>814001</v>
       </c>
       <c r="R3" t="n">
-        <v>7355641</v>
+        <v>7355442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125392591</v>
+        <v>125393611</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
+        <v>79536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>813924</v>
+        <v>814063</v>
       </c>
       <c r="R4" t="n">
-        <v>7355940</v>
+        <v>7355649</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125401325</v>
+        <v>125392271</v>
       </c>
       <c r="B5" t="n">
-        <v>78331</v>
+        <v>78684</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>814093</v>
+        <v>813991</v>
       </c>
       <c r="R5" t="n">
-        <v>7355602</v>
+        <v>7355833</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125393627</v>
+        <v>125394416</v>
       </c>
       <c r="B6" t="n">
-        <v>78331</v>
+        <v>56836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>813993</v>
+        <v>814013</v>
       </c>
       <c r="R6" t="n">
-        <v>7355850</v>
+        <v>7355681</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,6 +1161,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1173,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125393624</v>
+        <v>125392494</v>
       </c>
       <c r="B7" t="n">
-        <v>92448</v>
+        <v>90204</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>813879</v>
+        <v>814004</v>
       </c>
       <c r="R7" t="n">
-        <v>7355876</v>
+        <v>7355434</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,22 +1280,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125392494</v>
+        <v>125401289</v>
       </c>
       <c r="B8" t="n">
-        <v>90204</v>
+        <v>91131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>814004</v>
+        <v>813966</v>
       </c>
       <c r="R8" t="n">
-        <v>7355434</v>
+        <v>7355769</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,19 +1382,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125403785</v>
+        <v>125393624</v>
       </c>
       <c r="B9" t="n">
         <v>92448</v>
@@ -1429,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>814010</v>
+        <v>813879</v>
       </c>
       <c r="R9" t="n">
-        <v>7355734</v>
+        <v>7355876</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,22 +1484,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125393616</v>
+        <v>125392501</v>
       </c>
       <c r="B10" t="n">
-        <v>78684</v>
+        <v>91784</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>5454</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>813859</v>
+        <v>814052</v>
       </c>
       <c r="R10" t="n">
-        <v>7355858</v>
+        <v>7355484</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,22 +1586,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125392501</v>
+        <v>125393606</v>
       </c>
       <c r="B11" t="n">
-        <v>91784</v>
+        <v>79565</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5454</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>814052</v>
+        <v>813976</v>
       </c>
       <c r="R11" t="n">
-        <v>7355484</v>
+        <v>7355749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,22 +1688,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125392594</v>
+        <v>125392498</v>
       </c>
       <c r="B12" t="n">
-        <v>92448</v>
+        <v>78971</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>814057</v>
+        <v>814002</v>
       </c>
       <c r="R12" t="n">
-        <v>7355682</v>
+        <v>7355412</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,22 +1790,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125401313</v>
+        <v>125392590</v>
       </c>
       <c r="B13" t="n">
-        <v>56836</v>
+        <v>91131</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>813998</v>
+        <v>813970</v>
       </c>
       <c r="R13" t="n">
-        <v>7355672</v>
+        <v>7355771</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1875,11 +1880,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1892,22 +1892,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125392268</v>
+        <v>125393608</v>
       </c>
       <c r="B14" t="n">
-        <v>92646</v>
+        <v>79565</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>814049</v>
+        <v>814054</v>
       </c>
       <c r="R14" t="n">
-        <v>7355786</v>
+        <v>7355641</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1994,19 +1994,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125392504</v>
+        <v>125392275</v>
       </c>
       <c r="B15" t="n">
         <v>92448</v>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>813963</v>
+        <v>814068</v>
       </c>
       <c r="R15" t="n">
-        <v>7355408</v>
+        <v>7355802</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2096,22 +2096,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125393614</v>
+        <v>125401324</v>
       </c>
       <c r="B16" t="n">
-        <v>78971</v>
+        <v>92442</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>814021</v>
+        <v>813960</v>
       </c>
       <c r="R16" t="n">
-        <v>7355670</v>
+        <v>7355731</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2198,22 +2198,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125393609</v>
+        <v>125401298</v>
       </c>
       <c r="B17" t="n">
-        <v>79565</v>
+        <v>92448</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>814066</v>
+        <v>813922</v>
       </c>
       <c r="R17" t="n">
-        <v>7355537</v>
+        <v>7355853</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,22 +2300,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125392507</v>
+        <v>125401315</v>
       </c>
       <c r="B18" t="n">
-        <v>92448</v>
+        <v>78684</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>814049</v>
+        <v>813936</v>
       </c>
       <c r="R18" t="n">
-        <v>7355489</v>
+        <v>7355848</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2402,19 +2402,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125392275</v>
+        <v>125392596</v>
       </c>
       <c r="B19" t="n">
         <v>92448</v>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>814068</v>
+        <v>813911</v>
       </c>
       <c r="R19" t="n">
-        <v>7355802</v>
+        <v>7355874</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2504,22 +2504,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125403783</v>
+        <v>125392592</v>
       </c>
       <c r="B20" t="n">
-        <v>92448</v>
+        <v>78684</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>813951</v>
+        <v>813924</v>
       </c>
       <c r="R20" t="n">
-        <v>7355737</v>
+        <v>7355940</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2606,22 +2606,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125401321</v>
+        <v>125393614</v>
       </c>
       <c r="B21" t="n">
-        <v>92448</v>
+        <v>78971</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>813851</v>
+        <v>814021</v>
       </c>
       <c r="R21" t="n">
-        <v>7355951</v>
+        <v>7355670</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2708,22 +2708,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125403784</v>
+        <v>125393603</v>
       </c>
       <c r="B22" t="n">
-        <v>92448</v>
+        <v>79565</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,13 +2760,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>813985</v>
+        <v>813848</v>
       </c>
       <c r="R22" t="n">
-        <v>7355756</v>
+        <v>7355853</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2810,22 +2810,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125392272</v>
+        <v>125393619</v>
       </c>
       <c r="B23" t="n">
-        <v>91326</v>
+        <v>78684</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>814011</v>
+        <v>814069</v>
       </c>
       <c r="R23" t="n">
-        <v>7355730</v>
+        <v>7355541</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2912,22 +2912,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125392267</v>
+        <v>125392591</v>
       </c>
       <c r="B24" t="n">
-        <v>90204</v>
+        <v>79565</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>814049</v>
+        <v>813924</v>
       </c>
       <c r="R24" t="n">
-        <v>7355602</v>
+        <v>7355940</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3014,22 +3014,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125401299</v>
+        <v>125393602</v>
       </c>
       <c r="B25" t="n">
-        <v>92448</v>
+        <v>79565</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>814052</v>
+        <v>814085</v>
       </c>
       <c r="R25" t="n">
-        <v>7355644</v>
+        <v>7355609</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3116,22 +3116,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125393605</v>
+        <v>125393628</v>
       </c>
       <c r="B26" t="n">
-        <v>79565</v>
+        <v>78331</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>813983</v>
+        <v>813979</v>
       </c>
       <c r="R26" t="n">
-        <v>7355808</v>
+        <v>7355768</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125393626</v>
+        <v>125393622</v>
       </c>
       <c r="B27" t="n">
-        <v>78331</v>
+        <v>78683</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,21 +3246,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>813874</v>
+        <v>814058</v>
       </c>
       <c r="R27" t="n">
-        <v>7355877</v>
+        <v>7355641</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125393613</v>
+        <v>125401303</v>
       </c>
       <c r="B28" t="n">
-        <v>78971</v>
+        <v>78331</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,25 +3344,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6434</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>813953</v>
+        <v>813955</v>
       </c>
       <c r="R28" t="n">
-        <v>7355711</v>
+        <v>7355863</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3422,22 +3422,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125392590</v>
+        <v>125401319</v>
       </c>
       <c r="B29" t="n">
-        <v>91131</v>
+        <v>92448</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>813970</v>
+        <v>813998</v>
       </c>
       <c r="R29" t="n">
-        <v>7355771</v>
+        <v>7355850</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3524,22 +3524,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125401312</v>
+        <v>125392267</v>
       </c>
       <c r="B30" t="n">
-        <v>79565</v>
+        <v>90204</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,21 +3552,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>813943</v>
+        <v>814049</v>
       </c>
       <c r="R30" t="n">
-        <v>7355850</v>
+        <v>7355602</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3626,22 +3626,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125392502</v>
+        <v>125392594</v>
       </c>
       <c r="B31" t="n">
-        <v>91424</v>
+        <v>92448</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3650,25 +3650,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3678,13 +3678,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>813982</v>
+        <v>814057</v>
       </c>
       <c r="R31" t="n">
-        <v>7355407</v>
+        <v>7355682</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3728,22 +3728,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125394416</v>
+        <v>125403783</v>
       </c>
       <c r="B32" t="n">
-        <v>56836</v>
+        <v>92448</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,13 +3780,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>814013</v>
+        <v>813951</v>
       </c>
       <c r="R32" t="n">
-        <v>7355681</v>
+        <v>7355737</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3816,11 +3816,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3835,22 +3830,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125393625</v>
+        <v>125401301</v>
       </c>
       <c r="B33" t="n">
-        <v>77874</v>
+        <v>92442</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3858,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3882,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>813993</v>
+        <v>814046</v>
       </c>
       <c r="R33" t="n">
-        <v>7355850</v>
+        <v>7355641</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3937,22 +3932,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125393603</v>
+        <v>125401317</v>
       </c>
       <c r="B34" t="n">
-        <v>79565</v>
+        <v>78592</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3965,21 +3960,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3989,13 +3984,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>813848</v>
+        <v>813998</v>
       </c>
       <c r="R34" t="n">
-        <v>7355853</v>
+        <v>7355852</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4039,22 +4034,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125401314</v>
+        <v>125401318</v>
       </c>
       <c r="B35" t="n">
-        <v>78684</v>
+        <v>78592</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4067,21 +4062,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4091,10 +4086,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>813899</v>
+        <v>814001</v>
       </c>
       <c r="R35" t="n">
-        <v>7355975</v>
+        <v>7355662</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4153,10 +4148,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125393606</v>
+        <v>125393629</v>
       </c>
       <c r="B36" t="n">
-        <v>79565</v>
+        <v>78331</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4169,21 +4164,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4193,10 +4188,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>813976</v>
+        <v>814063</v>
       </c>
       <c r="R36" t="n">
-        <v>7355749</v>
+        <v>7355649</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4255,10 +4250,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125392597</v>
+        <v>125393626</v>
       </c>
       <c r="B37" t="n">
-        <v>92448</v>
+        <v>78331</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4267,25 +4262,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4295,13 +4290,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>814123</v>
+        <v>813874</v>
       </c>
       <c r="R37" t="n">
-        <v>7355495</v>
+        <v>7355877</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4345,22 +4340,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125393617</v>
+        <v>125403784</v>
       </c>
       <c r="B38" t="n">
-        <v>78684</v>
+        <v>92448</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4369,25 +4364,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4397,13 +4392,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>813999</v>
+        <v>813985</v>
       </c>
       <c r="R38" t="n">
-        <v>7355845</v>
+        <v>7355756</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4447,22 +4442,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125392499</v>
+        <v>125401292</v>
       </c>
       <c r="B39" t="n">
-        <v>92646</v>
+        <v>56836</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4471,25 +4466,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4499,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>814055</v>
+        <v>813980</v>
       </c>
       <c r="R39" t="n">
-        <v>7355488</v>
+        <v>7355837</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4539,7 +4534,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Kollekt</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4554,22 +4549,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125392595</v>
+        <v>125393615</v>
       </c>
       <c r="B40" t="n">
-        <v>92448</v>
+        <v>78684</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4578,25 +4573,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4606,13 +4601,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>813850</v>
+        <v>814053</v>
       </c>
       <c r="R40" t="n">
-        <v>7355937</v>
+        <v>7355646</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4656,22 +4651,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125401288</v>
+        <v>125401297</v>
       </c>
       <c r="B41" t="n">
-        <v>91088</v>
+        <v>92448</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4680,25 +4675,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4708,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>813970</v>
+        <v>813885</v>
       </c>
       <c r="R41" t="n">
-        <v>7355705</v>
+        <v>7355896</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,10 +4765,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125393620</v>
+        <v>125401325</v>
       </c>
       <c r="B42" t="n">
-        <v>80900</v>
+        <v>78331</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4786,21 +4781,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1049</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4810,13 +4805,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>813875</v>
+        <v>814093</v>
       </c>
       <c r="R42" t="n">
-        <v>7355877</v>
+        <v>7355602</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4860,12 +4855,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4974,10 +4969,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125392508</v>
+        <v>125393621</v>
       </c>
       <c r="B44" t="n">
-        <v>77874</v>
+        <v>78683</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4990,21 +4985,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5014,10 +5009,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>814001</v>
+        <v>813934</v>
       </c>
       <c r="R44" t="n">
-        <v>7355442</v>
+        <v>7355844</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5064,19 +5059,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125392596</v>
+        <v>125392503</v>
       </c>
       <c r="B45" t="n">
         <v>92448</v>
@@ -5116,13 +5111,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>813911</v>
+        <v>814058</v>
       </c>
       <c r="R45" t="n">
-        <v>7355874</v>
+        <v>7355447</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5166,22 +5161,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125393611</v>
+        <v>125392507</v>
       </c>
       <c r="B46" t="n">
-        <v>79536</v>
+        <v>92448</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5190,25 +5185,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5218,10 +5213,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>814063</v>
+        <v>814049</v>
       </c>
       <c r="R46" t="n">
-        <v>7355649</v>
+        <v>7355489</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5268,22 +5263,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125392592</v>
+        <v>125393607</v>
       </c>
       <c r="B47" t="n">
-        <v>78684</v>
+        <v>79565</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5296,21 +5291,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5320,13 +5315,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>813924</v>
+        <v>813971</v>
       </c>
       <c r="R47" t="n">
-        <v>7355940</v>
+        <v>7355703</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5370,22 +5365,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125401310</v>
+        <v>125392502</v>
       </c>
       <c r="B48" t="n">
-        <v>79565</v>
+        <v>91424</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5394,25 +5389,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5422,13 +5417,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>814093</v>
+        <v>813982</v>
       </c>
       <c r="R48" t="n">
-        <v>7355601</v>
+        <v>7355407</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5472,22 +5467,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125401324</v>
+        <v>125393616</v>
       </c>
       <c r="B49" t="n">
-        <v>92442</v>
+        <v>78684</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5500,21 +5495,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5524,13 +5519,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>813960</v>
+        <v>813859</v>
       </c>
       <c r="R49" t="n">
-        <v>7355731</v>
+        <v>7355858</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5574,19 +5569,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125401319</v>
+        <v>125401296</v>
       </c>
       <c r="B50" t="n">
         <v>92448</v>
@@ -5626,13 +5621,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>813998</v>
+        <v>813777</v>
       </c>
       <c r="R50" t="n">
-        <v>7355850</v>
+        <v>7355862</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5662,6 +5657,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Häxring</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5676,22 +5676,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125401315</v>
+        <v>125392505</v>
       </c>
       <c r="B51" t="n">
-        <v>78684</v>
+        <v>92448</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5700,25 +5700,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5728,13 +5728,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>813936</v>
+        <v>813992</v>
       </c>
       <c r="R51" t="n">
-        <v>7355848</v>
+        <v>7355418</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5778,22 +5778,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125392496</v>
+        <v>125393605</v>
       </c>
       <c r="B52" t="n">
-        <v>56836</v>
+        <v>79565</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5802,25 +5802,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>814003</v>
+        <v>813983</v>
       </c>
       <c r="R52" t="n">
-        <v>7355454</v>
+        <v>7355808</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5880,22 +5880,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125392495</v>
+        <v>125401288</v>
       </c>
       <c r="B53" t="n">
-        <v>56836</v>
+        <v>91088</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5904,25 +5904,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>3242</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>814057</v>
+        <v>813970</v>
       </c>
       <c r="R53" t="n">
-        <v>7355446</v>
+        <v>7355705</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5982,22 +5982,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125393629</v>
+        <v>125401311</v>
       </c>
       <c r="B54" t="n">
-        <v>78331</v>
+        <v>79565</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6010,21 +6010,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6034,13 +6034,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>814063</v>
+        <v>813899</v>
       </c>
       <c r="R54" t="n">
-        <v>7355649</v>
+        <v>7355971</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6084,22 +6084,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125393621</v>
+        <v>125393620</v>
       </c>
       <c r="B55" t="n">
-        <v>78683</v>
+        <v>80900</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6112,21 +6112,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>813934</v>
+        <v>813875</v>
       </c>
       <c r="R55" t="n">
-        <v>7355844</v>
+        <v>7355877</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6198,10 +6198,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125393622</v>
+        <v>125393623</v>
       </c>
       <c r="B56" t="n">
-        <v>78683</v>
+        <v>78592</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6214,21 +6214,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>814058</v>
+        <v>814062</v>
       </c>
       <c r="R56" t="n">
-        <v>7355641</v>
+        <v>7355547</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6300,10 +6300,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125393607</v>
+        <v>125392495</v>
       </c>
       <c r="B57" t="n">
-        <v>79565</v>
+        <v>56836</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6312,25 +6312,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>813971</v>
+        <v>814057</v>
       </c>
       <c r="R57" t="n">
-        <v>7355703</v>
+        <v>7355446</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6390,22 +6390,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125392271</v>
+        <v>125392496</v>
       </c>
       <c r="B58" t="n">
-        <v>78684</v>
+        <v>56836</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6414,25 +6414,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6442,13 +6442,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>813991</v>
+        <v>814003</v>
       </c>
       <c r="R58" t="n">
-        <v>7355833</v>
+        <v>7355454</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6492,22 +6492,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125401289</v>
+        <v>125392595</v>
       </c>
       <c r="B59" t="n">
-        <v>91131</v>
+        <v>92448</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6520,21 +6520,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6544,13 +6544,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>813966</v>
+        <v>813850</v>
       </c>
       <c r="R59" t="n">
-        <v>7355769</v>
+        <v>7355937</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6594,22 +6594,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125401317</v>
+        <v>125394417</v>
       </c>
       <c r="B60" t="n">
-        <v>78592</v>
+        <v>92448</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6618,25 +6618,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6646,13 +6646,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>813998</v>
+        <v>813952</v>
       </c>
       <c r="R60" t="n">
-        <v>7355852</v>
+        <v>7355835</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6696,22 +6696,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125393602</v>
+        <v>125393610</v>
       </c>
       <c r="B61" t="n">
-        <v>79565</v>
+        <v>79536</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6724,21 +6724,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>814085</v>
+        <v>813948</v>
       </c>
       <c r="R61" t="n">
-        <v>7355609</v>
+        <v>7355861</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6810,10 +6810,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125401318</v>
+        <v>125401299</v>
       </c>
       <c r="B62" t="n">
-        <v>78592</v>
+        <v>92448</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6822,25 +6822,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6850,13 +6850,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>814001</v>
+        <v>814052</v>
       </c>
       <c r="R62" t="n">
-        <v>7355662</v>
+        <v>7355644</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6900,22 +6900,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125394419</v>
+        <v>125392272</v>
       </c>
       <c r="B63" t="n">
-        <v>92448</v>
+        <v>91326</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6924,25 +6924,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,13 +6952,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>813962</v>
+        <v>814011</v>
       </c>
       <c r="R63" t="n">
-        <v>7355721</v>
+        <v>7355730</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7002,22 +7002,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125393619</v>
+        <v>125392504</v>
       </c>
       <c r="B64" t="n">
-        <v>78684</v>
+        <v>92448</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7026,25 +7026,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7054,10 +7054,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>814069</v>
+        <v>813963</v>
       </c>
       <c r="R64" t="n">
-        <v>7355541</v>
+        <v>7355408</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7104,19 +7104,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125401297</v>
+        <v>125401323</v>
       </c>
       <c r="B65" t="n">
         <v>92448</v>
@@ -7156,13 +7156,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>813885</v>
+        <v>813969</v>
       </c>
       <c r="R65" t="n">
-        <v>7355896</v>
+        <v>7355700</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7206,22 +7206,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125393610</v>
+        <v>125393618</v>
       </c>
       <c r="B66" t="n">
-        <v>79536</v>
+        <v>78684</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7234,21 +7234,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7258,10 +7258,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>813948</v>
+        <v>813976</v>
       </c>
       <c r="R66" t="n">
-        <v>7355861</v>
+        <v>7355749</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7320,10 +7320,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125392498</v>
+        <v>125392499</v>
       </c>
       <c r="B67" t="n">
-        <v>78971</v>
+        <v>92646</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7332,25 +7332,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6434</v>
+        <v>2079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7360,10 +7360,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>814002</v>
+        <v>814055</v>
       </c>
       <c r="R67" t="n">
-        <v>7355412</v>
+        <v>7355488</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7396,6 +7396,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7422,10 +7427,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125392274</v>
+        <v>125394420</v>
       </c>
       <c r="B68" t="n">
-        <v>78947</v>
+        <v>92448</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7434,25 +7439,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7462,13 +7467,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>814062</v>
+        <v>813977</v>
       </c>
       <c r="R68" t="n">
-        <v>7355640</v>
+        <v>7355690</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7512,22 +7517,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125393628</v>
+        <v>125392497</v>
       </c>
       <c r="B69" t="n">
-        <v>78331</v>
+        <v>92440</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7540,21 +7545,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6437</v>
+        <v>4361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7564,10 +7569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>813979</v>
+        <v>814027</v>
       </c>
       <c r="R69" t="n">
-        <v>7355768</v>
+        <v>7355486</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7614,22 +7619,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125393615</v>
+        <v>125403785</v>
       </c>
       <c r="B70" t="n">
-        <v>78684</v>
+        <v>92448</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7638,25 +7643,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7666,13 +7671,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>814053</v>
+        <v>814010</v>
       </c>
       <c r="R70" t="n">
-        <v>7355646</v>
+        <v>7355734</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7716,19 +7721,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125401323</v>
+        <v>125401321</v>
       </c>
       <c r="B71" t="n">
         <v>92448</v>
@@ -7768,10 +7773,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>813969</v>
+        <v>813851</v>
       </c>
       <c r="R71" t="n">
-        <v>7355700</v>
+        <v>7355951</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7830,10 +7835,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125401296</v>
+        <v>125393625</v>
       </c>
       <c r="B72" t="n">
-        <v>92448</v>
+        <v>77874</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7842,25 +7847,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7870,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>813777</v>
+        <v>813993</v>
       </c>
       <c r="R72" t="n">
-        <v>7355862</v>
+        <v>7355850</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7908,11 +7913,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Häxring</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -7925,22 +7925,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125393618</v>
+        <v>125393613</v>
       </c>
       <c r="B73" t="n">
-        <v>78684</v>
+        <v>78971</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7949,25 +7949,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7977,10 +7977,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>813976</v>
+        <v>813953</v>
       </c>
       <c r="R73" t="n">
-        <v>7355749</v>
+        <v>7355711</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8039,10 +8039,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125393623</v>
+        <v>125393627</v>
       </c>
       <c r="B74" t="n">
-        <v>78592</v>
+        <v>78331</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8055,21 +8055,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>814062</v>
+        <v>813993</v>
       </c>
       <c r="R74" t="n">
-        <v>7355547</v>
+        <v>7355850</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8141,10 +8141,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125392505</v>
+        <v>125392274</v>
       </c>
       <c r="B75" t="n">
-        <v>92448</v>
+        <v>78947</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8153,25 +8153,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8181,13 +8181,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>813992</v>
+        <v>814062</v>
       </c>
       <c r="R75" t="n">
-        <v>7355418</v>
+        <v>7355640</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8231,22 +8231,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125401303</v>
+        <v>125401322</v>
       </c>
       <c r="B76" t="n">
-        <v>78331</v>
+        <v>92448</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8255,25 +8255,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8283,13 +8283,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>813955</v>
+        <v>813963</v>
       </c>
       <c r="R76" t="n">
-        <v>7355863</v>
+        <v>7355778</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8333,22 +8333,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125401311</v>
+        <v>125392268</v>
       </c>
       <c r="B77" t="n">
-        <v>79565</v>
+        <v>92646</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8361,21 +8361,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8385,10 +8385,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>813899</v>
+        <v>814049</v>
       </c>
       <c r="R77" t="n">
-        <v>7355971</v>
+        <v>7355786</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8435,22 +8435,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125394420</v>
+        <v>125393617</v>
       </c>
       <c r="B78" t="n">
-        <v>92448</v>
+        <v>78684</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8459,25 +8459,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>813977</v>
+        <v>813999</v>
       </c>
       <c r="R78" t="n">
-        <v>7355690</v>
+        <v>7355845</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8537,19 +8537,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125393608</v>
+        <v>125401310</v>
       </c>
       <c r="B79" t="n">
         <v>79565</v>
@@ -8589,13 +8589,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>814054</v>
+        <v>814093</v>
       </c>
       <c r="R79" t="n">
-        <v>7355641</v>
+        <v>7355601</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8639,22 +8639,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125401322</v>
+        <v>125401314</v>
       </c>
       <c r="B80" t="n">
-        <v>92448</v>
+        <v>78684</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8663,25 +8663,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8691,10 +8691,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>813963</v>
+        <v>813899</v>
       </c>
       <c r="R80" t="n">
-        <v>7355778</v>
+        <v>7355975</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8753,10 +8753,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125401298</v>
+        <v>125401313</v>
       </c>
       <c r="B81" t="n">
-        <v>92448</v>
+        <v>56836</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8769,21 +8769,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8793,13 +8793,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>813922</v>
+        <v>813998</v>
       </c>
       <c r="R81" t="n">
-        <v>7355853</v>
+        <v>7355672</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8829,6 +8829,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8843,22 +8848,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125401292</v>
+        <v>125393609</v>
       </c>
       <c r="B82" t="n">
-        <v>56836</v>
+        <v>79565</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8867,25 +8872,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8895,10 +8900,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>813980</v>
+        <v>814066</v>
       </c>
       <c r="R82" t="n">
-        <v>7355837</v>
+        <v>7355537</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8933,11 +8938,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -8950,19 +8950,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125392503</v>
+        <v>125392597</v>
       </c>
       <c r="B83" t="n">
         <v>92448</v>
@@ -9002,13 +9002,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>814058</v>
+        <v>814123</v>
       </c>
       <c r="R83" t="n">
-        <v>7355447</v>
+        <v>7355495</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9052,22 +9052,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125392497</v>
+        <v>125401312</v>
       </c>
       <c r="B84" t="n">
-        <v>92440</v>
+        <v>79565</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9080,21 +9080,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>814027</v>
+        <v>813943</v>
       </c>
       <c r="R84" t="n">
-        <v>7355486</v>
+        <v>7355850</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9154,22 +9154,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125417990</v>
+        <v>125433173</v>
       </c>
       <c r="B85" t="n">
-        <v>56836</v>
+        <v>92448</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9182,42 +9182,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Bergträskryggen, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>814036</v>
+        <v>813919</v>
       </c>
       <c r="R85" t="n">
-        <v>7355516</v>
+        <v>7355726</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9252,39 +9244,35 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125433170</v>
+        <v>125417989</v>
       </c>
       <c r="B86" t="n">
-        <v>79565</v>
+        <v>56836</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9293,38 +9281,46 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bergträskryggen, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>813923</v>
+        <v>814054</v>
       </c>
       <c r="R86" t="n">
-        <v>7355691</v>
+        <v>7355732</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9371,22 +9367,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125433173</v>
+        <v>125433171</v>
       </c>
       <c r="B87" t="n">
-        <v>92448</v>
+        <v>79536</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9395,25 +9391,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9423,10 +9419,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>813919</v>
+        <v>814007</v>
       </c>
       <c r="R87" t="n">
-        <v>7355726</v>
+        <v>7355824</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9467,7 +9463,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9486,10 +9481,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125433174</v>
+        <v>125433170</v>
       </c>
       <c r="B88" t="n">
-        <v>92448</v>
+        <v>79565</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9498,25 +9493,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9526,10 +9521,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>813928</v>
+        <v>813923</v>
       </c>
       <c r="R88" t="n">
-        <v>7355688</v>
+        <v>7355691</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9570,7 +9565,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9589,7 +9583,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125417991</v>
+        <v>125433174</v>
       </c>
       <c r="B89" t="n">
         <v>92448</v>
@@ -9629,10 +9623,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>813973</v>
+        <v>813928</v>
       </c>
       <c r="R89" t="n">
-        <v>7355786</v>
+        <v>7355688</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9673,28 +9667,29 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125433171</v>
+        <v>125417991</v>
       </c>
       <c r="B90" t="n">
-        <v>79536</v>
+        <v>92448</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9703,25 +9698,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9731,10 +9726,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>814007</v>
+        <v>813973</v>
       </c>
       <c r="R90" t="n">
-        <v>7355824</v>
+        <v>7355786</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9781,22 +9776,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125433172</v>
+        <v>125417990</v>
       </c>
       <c r="B91" t="n">
-        <v>78684</v>
+        <v>56836</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9805,38 +9800,46 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Bergträskryggen, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>813909</v>
+        <v>814036</v>
       </c>
       <c r="R91" t="n">
-        <v>7355667</v>
+        <v>7355516</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9871,6 +9874,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -9883,22 +9891,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125417989</v>
+        <v>125433172</v>
       </c>
       <c r="B92" t="n">
-        <v>56836</v>
+        <v>78684</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9907,46 +9915,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bergträskryggen, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>814054</v>
+        <v>813909</v>
       </c>
       <c r="R92" t="n">
-        <v>7355732</v>
+        <v>7355667</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9993,12 +9993,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10115,10 +10115,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125395032</v>
+        <v>125395033</v>
       </c>
       <c r="B94" t="n">
-        <v>91088</v>
+        <v>91424</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10127,25 +10127,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3242</v>
+        <v>65</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10155,10 +10155,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>813965</v>
+        <v>814076</v>
       </c>
       <c r="R94" t="n">
-        <v>7355712</v>
+        <v>7355650</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10217,10 +10217,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125395033</v>
+        <v>125395032</v>
       </c>
       <c r="B95" t="n">
-        <v>91424</v>
+        <v>91088</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10229,25 +10229,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>65</v>
+        <v>3242</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10257,10 +10257,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>814076</v>
+        <v>813965</v>
       </c>
       <c r="R95" t="n">
-        <v>7355650</v>
+        <v>7355712</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125392590</v>
+        <v>125401324</v>
       </c>
       <c r="B13" t="n">
-        <v>91131</v>
+        <v>92442</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>813970</v>
+        <v>813960</v>
       </c>
       <c r="R13" t="n">
-        <v>7355771</v>
+        <v>7355731</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1892,22 +1892,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125393608</v>
+        <v>125401298</v>
       </c>
       <c r="B14" t="n">
-        <v>79565</v>
+        <v>92448</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>814054</v>
+        <v>813922</v>
       </c>
       <c r="R14" t="n">
-        <v>7355641</v>
+        <v>7355853</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,22 +1994,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125392275</v>
+        <v>125392590</v>
       </c>
       <c r="B15" t="n">
-        <v>92448</v>
+        <v>91131</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>814068</v>
+        <v>813970</v>
       </c>
       <c r="R15" t="n">
-        <v>7355802</v>
+        <v>7355771</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2096,22 +2096,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125401324</v>
+        <v>125393608</v>
       </c>
       <c r="B16" t="n">
-        <v>92442</v>
+        <v>79565</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>813960</v>
+        <v>814054</v>
       </c>
       <c r="R16" t="n">
-        <v>7355731</v>
+        <v>7355641</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2198,19 +2198,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125401298</v>
+        <v>125392275</v>
       </c>
       <c r="B17" t="n">
         <v>92448</v>
@@ -2250,13 +2250,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>813922</v>
+        <v>814068</v>
       </c>
       <c r="R17" t="n">
-        <v>7355853</v>
+        <v>7355802</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2300,12 +2300,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125403783</v>
+        <v>125393629</v>
       </c>
       <c r="B32" t="n">
-        <v>92448</v>
+        <v>78331</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3752,25 +3752,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,13 +3780,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>813951</v>
+        <v>814063</v>
       </c>
       <c r="R32" t="n">
-        <v>7355737</v>
+        <v>7355649</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3830,22 +3830,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125401301</v>
+        <v>125403783</v>
       </c>
       <c r="B33" t="n">
-        <v>92442</v>
+        <v>92448</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3854,25 +3854,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3882,13 +3882,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>814046</v>
+        <v>813951</v>
       </c>
       <c r="R33" t="n">
-        <v>7355641</v>
+        <v>7355737</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3932,22 +3932,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125401317</v>
+        <v>125401301</v>
       </c>
       <c r="B34" t="n">
-        <v>78592</v>
+        <v>92442</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3984,13 +3984,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>813998</v>
+        <v>814046</v>
       </c>
       <c r="R34" t="n">
-        <v>7355852</v>
+        <v>7355641</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4034,19 +4034,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125401318</v>
+        <v>125401317</v>
       </c>
       <c r="B35" t="n">
         <v>78592</v>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>814001</v>
+        <v>813998</v>
       </c>
       <c r="R35" t="n">
-        <v>7355662</v>
+        <v>7355852</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125393629</v>
+        <v>125401318</v>
       </c>
       <c r="B36" t="n">
-        <v>78331</v>
+        <v>78592</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4164,21 +4164,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4188,13 +4188,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>814063</v>
+        <v>814001</v>
       </c>
       <c r="R36" t="n">
-        <v>7355649</v>
+        <v>7355662</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4238,22 +4238,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125393626</v>
+        <v>125403784</v>
       </c>
       <c r="B37" t="n">
-        <v>78331</v>
+        <v>92448</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4262,25 +4262,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>813874</v>
+        <v>813985</v>
       </c>
       <c r="R37" t="n">
-        <v>7355877</v>
+        <v>7355756</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4340,22 +4340,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125403784</v>
+        <v>125401292</v>
       </c>
       <c r="B38" t="n">
-        <v>92448</v>
+        <v>56836</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4368,21 +4368,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4392,13 +4392,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>813985</v>
+        <v>813980</v>
       </c>
       <c r="R38" t="n">
-        <v>7355756</v>
+        <v>7355837</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4428,6 +4428,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4442,22 +4447,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125401292</v>
+        <v>125393626</v>
       </c>
       <c r="B39" t="n">
-        <v>56836</v>
+        <v>78331</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4466,25 +4471,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4494,10 +4499,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>813980</v>
+        <v>813874</v>
       </c>
       <c r="R39" t="n">
-        <v>7355837</v>
+        <v>7355877</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4532,11 +4537,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4549,12 +4549,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125401297</v>
+        <v>125392506</v>
       </c>
       <c r="B41" t="n">
         <v>92448</v>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>813885</v>
+        <v>813996</v>
       </c>
       <c r="R41" t="n">
-        <v>7355896</v>
+        <v>7355461</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4753,22 +4753,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125401325</v>
+        <v>125393621</v>
       </c>
       <c r="B42" t="n">
-        <v>78331</v>
+        <v>78683</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4805,13 +4805,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>814093</v>
+        <v>813934</v>
       </c>
       <c r="R42" t="n">
-        <v>7355602</v>
+        <v>7355844</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4855,19 +4855,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125392506</v>
+        <v>125392503</v>
       </c>
       <c r="B43" t="n">
         <v>92448</v>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>813996</v>
+        <v>814058</v>
       </c>
       <c r="R43" t="n">
-        <v>7355461</v>
+        <v>7355447</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125393621</v>
+        <v>125392507</v>
       </c>
       <c r="B44" t="n">
-        <v>78683</v>
+        <v>92448</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>813934</v>
+        <v>814049</v>
       </c>
       <c r="R44" t="n">
-        <v>7355844</v>
+        <v>7355489</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5059,22 +5059,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125392503</v>
+        <v>125393607</v>
       </c>
       <c r="B45" t="n">
-        <v>92448</v>
+        <v>79565</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5083,25 +5083,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>814058</v>
+        <v>813971</v>
       </c>
       <c r="R45" t="n">
-        <v>7355447</v>
+        <v>7355703</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5161,19 +5161,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125392507</v>
+        <v>125401297</v>
       </c>
       <c r="B46" t="n">
         <v>92448</v>
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>814049</v>
+        <v>813885</v>
       </c>
       <c r="R46" t="n">
-        <v>7355489</v>
+        <v>7355896</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5263,22 +5263,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125393607</v>
+        <v>125401325</v>
       </c>
       <c r="B47" t="n">
-        <v>79565</v>
+        <v>78331</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5291,21 +5291,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5315,13 +5315,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>813971</v>
+        <v>814093</v>
       </c>
       <c r="R47" t="n">
-        <v>7355703</v>
+        <v>7355602</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5365,12 +5365,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5688,10 +5688,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125392505</v>
+        <v>125401288</v>
       </c>
       <c r="B51" t="n">
-        <v>92448</v>
+        <v>91088</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5700,25 +5700,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>813992</v>
+        <v>813970</v>
       </c>
       <c r="R51" t="n">
-        <v>7355418</v>
+        <v>7355705</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5778,19 +5778,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125393605</v>
+        <v>125401311</v>
       </c>
       <c r="B52" t="n">
         <v>79565</v>
@@ -5830,13 +5830,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>813983</v>
+        <v>813899</v>
       </c>
       <c r="R52" t="n">
-        <v>7355808</v>
+        <v>7355971</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5880,22 +5880,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125401288</v>
+        <v>125393620</v>
       </c>
       <c r="B53" t="n">
-        <v>91088</v>
+        <v>80900</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5908,21 +5908,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3242</v>
+        <v>1049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>813970</v>
+        <v>813875</v>
       </c>
       <c r="R53" t="n">
-        <v>7355705</v>
+        <v>7355877</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5982,22 +5982,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125401311</v>
+        <v>125393623</v>
       </c>
       <c r="B54" t="n">
-        <v>79565</v>
+        <v>78592</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6010,21 +6010,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6034,13 +6034,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>813899</v>
+        <v>814062</v>
       </c>
       <c r="R54" t="n">
-        <v>7355971</v>
+        <v>7355547</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6084,22 +6084,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125393620</v>
+        <v>125392505</v>
       </c>
       <c r="B55" t="n">
-        <v>80900</v>
+        <v>92448</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6108,25 +6108,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>813875</v>
+        <v>813992</v>
       </c>
       <c r="R55" t="n">
-        <v>7355877</v>
+        <v>7355418</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6186,22 +6186,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125393623</v>
+        <v>125393605</v>
       </c>
       <c r="B56" t="n">
-        <v>78592</v>
+        <v>79565</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6214,21 +6214,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>814062</v>
+        <v>813983</v>
       </c>
       <c r="R56" t="n">
-        <v>7355547</v>
+        <v>7355808</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6912,10 +6912,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125392272</v>
+        <v>125393618</v>
       </c>
       <c r="B63" t="n">
-        <v>91326</v>
+        <v>78684</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6924,25 +6924,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6952,13 +6952,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>814011</v>
+        <v>813976</v>
       </c>
       <c r="R63" t="n">
-        <v>7355730</v>
+        <v>7355749</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7002,22 +7002,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125392504</v>
+        <v>125392272</v>
       </c>
       <c r="B64" t="n">
-        <v>92448</v>
+        <v>91326</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7026,25 +7026,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7054,13 +7054,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>813963</v>
+        <v>814011</v>
       </c>
       <c r="R64" t="n">
-        <v>7355408</v>
+        <v>7355730</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7104,19 +7104,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125401323</v>
+        <v>125392504</v>
       </c>
       <c r="B65" t="n">
         <v>92448</v>
@@ -7156,13 +7156,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>813969</v>
+        <v>813963</v>
       </c>
       <c r="R65" t="n">
-        <v>7355700</v>
+        <v>7355408</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7206,22 +7206,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125393618</v>
+        <v>125401323</v>
       </c>
       <c r="B66" t="n">
-        <v>78684</v>
+        <v>92448</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7230,25 +7230,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7258,13 +7258,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>813976</v>
+        <v>813969</v>
       </c>
       <c r="R66" t="n">
-        <v>7355749</v>
+        <v>7355700</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7308,12 +7308,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7835,10 +7835,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125393625</v>
+        <v>125401322</v>
       </c>
       <c r="B72" t="n">
-        <v>77874</v>
+        <v>92448</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7847,25 +7847,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7875,13 +7875,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>813993</v>
+        <v>813963</v>
       </c>
       <c r="R72" t="n">
-        <v>7355850</v>
+        <v>7355778</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7925,22 +7925,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125393613</v>
+        <v>125393625</v>
       </c>
       <c r="B73" t="n">
-        <v>78971</v>
+        <v>77874</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7949,25 +7949,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6434</v>
+        <v>6487</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7977,10 +7977,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>813953</v>
+        <v>813993</v>
       </c>
       <c r="R73" t="n">
-        <v>7355711</v>
+        <v>7355850</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8039,10 +8039,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125393627</v>
+        <v>125393613</v>
       </c>
       <c r="B74" t="n">
-        <v>78331</v>
+        <v>78971</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8051,25 +8051,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>813993</v>
+        <v>813953</v>
       </c>
       <c r="R74" t="n">
-        <v>7355850</v>
+        <v>7355711</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8141,10 +8141,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125392274</v>
+        <v>125393627</v>
       </c>
       <c r="B75" t="n">
-        <v>78947</v>
+        <v>78331</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8157,21 +8157,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8181,13 +8181,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>814062</v>
+        <v>813993</v>
       </c>
       <c r="R75" t="n">
-        <v>7355640</v>
+        <v>7355850</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8231,22 +8231,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125401322</v>
+        <v>125392274</v>
       </c>
       <c r="B76" t="n">
-        <v>92448</v>
+        <v>78947</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8255,25 +8255,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8283,10 +8283,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>813963</v>
+        <v>814062</v>
       </c>
       <c r="R76" t="n">
-        <v>7355778</v>
+        <v>7355640</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8333,12 +8333,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -2312,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125401315</v>
+        <v>125392592</v>
       </c>
       <c r="B18" t="n">
         <v>78684</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>813936</v>
+        <v>813924</v>
       </c>
       <c r="R18" t="n">
-        <v>7355848</v>
+        <v>7355940</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2402,12 +2402,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125392592</v>
+        <v>125401315</v>
       </c>
       <c r="B20" t="n">
         <v>78684</v>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>813924</v>
+        <v>813936</v>
       </c>
       <c r="R20" t="n">
-        <v>7355940</v>
+        <v>7355848</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2606,22 +2606,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125393614</v>
+        <v>125393619</v>
       </c>
       <c r="B21" t="n">
-        <v>78971</v>
+        <v>78684</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>814021</v>
+        <v>814069</v>
       </c>
       <c r="R21" t="n">
-        <v>7355670</v>
+        <v>7355541</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125393603</v>
+        <v>125393614</v>
       </c>
       <c r="B22" t="n">
-        <v>79565</v>
+        <v>78971</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>813848</v>
+        <v>814021</v>
       </c>
       <c r="R22" t="n">
-        <v>7355853</v>
+        <v>7355670</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125393619</v>
+        <v>125393603</v>
       </c>
       <c r="B23" t="n">
-        <v>78684</v>
+        <v>79565</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>814069</v>
+        <v>813848</v>
       </c>
       <c r="R23" t="n">
-        <v>7355541</v>
+        <v>7355853</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125392591</v>
+        <v>125393626</v>
       </c>
       <c r="B11" t="n">
-        <v>79585</v>
+        <v>78373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>813924</v>
+        <v>813874</v>
       </c>
       <c r="R11" t="n">
-        <v>7355940</v>
+        <v>7355877</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125393608</v>
+        <v>125393628</v>
       </c>
       <c r="B12" t="n">
-        <v>79585</v>
+        <v>78373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>814054</v>
+        <v>813979</v>
       </c>
       <c r="R12" t="n">
-        <v>7355641</v>
+        <v>7355768</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125393624</v>
+        <v>125392591</v>
       </c>
       <c r="B13" t="n">
-        <v>92502</v>
+        <v>79585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>813879</v>
+        <v>813924</v>
       </c>
       <c r="R13" t="n">
-        <v>7355876</v>
+        <v>7355940</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125393626</v>
+        <v>125393608</v>
       </c>
       <c r="B14" t="n">
-        <v>78373</v>
+        <v>79585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>813874</v>
+        <v>814054</v>
       </c>
       <c r="R14" t="n">
-        <v>7355877</v>
+        <v>7355641</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125393628</v>
+        <v>125393624</v>
       </c>
       <c r="B15" t="n">
-        <v>78373</v>
+        <v>92502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>813979</v>
+        <v>813879</v>
       </c>
       <c r="R15" t="n">
-        <v>7355768</v>
+        <v>7355876</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125401310</v>
+        <v>125393617</v>
       </c>
       <c r="B23" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>814093</v>
+        <v>813999</v>
       </c>
       <c r="R23" t="n">
-        <v>7355601</v>
+        <v>7355845</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2797,44 +2797,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125394417</v>
+        <v>125393610</v>
       </c>
       <c r="B24" t="n">
-        <v>92502</v>
+        <v>79556</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>813952</v>
+        <v>813948</v>
       </c>
       <c r="R24" t="n">
-        <v>7355835</v>
+        <v>7355861</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2894,22 +2894,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125393617</v>
+        <v>125401310</v>
       </c>
       <c r="B25" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>813999</v>
+        <v>814093</v>
       </c>
       <c r="R25" t="n">
-        <v>7355845</v>
+        <v>7355601</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2991,44 +2991,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125393610</v>
+        <v>125392272</v>
       </c>
       <c r="B26" t="n">
-        <v>79556</v>
+        <v>91380</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,13 +3038,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>813948</v>
+        <v>814011</v>
       </c>
       <c r="R26" t="n">
-        <v>7355861</v>
+        <v>7355730</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3088,44 +3088,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125392272</v>
+        <v>125394417</v>
       </c>
       <c r="B27" t="n">
-        <v>91380</v>
+        <v>92502</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>814011</v>
+        <v>813952</v>
       </c>
       <c r="R27" t="n">
-        <v>7355730</v>
+        <v>7355835</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3185,12 +3185,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125401292</v>
+        <v>125401322</v>
       </c>
       <c r="B33" t="n">
-        <v>56843</v>
+        <v>92502</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3693,21 +3693,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,13 +3717,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>813980</v>
+        <v>813963</v>
       </c>
       <c r="R33" t="n">
-        <v>7355837</v>
+        <v>7355778</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3753,11 +3753,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3772,44 +3767,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125401322</v>
+        <v>125401303</v>
       </c>
       <c r="B34" t="n">
-        <v>92502</v>
+        <v>78373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,13 +3814,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>813963</v>
+        <v>813955</v>
       </c>
       <c r="R34" t="n">
-        <v>7355778</v>
+        <v>7355863</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3869,44 +3864,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125401303</v>
+        <v>125401292</v>
       </c>
       <c r="B35" t="n">
-        <v>78373</v>
+        <v>56843</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>813955</v>
+        <v>813980</v>
       </c>
       <c r="R35" t="n">
-        <v>7355863</v>
+        <v>7355837</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3952,6 +3947,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5244,32 +5244,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125393619</v>
+        <v>125394416</v>
       </c>
       <c r="B49" t="n">
-        <v>78726</v>
+        <v>56843</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>814069</v>
+        <v>814013</v>
       </c>
       <c r="R49" t="n">
-        <v>7355541</v>
+        <v>7355681</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5317,6 +5317,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5329,12 +5334,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5443,32 +5448,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125394416</v>
+        <v>125393619</v>
       </c>
       <c r="B51" t="n">
-        <v>56843</v>
+        <v>78726</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5478,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>814013</v>
+        <v>814069</v>
       </c>
       <c r="R51" t="n">
-        <v>7355681</v>
+        <v>7355541</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5516,11 +5521,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5533,12 +5533,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6127,10 +6127,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125393613</v>
+        <v>125392507</v>
       </c>
       <c r="B58" t="n">
-        <v>78991</v>
+        <v>92502</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6138,21 +6138,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>813953</v>
+        <v>814049</v>
       </c>
       <c r="R58" t="n">
-        <v>7355711</v>
+        <v>7355489</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6212,22 +6212,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125392274</v>
+        <v>125392508</v>
       </c>
       <c r="B59" t="n">
-        <v>78967</v>
+        <v>77916</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6235,21 +6235,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6259,13 +6259,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>814062</v>
+        <v>814001</v>
       </c>
       <c r="R59" t="n">
-        <v>7355640</v>
+        <v>7355442</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6309,22 +6309,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125393615</v>
+        <v>125393602</v>
       </c>
       <c r="B60" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6332,21 +6332,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>814053</v>
+        <v>814085</v>
       </c>
       <c r="R60" t="n">
-        <v>7355646</v>
+        <v>7355609</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6418,32 +6418,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125392508</v>
+        <v>125393613</v>
       </c>
       <c r="B61" t="n">
-        <v>77916</v>
+        <v>78991</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6487</v>
+        <v>6434</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>814001</v>
+        <v>813953</v>
       </c>
       <c r="R61" t="n">
-        <v>7355442</v>
+        <v>7355711</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6503,22 +6503,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125393602</v>
+        <v>125392274</v>
       </c>
       <c r="B62" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6526,21 +6526,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6550,13 +6550,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>814085</v>
+        <v>814062</v>
       </c>
       <c r="R62" t="n">
-        <v>7355609</v>
+        <v>7355640</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6600,44 +6600,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125392507</v>
+        <v>125393615</v>
       </c>
       <c r="B63" t="n">
-        <v>92502</v>
+        <v>78726</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6647,10 +6647,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>814049</v>
+        <v>814053</v>
       </c>
       <c r="R63" t="n">
-        <v>7355489</v>
+        <v>7355646</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6697,12 +6697,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7781,10 +7781,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125392494</v>
+        <v>125393607</v>
       </c>
       <c r="B75" t="n">
-        <v>90258</v>
+        <v>79585</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7792,21 +7792,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7816,10 +7816,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>814004</v>
+        <v>813971</v>
       </c>
       <c r="R75" t="n">
-        <v>7355434</v>
+        <v>7355703</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7866,22 +7866,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125393607</v>
+        <v>125392494</v>
       </c>
       <c r="B76" t="n">
-        <v>79585</v>
+        <v>90258</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7889,21 +7889,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>813971</v>
+        <v>814004</v>
       </c>
       <c r="R76" t="n">
-        <v>7355703</v>
+        <v>7355434</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7963,12 +7963,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8072,32 +8072,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125392506</v>
+        <v>125392267</v>
       </c>
       <c r="B78" t="n">
-        <v>92502</v>
+        <v>90258</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>813996</v>
+        <v>814049</v>
       </c>
       <c r="R78" t="n">
-        <v>7355461</v>
+        <v>7355602</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8157,44 +8157,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125392505</v>
+        <v>125393623</v>
       </c>
       <c r="B79" t="n">
-        <v>92502</v>
+        <v>78634</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8204,10 +8204,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>813992</v>
+        <v>814062</v>
       </c>
       <c r="R79" t="n">
-        <v>7355418</v>
+        <v>7355547</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8254,44 +8254,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125392267</v>
+        <v>125392506</v>
       </c>
       <c r="B80" t="n">
-        <v>90258</v>
+        <v>92502</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8301,13 +8301,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>814049</v>
+        <v>813996</v>
       </c>
       <c r="R80" t="n">
-        <v>7355602</v>
+        <v>7355461</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8351,44 +8351,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125393623</v>
+        <v>125392505</v>
       </c>
       <c r="B81" t="n">
-        <v>78634</v>
+        <v>92502</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8398,10 +8398,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>814062</v>
+        <v>813992</v>
       </c>
       <c r="R81" t="n">
-        <v>7355547</v>
+        <v>7355418</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8448,12 +8448,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125401321</v>
+        <v>125393605</v>
       </c>
       <c r="B2" t="n">
-        <v>92502</v>
+        <v>79585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>813851</v>
+        <v>813983</v>
       </c>
       <c r="R2" t="n">
-        <v>7355951</v>
+        <v>7355808</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125393605</v>
+        <v>125393625</v>
       </c>
       <c r="B3" t="n">
-        <v>79585</v>
+        <v>77916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>813983</v>
+        <v>813993</v>
       </c>
       <c r="R3" t="n">
-        <v>7355808</v>
+        <v>7355850</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125393625</v>
+        <v>125401321</v>
       </c>
       <c r="B4" t="n">
-        <v>77916</v>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>813993</v>
+        <v>813851</v>
       </c>
       <c r="R4" t="n">
-        <v>7355850</v>
+        <v>7355951</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125401289</v>
+        <v>125401288</v>
       </c>
       <c r="B8" t="n">
-        <v>91185</v>
+        <v>91149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>813966</v>
+        <v>813970</v>
       </c>
       <c r="R8" t="n">
-        <v>7355769</v>
+        <v>7355705</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125401288</v>
+        <v>125401289</v>
       </c>
       <c r="B9" t="n">
-        <v>91142</v>
+        <v>91192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>813970</v>
+        <v>813966</v>
       </c>
       <c r="R9" t="n">
-        <v>7355705</v>
+        <v>7355769</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125393626</v>
+        <v>125393624</v>
       </c>
       <c r="B11" t="n">
-        <v>78373</v>
+        <v>92509</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>813874</v>
+        <v>813879</v>
       </c>
       <c r="R11" t="n">
-        <v>7355877</v>
+        <v>7355876</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125393628</v>
+        <v>125392591</v>
       </c>
       <c r="B12" t="n">
-        <v>78373</v>
+        <v>79585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,13 +1680,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>813979</v>
+        <v>813924</v>
       </c>
       <c r="R12" t="n">
-        <v>7355768</v>
+        <v>7355940</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1730,22 +1730,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125392591</v>
+        <v>125393626</v>
       </c>
       <c r="B13" t="n">
-        <v>79585</v>
+        <v>78373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>813924</v>
+        <v>813874</v>
       </c>
       <c r="R13" t="n">
-        <v>7355940</v>
+        <v>7355877</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,12 +1827,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125393624</v>
+        <v>125393628</v>
       </c>
       <c r="B15" t="n">
-        <v>92502</v>
+        <v>78373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>813879</v>
+        <v>813979</v>
       </c>
       <c r="R15" t="n">
-        <v>7355876</v>
+        <v>7355768</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>125392594</v>
       </c>
       <c r="B17" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>125392504</v>
       </c>
       <c r="B18" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>125392275</v>
       </c>
       <c r="B19" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2518,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125403785</v>
+        <v>125401301</v>
       </c>
       <c r="B21" t="n">
-        <v>92502</v>
+        <v>92503</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,13 +2553,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>814010</v>
+        <v>814046</v>
       </c>
       <c r="R21" t="n">
-        <v>7355734</v>
+        <v>7355641</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2603,44 +2603,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125401301</v>
+        <v>125403785</v>
       </c>
       <c r="B22" t="n">
-        <v>92496</v>
+        <v>92509</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,13 +2650,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>814046</v>
+        <v>814010</v>
       </c>
       <c r="R22" t="n">
-        <v>7355641</v>
+        <v>7355734</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2700,44 +2700,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125393617</v>
+        <v>125394417</v>
       </c>
       <c r="B23" t="n">
-        <v>78726</v>
+        <v>92509</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>813999</v>
+        <v>813952</v>
       </c>
       <c r="R23" t="n">
-        <v>7355845</v>
+        <v>7355835</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2797,44 +2797,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125393610</v>
+        <v>125392272</v>
       </c>
       <c r="B24" t="n">
-        <v>79556</v>
+        <v>91387</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>813948</v>
+        <v>814011</v>
       </c>
       <c r="R24" t="n">
-        <v>7355861</v>
+        <v>7355730</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2894,22 +2894,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125401310</v>
+        <v>125393610</v>
       </c>
       <c r="B25" t="n">
-        <v>79585</v>
+        <v>79556</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>814093</v>
+        <v>813948</v>
       </c>
       <c r="R25" t="n">
-        <v>7355601</v>
+        <v>7355861</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2991,44 +2991,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125392272</v>
+        <v>125393617</v>
       </c>
       <c r="B26" t="n">
-        <v>91380</v>
+        <v>78726</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,13 +3038,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>814011</v>
+        <v>813999</v>
       </c>
       <c r="R26" t="n">
-        <v>7355730</v>
+        <v>7355845</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3088,44 +3088,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125394417</v>
+        <v>125401310</v>
       </c>
       <c r="B27" t="n">
-        <v>92502</v>
+        <v>79585</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>813952</v>
+        <v>814093</v>
       </c>
       <c r="R27" t="n">
-        <v>7355835</v>
+        <v>7355601</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3185,12 +3185,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125392595</v>
+        <v>125401325</v>
       </c>
       <c r="B29" t="n">
-        <v>92502</v>
+        <v>78373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>813850</v>
+        <v>814093</v>
       </c>
       <c r="R29" t="n">
-        <v>7355937</v>
+        <v>7355602</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3379,22 +3379,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125392596</v>
+        <v>125392595</v>
       </c>
       <c r="B30" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>813911</v>
+        <v>813850</v>
       </c>
       <c r="R30" t="n">
-        <v>7355874</v>
+        <v>7355937</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3488,10 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125403784</v>
+        <v>125392596</v>
       </c>
       <c r="B31" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>813985</v>
+        <v>813911</v>
       </c>
       <c r="R31" t="n">
-        <v>7355756</v>
+        <v>7355874</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3573,44 +3573,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125401325</v>
+        <v>125403784</v>
       </c>
       <c r="B32" t="n">
-        <v>78373</v>
+        <v>92509</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>814093</v>
+        <v>813985</v>
       </c>
       <c r="R32" t="n">
-        <v>7355602</v>
+        <v>7355756</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3670,22 +3670,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125401322</v>
+        <v>125392597</v>
       </c>
       <c r="B33" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>813963</v>
+        <v>814123</v>
       </c>
       <c r="R33" t="n">
-        <v>7355778</v>
+        <v>7355495</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3767,12 +3767,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125392597</v>
+        <v>125392268</v>
       </c>
       <c r="B36" t="n">
-        <v>92502</v>
+        <v>92707</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>814123</v>
+        <v>814049</v>
       </c>
       <c r="R36" t="n">
-        <v>7355495</v>
+        <v>7355786</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4063,44 +4063,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125392268</v>
+        <v>125401322</v>
       </c>
       <c r="B37" t="n">
-        <v>92700</v>
+        <v>92509</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>814049</v>
+        <v>813963</v>
       </c>
       <c r="R37" t="n">
-        <v>7355786</v>
+        <v>7355778</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4160,12 +4160,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125394420</v>
+        <v>125393614</v>
       </c>
       <c r="B39" t="n">
-        <v>92502</v>
+        <v>78991</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>813977</v>
+        <v>814021</v>
       </c>
       <c r="R39" t="n">
-        <v>7355690</v>
+        <v>7355670</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4354,22 +4354,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125392503</v>
+        <v>125392590</v>
       </c>
       <c r="B40" t="n">
-        <v>92502</v>
+        <v>91192</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4377,21 +4377,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,13 +4401,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>814058</v>
+        <v>813970</v>
       </c>
       <c r="R40" t="n">
-        <v>7355447</v>
+        <v>7355771</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4451,12 +4451,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125393614</v>
+        <v>125394420</v>
       </c>
       <c r="B42" t="n">
-        <v>78991</v>
+        <v>92509</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4571,21 +4571,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>814021</v>
+        <v>813977</v>
       </c>
       <c r="R42" t="n">
-        <v>7355670</v>
+        <v>7355690</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4645,22 +4645,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125392590</v>
+        <v>125392503</v>
       </c>
       <c r="B43" t="n">
-        <v>91185</v>
+        <v>92509</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4668,21 +4668,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,13 +4692,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>813970</v>
+        <v>814058</v>
       </c>
       <c r="R43" t="n">
-        <v>7355771</v>
+        <v>7355447</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4742,22 +4742,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125401324</v>
+        <v>125393629</v>
       </c>
       <c r="B44" t="n">
-        <v>92496</v>
+        <v>78373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4765,21 +4765,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4789,13 +4789,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>813960</v>
+        <v>814063</v>
       </c>
       <c r="R44" t="n">
-        <v>7355731</v>
+        <v>7355649</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4839,44 +4839,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125401298</v>
+        <v>125401324</v>
       </c>
       <c r="B45" t="n">
-        <v>92502</v>
+        <v>92503</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4886,13 +4886,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>813922</v>
+        <v>813960</v>
       </c>
       <c r="R45" t="n">
-        <v>7355853</v>
+        <v>7355731</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4936,44 +4936,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125393629</v>
+        <v>125401298</v>
       </c>
       <c r="B46" t="n">
-        <v>78373</v>
+        <v>92509</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>814063</v>
+        <v>813922</v>
       </c>
       <c r="R46" t="n">
-        <v>7355649</v>
+        <v>7355853</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5033,22 +5033,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125392499</v>
+        <v>125393627</v>
       </c>
       <c r="B47" t="n">
-        <v>92700</v>
+        <v>78373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5056,21 +5056,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>814055</v>
+        <v>813993</v>
       </c>
       <c r="R47" t="n">
-        <v>7355488</v>
+        <v>7355850</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5118,11 +5118,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5135,22 +5130,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125393627</v>
+        <v>125393619</v>
       </c>
       <c r="B48" t="n">
-        <v>78373</v>
+        <v>78726</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5158,21 +5153,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5182,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>813993</v>
+        <v>814069</v>
       </c>
       <c r="R48" t="n">
-        <v>7355850</v>
+        <v>7355541</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5244,32 +5239,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125394416</v>
+        <v>125392499</v>
       </c>
       <c r="B49" t="n">
-        <v>56843</v>
+        <v>92707</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5279,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>814013</v>
+        <v>814055</v>
       </c>
       <c r="R49" t="n">
-        <v>7355681</v>
+        <v>7355488</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5319,7 +5314,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5334,19 +5329,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125401313</v>
+        <v>125394416</v>
       </c>
       <c r="B50" t="n">
         <v>56843</v>
@@ -5381,13 +5376,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>813998</v>
+        <v>814013</v>
       </c>
       <c r="R50" t="n">
-        <v>7355672</v>
+        <v>7355681</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5436,44 +5431,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125393619</v>
+        <v>125401313</v>
       </c>
       <c r="B51" t="n">
-        <v>78726</v>
+        <v>56843</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5483,13 +5478,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>814069</v>
+        <v>813998</v>
       </c>
       <c r="R51" t="n">
-        <v>7355541</v>
+        <v>7355672</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5519,6 +5514,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5533,44 +5533,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125392502</v>
+        <v>125393606</v>
       </c>
       <c r="B52" t="n">
-        <v>91478</v>
+        <v>79585</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5580,10 +5580,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>813982</v>
+        <v>813976</v>
       </c>
       <c r="R52" t="n">
-        <v>7355407</v>
+        <v>7355749</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5630,44 +5630,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125393606</v>
+        <v>125392498</v>
       </c>
       <c r="B53" t="n">
-        <v>79585</v>
+        <v>78991</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>813976</v>
+        <v>814002</v>
       </c>
       <c r="R53" t="n">
-        <v>7355749</v>
+        <v>7355412</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5727,44 +5727,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125392498</v>
+        <v>125393622</v>
       </c>
       <c r="B54" t="n">
-        <v>78991</v>
+        <v>78725</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>814002</v>
+        <v>814058</v>
       </c>
       <c r="R54" t="n">
-        <v>7355412</v>
+        <v>7355641</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5824,22 +5824,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125393622</v>
+        <v>125401314</v>
       </c>
       <c r="B55" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,21 +5847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,13 +5871,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>814058</v>
+        <v>813899</v>
       </c>
       <c r="R55" t="n">
-        <v>7355641</v>
+        <v>7355975</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5921,44 +5921,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125392592</v>
+        <v>125392502</v>
       </c>
       <c r="B56" t="n">
-        <v>78726</v>
+        <v>91485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5968,13 +5968,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>813924</v>
+        <v>813982</v>
       </c>
       <c r="R56" t="n">
-        <v>7355940</v>
+        <v>7355407</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6018,19 +6018,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125401314</v>
+        <v>125392592</v>
       </c>
       <c r="B57" t="n">
         <v>78726</v>
@@ -6065,10 +6065,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>813899</v>
+        <v>813924</v>
       </c>
       <c r="R57" t="n">
-        <v>7355975</v>
+        <v>7355940</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6115,44 +6115,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125392507</v>
+        <v>125392508</v>
       </c>
       <c r="B58" t="n">
-        <v>92502</v>
+        <v>77916</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>814049</v>
+        <v>814001</v>
       </c>
       <c r="R58" t="n">
-        <v>7355489</v>
+        <v>7355442</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6224,32 +6224,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125392508</v>
+        <v>125393613</v>
       </c>
       <c r="B59" t="n">
-        <v>77916</v>
+        <v>78991</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6487</v>
+        <v>6434</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>814001</v>
+        <v>813953</v>
       </c>
       <c r="R59" t="n">
-        <v>7355442</v>
+        <v>7355711</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6309,12 +6309,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6418,10 +6418,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125393613</v>
+        <v>125392507</v>
       </c>
       <c r="B61" t="n">
-        <v>78991</v>
+        <v>92509</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6429,21 +6429,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>813953</v>
+        <v>814049</v>
       </c>
       <c r="R61" t="n">
-        <v>7355711</v>
+        <v>7355489</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6503,12 +6503,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6709,10 +6709,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125403783</v>
+        <v>125401297</v>
       </c>
       <c r="B64" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6744,13 +6744,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>813951</v>
+        <v>813885</v>
       </c>
       <c r="R64" t="n">
-        <v>7355737</v>
+        <v>7355896</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6794,22 +6794,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125401297</v>
+        <v>125403783</v>
       </c>
       <c r="B65" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6841,13 +6841,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>813885</v>
+        <v>813951</v>
       </c>
       <c r="R65" t="n">
-        <v>7355896</v>
+        <v>7355737</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6891,12 +6891,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7097,10 +7097,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125393603</v>
+        <v>125393620</v>
       </c>
       <c r="B68" t="n">
-        <v>79585</v>
+        <v>80942</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7108,21 +7108,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>813848</v>
+        <v>813875</v>
       </c>
       <c r="R68" t="n">
-        <v>7355853</v>
+        <v>7355877</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7194,32 +7194,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125401319</v>
+        <v>125392497</v>
       </c>
       <c r="B69" t="n">
-        <v>92502</v>
+        <v>92501</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7229,13 +7229,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>813998</v>
+        <v>814027</v>
       </c>
       <c r="R69" t="n">
-        <v>7355850</v>
+        <v>7355486</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7279,22 +7279,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125401299</v>
+        <v>125394419</v>
       </c>
       <c r="B70" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>814052</v>
+        <v>813962</v>
       </c>
       <c r="R70" t="n">
-        <v>7355644</v>
+        <v>7355721</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7376,22 +7376,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125393620</v>
+        <v>125393603</v>
       </c>
       <c r="B71" t="n">
-        <v>80942</v>
+        <v>79585</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7399,21 +7399,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7423,10 +7423,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>813875</v>
+        <v>813848</v>
       </c>
       <c r="R71" t="n">
-        <v>7355877</v>
+        <v>7355853</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7485,32 +7485,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125392497</v>
+        <v>125401299</v>
       </c>
       <c r="B72" t="n">
-        <v>92494</v>
+        <v>92509</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>814027</v>
+        <v>814052</v>
       </c>
       <c r="R72" t="n">
-        <v>7355486</v>
+        <v>7355644</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7570,22 +7570,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125394419</v>
+        <v>125401319</v>
       </c>
       <c r="B73" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7617,13 +7617,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>813962</v>
+        <v>813998</v>
       </c>
       <c r="R73" t="n">
-        <v>7355721</v>
+        <v>7355850</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7667,44 +7667,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125401296</v>
+        <v>125392501</v>
       </c>
       <c r="B74" t="n">
-        <v>92502</v>
+        <v>91845</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>5454</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>813777</v>
+        <v>814052</v>
       </c>
       <c r="R74" t="n">
-        <v>7355862</v>
+        <v>7355484</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7752,11 +7752,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Häxring</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -7769,12 +7764,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -7881,7 +7876,7 @@
         <v>125392494</v>
       </c>
       <c r="B76" t="n">
-        <v>90258</v>
+        <v>90265</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7975,32 +7970,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125392501</v>
+        <v>125401296</v>
       </c>
       <c r="B77" t="n">
-        <v>91838</v>
+        <v>92509</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5454</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8010,10 +8005,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>814052</v>
+        <v>813777</v>
       </c>
       <c r="R77" t="n">
-        <v>7355484</v>
+        <v>7355862</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8048,6 +8043,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Häxring</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8060,12 +8060,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8075,7 +8075,7 @@
         <v>125392267</v>
       </c>
       <c r="B78" t="n">
-        <v>90258</v>
+        <v>90265</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>125392506</v>
       </c>
       <c r="B80" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>125392505</v>
       </c>
       <c r="B81" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>125401323</v>
       </c>
       <c r="B84" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>125417991</v>
       </c>
       <c r="B87" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>125433174</v>
       </c>
       <c r="B88" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>125433173</v>
       </c>
       <c r="B91" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>125395032</v>
       </c>
       <c r="B94" t="n">
-        <v>91142</v>
+        <v>91149</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>125395033</v>
       </c>
       <c r="B95" t="n">
-        <v>91478</v>
+        <v>91485</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125393618</v>
+        <v>125401301</v>
       </c>
       <c r="B20" t="n">
-        <v>78726</v>
+        <v>92503</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>813976</v>
+        <v>814046</v>
       </c>
       <c r="R20" t="n">
-        <v>7355749</v>
+        <v>7355641</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2506,44 +2506,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125401301</v>
+        <v>125403785</v>
       </c>
       <c r="B21" t="n">
-        <v>92503</v>
+        <v>92509</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,13 +2553,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>814046</v>
+        <v>814010</v>
       </c>
       <c r="R21" t="n">
-        <v>7355641</v>
+        <v>7355734</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2603,44 +2603,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125403785</v>
+        <v>125393618</v>
       </c>
       <c r="B22" t="n">
-        <v>92509</v>
+        <v>78726</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,13 +2650,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>814010</v>
+        <v>813976</v>
       </c>
       <c r="R22" t="n">
-        <v>7355734</v>
+        <v>7355749</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2700,12 +2700,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3779,32 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125401303</v>
+        <v>125401292</v>
       </c>
       <c r="B34" t="n">
-        <v>78373</v>
+        <v>56843</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>813955</v>
+        <v>813980</v>
       </c>
       <c r="R34" t="n">
-        <v>7355863</v>
+        <v>7355837</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3850,6 +3850,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3876,32 +3881,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125401292</v>
+        <v>125392268</v>
       </c>
       <c r="B35" t="n">
-        <v>56843</v>
+        <v>92707</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,13 +3916,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>813980</v>
+        <v>814049</v>
       </c>
       <c r="R35" t="n">
-        <v>7355837</v>
+        <v>7355786</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3947,11 +3952,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3966,44 +3966,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125392268</v>
+        <v>125401322</v>
       </c>
       <c r="B36" t="n">
-        <v>92707</v>
+        <v>92509</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>814049</v>
+        <v>813963</v>
       </c>
       <c r="R36" t="n">
-        <v>7355786</v>
+        <v>7355778</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4063,44 +4063,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125401322</v>
+        <v>125401303</v>
       </c>
       <c r="B37" t="n">
-        <v>92509</v>
+        <v>78373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>813963</v>
+        <v>813955</v>
       </c>
       <c r="R37" t="n">
-        <v>7355778</v>
+        <v>7355863</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4160,12 +4160,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4754,10 +4754,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125393629</v>
+        <v>125401324</v>
       </c>
       <c r="B44" t="n">
-        <v>78373</v>
+        <v>92503</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4765,21 +4765,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4789,13 +4789,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>814063</v>
+        <v>813960</v>
       </c>
       <c r="R44" t="n">
-        <v>7355649</v>
+        <v>7355731</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4839,44 +4839,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125401324</v>
+        <v>125401298</v>
       </c>
       <c r="B45" t="n">
-        <v>92503</v>
+        <v>92509</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4886,13 +4886,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>813960</v>
+        <v>813922</v>
       </c>
       <c r="R45" t="n">
-        <v>7355731</v>
+        <v>7355853</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4936,44 +4936,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125401298</v>
+        <v>125393629</v>
       </c>
       <c r="B46" t="n">
-        <v>92509</v>
+        <v>78373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>813922</v>
+        <v>814063</v>
       </c>
       <c r="R46" t="n">
-        <v>7355853</v>
+        <v>7355649</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5033,12 +5033,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -7097,32 +7097,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125393620</v>
+        <v>125401299</v>
       </c>
       <c r="B68" t="n">
-        <v>80942</v>
+        <v>92509</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>813875</v>
+        <v>814052</v>
       </c>
       <c r="R68" t="n">
-        <v>7355877</v>
+        <v>7355644</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7182,44 +7182,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125392497</v>
+        <v>125401319</v>
       </c>
       <c r="B69" t="n">
-        <v>92501</v>
+        <v>92509</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7229,13 +7229,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>814027</v>
+        <v>813998</v>
       </c>
       <c r="R69" t="n">
-        <v>7355486</v>
+        <v>7355850</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7279,44 +7279,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125394419</v>
+        <v>125393620</v>
       </c>
       <c r="B70" t="n">
-        <v>92509</v>
+        <v>80942</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>813962</v>
+        <v>813875</v>
       </c>
       <c r="R70" t="n">
-        <v>7355721</v>
+        <v>7355877</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7376,22 +7376,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125393603</v>
+        <v>125392497</v>
       </c>
       <c r="B71" t="n">
-        <v>79585</v>
+        <v>92501</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7399,21 +7399,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7423,10 +7423,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>813848</v>
+        <v>814027</v>
       </c>
       <c r="R71" t="n">
-        <v>7355853</v>
+        <v>7355486</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7473,19 +7473,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125401299</v>
+        <v>125394419</v>
       </c>
       <c r="B72" t="n">
         <v>92509</v>
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>814052</v>
+        <v>813962</v>
       </c>
       <c r="R72" t="n">
-        <v>7355644</v>
+        <v>7355721</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7570,44 +7570,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125401319</v>
+        <v>125393603</v>
       </c>
       <c r="B73" t="n">
-        <v>92509</v>
+        <v>79585</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7617,13 +7617,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>813998</v>
+        <v>813848</v>
       </c>
       <c r="R73" t="n">
-        <v>7355850</v>
+        <v>7355853</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7667,12 +7667,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125401301</v>
+        <v>125393618</v>
       </c>
       <c r="B20" t="n">
-        <v>92503</v>
+        <v>78726</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>814046</v>
+        <v>813976</v>
       </c>
       <c r="R20" t="n">
-        <v>7355641</v>
+        <v>7355749</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2506,44 +2506,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125403785</v>
+        <v>125401301</v>
       </c>
       <c r="B21" t="n">
-        <v>92509</v>
+        <v>92503</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,13 +2553,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>814010</v>
+        <v>814046</v>
       </c>
       <c r="R21" t="n">
-        <v>7355734</v>
+        <v>7355641</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2603,44 +2603,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125393618</v>
+        <v>125403785</v>
       </c>
       <c r="B22" t="n">
-        <v>78726</v>
+        <v>92509</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,13 +2650,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>813976</v>
+        <v>814010</v>
       </c>
       <c r="R22" t="n">
-        <v>7355749</v>
+        <v>7355734</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2700,12 +2700,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125401325</v>
+        <v>125392595</v>
       </c>
       <c r="B29" t="n">
-        <v>78373</v>
+        <v>92509</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>814093</v>
+        <v>813850</v>
       </c>
       <c r="R29" t="n">
-        <v>7355602</v>
+        <v>7355937</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3379,19 +3379,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125392595</v>
+        <v>125392596</v>
       </c>
       <c r="B30" t="n">
         <v>92509</v>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>813850</v>
+        <v>813911</v>
       </c>
       <c r="R30" t="n">
-        <v>7355937</v>
+        <v>7355874</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125392596</v>
+        <v>125401325</v>
       </c>
       <c r="B31" t="n">
-        <v>92509</v>
+        <v>78373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>813911</v>
+        <v>814093</v>
       </c>
       <c r="R31" t="n">
-        <v>7355874</v>
+        <v>7355602</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3573,12 +3573,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -5045,10 +5045,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125393627</v>
+        <v>125393619</v>
       </c>
       <c r="B47" t="n">
-        <v>78373</v>
+        <v>78726</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5056,21 +5056,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>813993</v>
+        <v>814069</v>
       </c>
       <c r="R47" t="n">
-        <v>7355850</v>
+        <v>7355541</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5142,32 +5142,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125393619</v>
+        <v>125401313</v>
       </c>
       <c r="B48" t="n">
-        <v>78726</v>
+        <v>56843</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>814069</v>
+        <v>813998</v>
       </c>
       <c r="R48" t="n">
-        <v>7355541</v>
+        <v>7355672</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5213,6 +5213,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5227,22 +5232,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125392499</v>
+        <v>125393627</v>
       </c>
       <c r="B49" t="n">
-        <v>92707</v>
+        <v>78373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5250,21 +5255,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5274,10 +5279,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>814055</v>
+        <v>813993</v>
       </c>
       <c r="R49" t="n">
-        <v>7355488</v>
+        <v>7355850</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5312,11 +5317,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5329,44 +5329,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125394416</v>
+        <v>125392499</v>
       </c>
       <c r="B50" t="n">
-        <v>56843</v>
+        <v>92707</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>814013</v>
+        <v>814055</v>
       </c>
       <c r="R50" t="n">
-        <v>7355681</v>
+        <v>7355488</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5431,19 +5431,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125401313</v>
+        <v>125394416</v>
       </c>
       <c r="B51" t="n">
         <v>56843</v>
@@ -5478,13 +5478,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>813998</v>
+        <v>814013</v>
       </c>
       <c r="R51" t="n">
-        <v>7355672</v>
+        <v>7355681</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5533,22 +5533,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125393606</v>
+        <v>125401314</v>
       </c>
       <c r="B52" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5556,21 +5556,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>813976</v>
+        <v>813899</v>
       </c>
       <c r="R52" t="n">
-        <v>7355749</v>
+        <v>7355975</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5630,44 +5630,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125392498</v>
+        <v>125392592</v>
       </c>
       <c r="B53" t="n">
-        <v>78991</v>
+        <v>78726</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>814002</v>
+        <v>813924</v>
       </c>
       <c r="R53" t="n">
-        <v>7355412</v>
+        <v>7355940</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5727,22 +5727,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125393622</v>
+        <v>125393606</v>
       </c>
       <c r="B54" t="n">
-        <v>78725</v>
+        <v>79585</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>814058</v>
+        <v>813976</v>
       </c>
       <c r="R54" t="n">
-        <v>7355641</v>
+        <v>7355749</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5836,32 +5836,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125401314</v>
+        <v>125392498</v>
       </c>
       <c r="B55" t="n">
-        <v>78726</v>
+        <v>78991</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,13 +5871,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>813899</v>
+        <v>814002</v>
       </c>
       <c r="R55" t="n">
-        <v>7355975</v>
+        <v>7355412</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5921,44 +5921,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125392502</v>
+        <v>125393622</v>
       </c>
       <c r="B56" t="n">
-        <v>91485</v>
+        <v>78725</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>813982</v>
+        <v>814058</v>
       </c>
       <c r="R56" t="n">
-        <v>7355407</v>
+        <v>7355641</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6018,44 +6018,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125392592</v>
+        <v>125392502</v>
       </c>
       <c r="B57" t="n">
-        <v>78726</v>
+        <v>91485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6065,13 +6065,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>813924</v>
+        <v>813982</v>
       </c>
       <c r="R57" t="n">
-        <v>7355940</v>
+        <v>7355407</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6115,12 +6115,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7097,32 +7097,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125401299</v>
+        <v>125393620</v>
       </c>
       <c r="B68" t="n">
-        <v>92509</v>
+        <v>80942</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>814052</v>
+        <v>813875</v>
       </c>
       <c r="R68" t="n">
-        <v>7355644</v>
+        <v>7355877</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7182,44 +7182,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125401319</v>
+        <v>125392497</v>
       </c>
       <c r="B69" t="n">
-        <v>92509</v>
+        <v>92501</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7229,13 +7229,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>813998</v>
+        <v>814027</v>
       </c>
       <c r="R69" t="n">
-        <v>7355850</v>
+        <v>7355486</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7279,44 +7279,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125393620</v>
+        <v>125394419</v>
       </c>
       <c r="B70" t="n">
-        <v>80942</v>
+        <v>92509</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>813875</v>
+        <v>813962</v>
       </c>
       <c r="R70" t="n">
-        <v>7355877</v>
+        <v>7355721</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7376,22 +7376,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125392497</v>
+        <v>125393603</v>
       </c>
       <c r="B71" t="n">
-        <v>92501</v>
+        <v>79585</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7399,21 +7399,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7423,10 +7423,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>814027</v>
+        <v>813848</v>
       </c>
       <c r="R71" t="n">
-        <v>7355486</v>
+        <v>7355853</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7473,19 +7473,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125394419</v>
+        <v>125401299</v>
       </c>
       <c r="B72" t="n">
         <v>92509</v>
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>813962</v>
+        <v>814052</v>
       </c>
       <c r="R72" t="n">
-        <v>7355721</v>
+        <v>7355644</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7570,44 +7570,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125393603</v>
+        <v>125401319</v>
       </c>
       <c r="B73" t="n">
-        <v>79585</v>
+        <v>92509</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7617,13 +7617,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>813848</v>
+        <v>813998</v>
       </c>
       <c r="R73" t="n">
-        <v>7355853</v>
+        <v>7355850</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7667,12 +7667,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125393605</v>
+        <v>125401321</v>
       </c>
       <c r="B2" t="n">
-        <v>79585</v>
+        <v>92518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>813983</v>
+        <v>813851</v>
       </c>
       <c r="R2" t="n">
-        <v>7355808</v>
+        <v>7355951</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125393625</v>
+        <v>125393605</v>
       </c>
       <c r="B3" t="n">
-        <v>77916</v>
+        <v>79586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>813993</v>
+        <v>813983</v>
       </c>
       <c r="R3" t="n">
-        <v>7355850</v>
+        <v>7355808</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125401321</v>
+        <v>125393625</v>
       </c>
       <c r="B4" t="n">
-        <v>92509</v>
+        <v>77917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>813851</v>
+        <v>813993</v>
       </c>
       <c r="R4" t="n">
-        <v>7355951</v>
+        <v>7355850</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>125401317</v>
       </c>
       <c r="B5" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125393616</v>
       </c>
       <c r="B6" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125392271</v>
       </c>
       <c r="B7" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125401288</v>
+        <v>125401315</v>
       </c>
       <c r="B8" t="n">
-        <v>91149</v>
+        <v>78727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>813970</v>
+        <v>813936</v>
       </c>
       <c r="R8" t="n">
-        <v>7355705</v>
+        <v>7355848</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,44 +1342,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125401289</v>
+        <v>125401288</v>
       </c>
       <c r="B9" t="n">
-        <v>91192</v>
+        <v>91150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>813966</v>
+        <v>813970</v>
       </c>
       <c r="R9" t="n">
-        <v>7355769</v>
+        <v>7355705</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125401315</v>
+        <v>125401289</v>
       </c>
       <c r="B10" t="n">
-        <v>78726</v>
+        <v>91193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>813936</v>
+        <v>813966</v>
       </c>
       <c r="R10" t="n">
-        <v>7355848</v>
+        <v>7355769</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,12 +1536,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
         <v>125393624</v>
       </c>
       <c r="B11" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125392591</v>
       </c>
       <c r="B12" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125393626</v>
       </c>
       <c r="B13" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>125393608</v>
       </c>
       <c r="B14" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>125393628</v>
       </c>
       <c r="B15" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>125393611</v>
       </c>
       <c r="B16" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>125392594</v>
       </c>
       <c r="B17" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>125392504</v>
       </c>
       <c r="B18" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>125392275</v>
       </c>
       <c r="B19" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>125393618</v>
       </c>
       <c r="B20" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2518,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125401301</v>
+        <v>125403785</v>
       </c>
       <c r="B21" t="n">
-        <v>92503</v>
+        <v>92518</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,13 +2553,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>814046</v>
+        <v>814010</v>
       </c>
       <c r="R21" t="n">
-        <v>7355641</v>
+        <v>7355734</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2603,44 +2603,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125403785</v>
+        <v>125401301</v>
       </c>
       <c r="B22" t="n">
-        <v>92509</v>
+        <v>92512</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,13 +2650,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>814010</v>
+        <v>814046</v>
       </c>
       <c r="R22" t="n">
-        <v>7355734</v>
+        <v>7355641</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2700,22 +2700,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125394417</v>
+        <v>125392495</v>
       </c>
       <c r="B23" t="n">
-        <v>92509</v>
+        <v>56843</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>813952</v>
+        <v>814057</v>
       </c>
       <c r="R23" t="n">
-        <v>7355835</v>
+        <v>7355446</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2797,44 +2797,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125392272</v>
+        <v>125394417</v>
       </c>
       <c r="B24" t="n">
-        <v>91387</v>
+        <v>92518</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>814011</v>
+        <v>813952</v>
       </c>
       <c r="R24" t="n">
-        <v>7355730</v>
+        <v>7355835</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2894,44 +2894,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125393610</v>
+        <v>125392272</v>
       </c>
       <c r="B25" t="n">
-        <v>79556</v>
+        <v>91389</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>813948</v>
+        <v>814011</v>
       </c>
       <c r="R25" t="n">
-        <v>7355861</v>
+        <v>7355730</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2991,22 +2991,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125393617</v>
+        <v>125393610</v>
       </c>
       <c r="B26" t="n">
-        <v>78726</v>
+        <v>79557</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>813999</v>
+        <v>813948</v>
       </c>
       <c r="R26" t="n">
-        <v>7355845</v>
+        <v>7355861</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125401310</v>
+        <v>125393617</v>
       </c>
       <c r="B27" t="n">
-        <v>79585</v>
+        <v>78727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>814093</v>
+        <v>813999</v>
       </c>
       <c r="R27" t="n">
-        <v>7355601</v>
+        <v>7355845</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3185,44 +3185,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125392495</v>
+        <v>125401310</v>
       </c>
       <c r="B28" t="n">
-        <v>56843</v>
+        <v>79586</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>814057</v>
+        <v>814093</v>
       </c>
       <c r="R28" t="n">
-        <v>7355446</v>
+        <v>7355601</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3282,12 +3282,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3297,7 +3297,7 @@
         <v>125392595</v>
       </c>
       <c r="B29" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>125392596</v>
       </c>
       <c r="B30" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125401325</v>
+        <v>125403784</v>
       </c>
       <c r="B31" t="n">
-        <v>78373</v>
+        <v>92518</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>814093</v>
+        <v>813985</v>
       </c>
       <c r="R31" t="n">
-        <v>7355602</v>
+        <v>7355756</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3573,44 +3573,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125403784</v>
+        <v>125401325</v>
       </c>
       <c r="B32" t="n">
-        <v>92509</v>
+        <v>78374</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>813985</v>
+        <v>814093</v>
       </c>
       <c r="R32" t="n">
-        <v>7355756</v>
+        <v>7355602</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3670,12 +3670,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3685,7 +3685,7 @@
         <v>125392597</v>
       </c>
       <c r="B33" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3779,32 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125401292</v>
+        <v>125392268</v>
       </c>
       <c r="B34" t="n">
-        <v>56843</v>
+        <v>92710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,13 +3814,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>813980</v>
+        <v>814049</v>
       </c>
       <c r="R34" t="n">
-        <v>7355837</v>
+        <v>7355786</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3850,11 +3850,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3869,44 +3864,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125392268</v>
+        <v>125401292</v>
       </c>
       <c r="B35" t="n">
-        <v>92707</v>
+        <v>56843</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,13 +3911,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>814049</v>
+        <v>813980</v>
       </c>
       <c r="R35" t="n">
-        <v>7355786</v>
+        <v>7355837</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3952,6 +3947,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3966,12 +3966,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -3981,7 +3981,7 @@
         <v>125401322</v>
       </c>
       <c r="B36" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>125401303</v>
       </c>
       <c r="B37" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>125401318</v>
       </c>
       <c r="B38" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>125393614</v>
       </c>
       <c r="B39" t="n">
-        <v>78991</v>
+        <v>78992</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>125392590</v>
       </c>
       <c r="B40" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>125393609</v>
       </c>
       <c r="B41" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>125394420</v>
       </c>
       <c r="B42" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>125392503</v>
       </c>
       <c r="B43" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>125401324</v>
       </c>
       <c r="B44" t="n">
-        <v>92503</v>
+        <v>92512</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>125401298</v>
       </c>
       <c r="B45" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>125393629</v>
       </c>
       <c r="B46" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5045,10 +5045,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125393619</v>
+        <v>125393627</v>
       </c>
       <c r="B47" t="n">
-        <v>78726</v>
+        <v>78374</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5056,21 +5056,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>814069</v>
+        <v>813993</v>
       </c>
       <c r="R47" t="n">
-        <v>7355541</v>
+        <v>7355850</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5142,32 +5142,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125401313</v>
+        <v>125392499</v>
       </c>
       <c r="B48" t="n">
-        <v>56843</v>
+        <v>92710</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>813998</v>
+        <v>814055</v>
       </c>
       <c r="R48" t="n">
-        <v>7355672</v>
+        <v>7355488</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5232,44 +5232,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125393627</v>
+        <v>125394416</v>
       </c>
       <c r="B49" t="n">
-        <v>78373</v>
+        <v>56843</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>813993</v>
+        <v>814013</v>
       </c>
       <c r="R49" t="n">
-        <v>7355850</v>
+        <v>7355681</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5317,6 +5317,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5329,22 +5334,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125392499</v>
+        <v>125393619</v>
       </c>
       <c r="B50" t="n">
-        <v>92707</v>
+        <v>78727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5352,21 +5357,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5376,10 +5381,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>814055</v>
+        <v>814069</v>
       </c>
       <c r="R50" t="n">
-        <v>7355488</v>
+        <v>7355541</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5414,11 +5419,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5431,19 +5431,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125394416</v>
+        <v>125401313</v>
       </c>
       <c r="B51" t="n">
         <v>56843</v>
@@ -5478,13 +5478,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>814013</v>
+        <v>813998</v>
       </c>
       <c r="R51" t="n">
-        <v>7355681</v>
+        <v>7355672</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5533,22 +5533,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125401314</v>
+        <v>125393606</v>
       </c>
       <c r="B52" t="n">
-        <v>78726</v>
+        <v>79586</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5556,21 +5556,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>813899</v>
+        <v>813976</v>
       </c>
       <c r="R52" t="n">
-        <v>7355975</v>
+        <v>7355749</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5630,44 +5630,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125392592</v>
+        <v>125392498</v>
       </c>
       <c r="B53" t="n">
-        <v>78726</v>
+        <v>78992</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>813924</v>
+        <v>814002</v>
       </c>
       <c r="R53" t="n">
-        <v>7355940</v>
+        <v>7355412</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5727,22 +5727,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125393606</v>
+        <v>125393622</v>
       </c>
       <c r="B54" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>813976</v>
+        <v>814058</v>
       </c>
       <c r="R54" t="n">
-        <v>7355749</v>
+        <v>7355641</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5836,32 +5836,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125392498</v>
+        <v>125392502</v>
       </c>
       <c r="B55" t="n">
-        <v>78991</v>
+        <v>91489</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6434</v>
+        <v>65</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>814002</v>
+        <v>813982</v>
       </c>
       <c r="R55" t="n">
-        <v>7355412</v>
+        <v>7355407</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5933,10 +5933,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125393622</v>
+        <v>125392592</v>
       </c>
       <c r="B56" t="n">
-        <v>78725</v>
+        <v>78727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5944,21 +5944,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5968,13 +5968,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>814058</v>
+        <v>813924</v>
       </c>
       <c r="R56" t="n">
-        <v>7355641</v>
+        <v>7355940</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6018,44 +6018,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125392502</v>
+        <v>125401314</v>
       </c>
       <c r="B57" t="n">
-        <v>91485</v>
+        <v>78727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6065,13 +6065,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>813982</v>
+        <v>813899</v>
       </c>
       <c r="R57" t="n">
-        <v>7355407</v>
+        <v>7355975</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6115,22 +6115,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125392508</v>
+        <v>125393615</v>
       </c>
       <c r="B58" t="n">
-        <v>77916</v>
+        <v>78727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6138,21 +6138,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>814001</v>
+        <v>814053</v>
       </c>
       <c r="R58" t="n">
-        <v>7355442</v>
+        <v>7355646</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6212,44 +6212,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125393613</v>
+        <v>125392508</v>
       </c>
       <c r="B59" t="n">
-        <v>78991</v>
+        <v>77917</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6434</v>
+        <v>6487</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>813953</v>
+        <v>814001</v>
       </c>
       <c r="R59" t="n">
-        <v>7355711</v>
+        <v>7355442</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6309,44 +6309,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125393602</v>
+        <v>125393613</v>
       </c>
       <c r="B60" t="n">
-        <v>79585</v>
+        <v>78992</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>814085</v>
+        <v>813953</v>
       </c>
       <c r="R60" t="n">
-        <v>7355609</v>
+        <v>7355711</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6418,32 +6418,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125392507</v>
+        <v>125393602</v>
       </c>
       <c r="B61" t="n">
-        <v>92509</v>
+        <v>79586</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>814049</v>
+        <v>814085</v>
       </c>
       <c r="R61" t="n">
-        <v>7355489</v>
+        <v>7355609</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6503,44 +6503,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125392274</v>
+        <v>125392507</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>92518</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6550,13 +6550,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>814062</v>
+        <v>814049</v>
       </c>
       <c r="R62" t="n">
-        <v>7355640</v>
+        <v>7355489</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6600,22 +6600,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125393615</v>
+        <v>125392274</v>
       </c>
       <c r="B63" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6623,21 +6623,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6647,13 +6647,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>814053</v>
+        <v>814062</v>
       </c>
       <c r="R63" t="n">
-        <v>7355646</v>
+        <v>7355640</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6697,22 +6697,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125401297</v>
+        <v>125403783</v>
       </c>
       <c r="B64" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6744,13 +6744,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>813885</v>
+        <v>813951</v>
       </c>
       <c r="R64" t="n">
-        <v>7355896</v>
+        <v>7355737</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6794,22 +6794,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125403783</v>
+        <v>125401297</v>
       </c>
       <c r="B65" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6841,13 +6841,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>813951</v>
+        <v>813885</v>
       </c>
       <c r="R65" t="n">
-        <v>7355737</v>
+        <v>7355896</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6891,22 +6891,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125401312</v>
+        <v>125401311</v>
       </c>
       <c r="B66" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>813943</v>
+        <v>813899</v>
       </c>
       <c r="R66" t="n">
-        <v>7355850</v>
+        <v>7355971</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7000,10 +7000,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125401311</v>
+        <v>125401312</v>
       </c>
       <c r="B67" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7035,10 +7035,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>813899</v>
+        <v>813943</v>
       </c>
       <c r="R67" t="n">
-        <v>7355971</v>
+        <v>7355850</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7100,7 +7100,7 @@
         <v>125393620</v>
       </c>
       <c r="B68" t="n">
-        <v>80942</v>
+        <v>80943</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>125392497</v>
       </c>
       <c r="B69" t="n">
-        <v>92501</v>
+        <v>92510</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>125394419</v>
       </c>
       <c r="B70" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>125393603</v>
       </c>
       <c r="B71" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7485,10 +7485,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125401299</v>
+        <v>125401319</v>
       </c>
       <c r="B72" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7520,13 +7520,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>814052</v>
+        <v>813998</v>
       </c>
       <c r="R72" t="n">
-        <v>7355644</v>
+        <v>7355850</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7570,22 +7570,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125401319</v>
+        <v>125401299</v>
       </c>
       <c r="B73" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7617,13 +7617,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>813998</v>
+        <v>814052</v>
       </c>
       <c r="R73" t="n">
-        <v>7355850</v>
+        <v>7355644</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7667,12 +7667,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7682,7 +7682,7 @@
         <v>125392501</v>
       </c>
       <c r="B74" t="n">
-        <v>91845</v>
+        <v>91849</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>125393607</v>
       </c>
       <c r="B75" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7873,32 +7873,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125392494</v>
+        <v>125401296</v>
       </c>
       <c r="B76" t="n">
-        <v>90265</v>
+        <v>92518</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7908,10 +7908,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>814004</v>
+        <v>813777</v>
       </c>
       <c r="R76" t="n">
-        <v>7355434</v>
+        <v>7355862</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7946,6 +7946,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Häxring</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -7958,44 +7963,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125401296</v>
+        <v>125392494</v>
       </c>
       <c r="B77" t="n">
-        <v>92509</v>
+        <v>90266</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8005,10 +8010,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>813777</v>
+        <v>814004</v>
       </c>
       <c r="R77" t="n">
-        <v>7355862</v>
+        <v>7355434</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8043,11 +8048,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Häxring</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8060,44 +8060,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125392267</v>
+        <v>125392506</v>
       </c>
       <c r="B78" t="n">
-        <v>90265</v>
+        <v>92518</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>814049</v>
+        <v>813996</v>
       </c>
       <c r="R78" t="n">
-        <v>7355602</v>
+        <v>7355461</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8157,44 +8157,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125393623</v>
+        <v>125392505</v>
       </c>
       <c r="B79" t="n">
-        <v>78634</v>
+        <v>92518</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8204,10 +8204,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>814062</v>
+        <v>813992</v>
       </c>
       <c r="R79" t="n">
-        <v>7355547</v>
+        <v>7355418</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8254,44 +8254,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125392506</v>
+        <v>125392267</v>
       </c>
       <c r="B80" t="n">
-        <v>92509</v>
+        <v>90266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8301,13 +8301,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>813996</v>
+        <v>814049</v>
       </c>
       <c r="R80" t="n">
-        <v>7355461</v>
+        <v>7355602</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8351,44 +8351,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125392505</v>
+        <v>125393623</v>
       </c>
       <c r="B81" t="n">
-        <v>92509</v>
+        <v>78635</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8398,10 +8398,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>813992</v>
+        <v>814062</v>
       </c>
       <c r="R81" t="n">
-        <v>7355418</v>
+        <v>7355547</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8448,12 +8448,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8557,32 +8557,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125393621</v>
+        <v>125401323</v>
       </c>
       <c r="B83" t="n">
-        <v>78725</v>
+        <v>92518</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8592,13 +8592,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>813934</v>
+        <v>813969</v>
       </c>
       <c r="R83" t="n">
-        <v>7355844</v>
+        <v>7355700</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8642,44 +8642,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125401323</v>
+        <v>125393621</v>
       </c>
       <c r="B84" t="n">
-        <v>92509</v>
+        <v>78726</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8689,13 +8689,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>813969</v>
+        <v>813934</v>
       </c>
       <c r="R84" t="n">
-        <v>7355700</v>
+        <v>7355844</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8739,12 +8739,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -8754,7 +8754,7 @@
         <v>125433171</v>
       </c>
       <c r="B85" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>125417991</v>
       </c>
       <c r="B87" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>125433174</v>
       </c>
       <c r="B88" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>125433172</v>
       </c>
       <c r="B89" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>125433173</v>
       </c>
       <c r="B91" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>125433170</v>
       </c>
       <c r="B92" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>125395032</v>
       </c>
       <c r="B94" t="n">
-        <v>91149</v>
+        <v>91150</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>125395033</v>
       </c>
       <c r="B95" t="n">
-        <v>91485</v>
+        <v>91489</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125401321</v>
+        <v>125393605</v>
       </c>
       <c r="B2" t="n">
-        <v>92518</v>
+        <v>79586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>813851</v>
+        <v>813983</v>
       </c>
       <c r="R2" t="n">
-        <v>7355951</v>
+        <v>7355808</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125393605</v>
+        <v>125393625</v>
       </c>
       <c r="B3" t="n">
-        <v>79586</v>
+        <v>77917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>813983</v>
+        <v>813993</v>
       </c>
       <c r="R3" t="n">
-        <v>7355808</v>
+        <v>7355850</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125393625</v>
+        <v>125401321</v>
       </c>
       <c r="B4" t="n">
-        <v>77917</v>
+        <v>92518</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>813993</v>
+        <v>813851</v>
       </c>
       <c r="R4" t="n">
-        <v>7355850</v>
+        <v>7355951</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125403784</v>
+        <v>125401325</v>
       </c>
       <c r="B31" t="n">
-        <v>92518</v>
+        <v>78374</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>813985</v>
+        <v>814093</v>
       </c>
       <c r="R31" t="n">
-        <v>7355756</v>
+        <v>7355602</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3573,44 +3573,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125401325</v>
+        <v>125403784</v>
       </c>
       <c r="B32" t="n">
-        <v>78374</v>
+        <v>92518</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>814093</v>
+        <v>813985</v>
       </c>
       <c r="R32" t="n">
-        <v>7355602</v>
+        <v>7355756</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3670,12 +3670,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -5045,32 +5045,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125393627</v>
+        <v>125401313</v>
       </c>
       <c r="B47" t="n">
-        <v>78374</v>
+        <v>56843</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5080,13 +5080,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>813993</v>
+        <v>813998</v>
       </c>
       <c r="R47" t="n">
-        <v>7355850</v>
+        <v>7355672</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5116,6 +5116,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5130,22 +5135,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125392499</v>
+        <v>125393627</v>
       </c>
       <c r="B48" t="n">
-        <v>92710</v>
+        <v>78374</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5153,21 +5158,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5177,10 +5182,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>814055</v>
+        <v>813993</v>
       </c>
       <c r="R48" t="n">
-        <v>7355488</v>
+        <v>7355850</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5215,11 +5220,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5232,44 +5232,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125394416</v>
+        <v>125392499</v>
       </c>
       <c r="B49" t="n">
-        <v>56843</v>
+        <v>92710</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>814013</v>
+        <v>814055</v>
       </c>
       <c r="R49" t="n">
-        <v>7355681</v>
+        <v>7355488</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5334,44 +5334,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125393619</v>
+        <v>125394416</v>
       </c>
       <c r="B50" t="n">
-        <v>78727</v>
+        <v>56843</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>814069</v>
+        <v>814013</v>
       </c>
       <c r="R50" t="n">
-        <v>7355541</v>
+        <v>7355681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5419,6 +5419,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5431,44 +5436,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125401313</v>
+        <v>125393619</v>
       </c>
       <c r="B51" t="n">
-        <v>56843</v>
+        <v>78727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5478,13 +5483,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>813998</v>
+        <v>814069</v>
       </c>
       <c r="R51" t="n">
-        <v>7355672</v>
+        <v>7355541</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5514,11 +5519,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5533,22 +5533,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125393606</v>
+        <v>125392592</v>
       </c>
       <c r="B52" t="n">
-        <v>79586</v>
+        <v>78727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5556,21 +5556,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>813976</v>
+        <v>813924</v>
       </c>
       <c r="R52" t="n">
-        <v>7355749</v>
+        <v>7355940</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5630,44 +5630,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125392498</v>
+        <v>125393606</v>
       </c>
       <c r="B53" t="n">
-        <v>78992</v>
+        <v>79586</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>814002</v>
+        <v>813976</v>
       </c>
       <c r="R53" t="n">
-        <v>7355412</v>
+        <v>7355749</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5727,44 +5727,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125393622</v>
+        <v>125392498</v>
       </c>
       <c r="B54" t="n">
-        <v>78726</v>
+        <v>78992</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>814058</v>
+        <v>814002</v>
       </c>
       <c r="R54" t="n">
-        <v>7355641</v>
+        <v>7355412</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5824,44 +5824,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125392502</v>
+        <v>125393622</v>
       </c>
       <c r="B55" t="n">
-        <v>91489</v>
+        <v>78726</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>813982</v>
+        <v>814058</v>
       </c>
       <c r="R55" t="n">
-        <v>7355407</v>
+        <v>7355641</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5921,44 +5921,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125392592</v>
+        <v>125392502</v>
       </c>
       <c r="B56" t="n">
-        <v>78727</v>
+        <v>91489</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5968,13 +5968,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>813924</v>
+        <v>813982</v>
       </c>
       <c r="R56" t="n">
-        <v>7355940</v>
+        <v>7355407</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6018,12 +6018,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6127,10 +6127,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125393615</v>
+        <v>125392508</v>
       </c>
       <c r="B58" t="n">
-        <v>78727</v>
+        <v>77917</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6138,21 +6138,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>814053</v>
+        <v>814001</v>
       </c>
       <c r="R58" t="n">
-        <v>7355646</v>
+        <v>7355442</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6212,44 +6212,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125392508</v>
+        <v>125393613</v>
       </c>
       <c r="B59" t="n">
-        <v>77917</v>
+        <v>78992</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6487</v>
+        <v>6434</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>814001</v>
+        <v>813953</v>
       </c>
       <c r="R59" t="n">
-        <v>7355442</v>
+        <v>7355711</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6309,44 +6309,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125393613</v>
+        <v>125393602</v>
       </c>
       <c r="B60" t="n">
-        <v>78992</v>
+        <v>79586</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>813953</v>
+        <v>814085</v>
       </c>
       <c r="R60" t="n">
-        <v>7355711</v>
+        <v>7355609</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6418,32 +6418,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125393602</v>
+        <v>125392507</v>
       </c>
       <c r="B61" t="n">
-        <v>79586</v>
+        <v>92518</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>814085</v>
+        <v>814049</v>
       </c>
       <c r="R61" t="n">
-        <v>7355609</v>
+        <v>7355489</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6503,44 +6503,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125392507</v>
+        <v>125392274</v>
       </c>
       <c r="B62" t="n">
-        <v>92518</v>
+        <v>78968</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6550,13 +6550,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>814049</v>
+        <v>814062</v>
       </c>
       <c r="R62" t="n">
-        <v>7355489</v>
+        <v>7355640</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6600,22 +6600,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125392274</v>
+        <v>125393615</v>
       </c>
       <c r="B63" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6623,21 +6623,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6647,13 +6647,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>814062</v>
+        <v>814053</v>
       </c>
       <c r="R63" t="n">
-        <v>7355640</v>
+        <v>7355646</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6697,44 +6697,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125403783</v>
+        <v>125401311</v>
       </c>
       <c r="B64" t="n">
-        <v>92518</v>
+        <v>79586</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6744,10 +6744,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>813951</v>
+        <v>813899</v>
       </c>
       <c r="R64" t="n">
-        <v>7355737</v>
+        <v>7355971</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6794,44 +6794,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125401297</v>
+        <v>125401312</v>
       </c>
       <c r="B65" t="n">
-        <v>92518</v>
+        <v>79586</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6841,13 +6841,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>813885</v>
+        <v>813943</v>
       </c>
       <c r="R65" t="n">
-        <v>7355896</v>
+        <v>7355850</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6891,44 +6891,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125401311</v>
+        <v>125403783</v>
       </c>
       <c r="B66" t="n">
-        <v>79586</v>
+        <v>92518</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>813899</v>
+        <v>813951</v>
       </c>
       <c r="R66" t="n">
-        <v>7355971</v>
+        <v>7355737</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6988,44 +6988,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125401312</v>
+        <v>125401297</v>
       </c>
       <c r="B67" t="n">
-        <v>79586</v>
+        <v>92518</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>813943</v>
+        <v>813885</v>
       </c>
       <c r="R67" t="n">
-        <v>7355850</v>
+        <v>7355896</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7085,22 +7085,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125393620</v>
+        <v>125392497</v>
       </c>
       <c r="B68" t="n">
-        <v>80943</v>
+        <v>92510</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7108,21 +7108,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1049</v>
+        <v>4361</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>813875</v>
+        <v>814027</v>
       </c>
       <c r="R68" t="n">
-        <v>7355877</v>
+        <v>7355486</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7182,44 +7182,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125392497</v>
+        <v>125394419</v>
       </c>
       <c r="B69" t="n">
-        <v>92510</v>
+        <v>92518</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>814027</v>
+        <v>813962</v>
       </c>
       <c r="R69" t="n">
-        <v>7355486</v>
+        <v>7355721</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7279,44 +7279,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125394419</v>
+        <v>125393603</v>
       </c>
       <c r="B70" t="n">
-        <v>92518</v>
+        <v>79586</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>813962</v>
+        <v>813848</v>
       </c>
       <c r="R70" t="n">
-        <v>7355721</v>
+        <v>7355853</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7376,44 +7376,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125393603</v>
+        <v>125401319</v>
       </c>
       <c r="B71" t="n">
-        <v>79586</v>
+        <v>92518</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7423,13 +7423,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>813848</v>
+        <v>813998</v>
       </c>
       <c r="R71" t="n">
-        <v>7355853</v>
+        <v>7355850</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7473,19 +7473,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125401319</v>
+        <v>125401299</v>
       </c>
       <c r="B72" t="n">
         <v>92518</v>
@@ -7520,13 +7520,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>813998</v>
+        <v>814052</v>
       </c>
       <c r="R72" t="n">
-        <v>7355850</v>
+        <v>7355644</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7570,44 +7570,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125401299</v>
+        <v>125393620</v>
       </c>
       <c r="B73" t="n">
-        <v>92518</v>
+        <v>80943</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>814052</v>
+        <v>813875</v>
       </c>
       <c r="R73" t="n">
-        <v>7355644</v>
+        <v>7355877</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7667,12 +7667,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125393605</v>
       </c>
       <c r="B2" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125393625</v>
       </c>
       <c r="B3" t="n">
-        <v>77917</v>
+        <v>77921</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125401321</v>
       </c>
       <c r="B4" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125401317</v>
       </c>
       <c r="B5" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125393616</v>
       </c>
       <c r="B6" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125392271</v>
       </c>
       <c r="B7" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125401315</v>
       </c>
       <c r="B8" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125401288</v>
       </c>
       <c r="B9" t="n">
-        <v>91150</v>
+        <v>91154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125401289</v>
       </c>
       <c r="B10" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125393624</v>
       </c>
       <c r="B11" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125392591</v>
       </c>
       <c r="B12" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125393626</v>
       </c>
       <c r="B13" t="n">
-        <v>78374</v>
+        <v>78378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>125393608</v>
       </c>
       <c r="B14" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>125393628</v>
       </c>
       <c r="B15" t="n">
-        <v>78374</v>
+        <v>78378</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>125393611</v>
       </c>
       <c r="B16" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>125392594</v>
       </c>
       <c r="B17" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>125392504</v>
       </c>
       <c r="B18" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>125392275</v>
       </c>
       <c r="B19" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>125393618</v>
       </c>
       <c r="B20" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>125403785</v>
       </c>
       <c r="B21" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>125401301</v>
       </c>
       <c r="B22" t="n">
-        <v>92512</v>
+        <v>92516</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125392495</v>
+        <v>125392272</v>
       </c>
       <c r="B23" t="n">
-        <v>56843</v>
+        <v>91393</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>814057</v>
+        <v>814011</v>
       </c>
       <c r="R23" t="n">
-        <v>7355446</v>
+        <v>7355730</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2797,12 +2797,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2812,7 +2812,7 @@
         <v>125394417</v>
       </c>
       <c r="B24" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2906,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125392272</v>
+        <v>125392495</v>
       </c>
       <c r="B25" t="n">
-        <v>91389</v>
+        <v>56843</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>814011</v>
+        <v>814057</v>
       </c>
       <c r="R25" t="n">
-        <v>7355730</v>
+        <v>7355446</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2991,12 +2991,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3006,7 +3006,7 @@
         <v>125393610</v>
       </c>
       <c r="B26" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>125393617</v>
       </c>
       <c r="B27" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>125401310</v>
       </c>
       <c r="B28" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125392595</v>
+        <v>125401325</v>
       </c>
       <c r="B29" t="n">
-        <v>92518</v>
+        <v>78378</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>813850</v>
+        <v>814093</v>
       </c>
       <c r="R29" t="n">
-        <v>7355937</v>
+        <v>7355602</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3379,22 +3379,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125392596</v>
+        <v>125403784</v>
       </c>
       <c r="B30" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>813911</v>
+        <v>813985</v>
       </c>
       <c r="R30" t="n">
-        <v>7355874</v>
+        <v>7355756</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3476,44 +3476,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125401325</v>
+        <v>125392595</v>
       </c>
       <c r="B31" t="n">
-        <v>78374</v>
+        <v>92522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>814093</v>
+        <v>813850</v>
       </c>
       <c r="R31" t="n">
-        <v>7355602</v>
+        <v>7355937</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3573,22 +3573,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125403784</v>
+        <v>125392596</v>
       </c>
       <c r="B32" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>813985</v>
+        <v>813911</v>
       </c>
       <c r="R32" t="n">
-        <v>7355756</v>
+        <v>7355874</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3670,44 +3670,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125392597</v>
+        <v>125401303</v>
       </c>
       <c r="B33" t="n">
-        <v>92518</v>
+        <v>78378</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,13 +3717,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>814123</v>
+        <v>813955</v>
       </c>
       <c r="R33" t="n">
-        <v>7355495</v>
+        <v>7355863</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3767,44 +3767,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125392268</v>
+        <v>125401292</v>
       </c>
       <c r="B34" t="n">
-        <v>92710</v>
+        <v>56843</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,13 +3814,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>814049</v>
+        <v>813980</v>
       </c>
       <c r="R34" t="n">
-        <v>7355786</v>
+        <v>7355837</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3850,6 +3850,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3864,22 +3869,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125401292</v>
+        <v>125401322</v>
       </c>
       <c r="B35" t="n">
-        <v>56843</v>
+        <v>92522</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3887,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,13 +3916,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>813980</v>
+        <v>813963</v>
       </c>
       <c r="R35" t="n">
-        <v>7355837</v>
+        <v>7355778</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3947,11 +3952,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3966,22 +3966,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125401322</v>
+        <v>125392597</v>
       </c>
       <c r="B36" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>813963</v>
+        <v>814123</v>
       </c>
       <c r="R36" t="n">
-        <v>7355778</v>
+        <v>7355495</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4063,22 +4063,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125401303</v>
+        <v>125392268</v>
       </c>
       <c r="B37" t="n">
-        <v>78374</v>
+        <v>92714</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4086,21 +4086,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>813955</v>
+        <v>814049</v>
       </c>
       <c r="R37" t="n">
-        <v>7355863</v>
+        <v>7355786</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4160,12 +4160,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4175,7 +4175,7 @@
         <v>125401318</v>
       </c>
       <c r="B38" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>125393614</v>
       </c>
       <c r="B39" t="n">
-        <v>78992</v>
+        <v>78996</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>125392590</v>
       </c>
       <c r="B40" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>125393609</v>
       </c>
       <c r="B41" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>125394420</v>
       </c>
       <c r="B42" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>125392503</v>
       </c>
       <c r="B43" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4754,10 +4754,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125401324</v>
+        <v>125393629</v>
       </c>
       <c r="B44" t="n">
-        <v>92512</v>
+        <v>78378</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4765,21 +4765,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4789,13 +4789,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>813960</v>
+        <v>814063</v>
       </c>
       <c r="R44" t="n">
-        <v>7355731</v>
+        <v>7355649</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4839,44 +4839,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125401298</v>
+        <v>125401324</v>
       </c>
       <c r="B45" t="n">
-        <v>92518</v>
+        <v>92516</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4886,13 +4886,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>813922</v>
+        <v>813960</v>
       </c>
       <c r="R45" t="n">
-        <v>7355853</v>
+        <v>7355731</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4936,44 +4936,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125393629</v>
+        <v>125401298</v>
       </c>
       <c r="B46" t="n">
-        <v>78374</v>
+        <v>92522</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>814063</v>
+        <v>813922</v>
       </c>
       <c r="R46" t="n">
-        <v>7355649</v>
+        <v>7355853</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5033,12 +5033,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5147,10 +5147,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125393627</v>
+        <v>125392499</v>
       </c>
       <c r="B48" t="n">
-        <v>78374</v>
+        <v>92714</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5158,21 +5158,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>813993</v>
+        <v>814055</v>
       </c>
       <c r="R48" t="n">
-        <v>7355850</v>
+        <v>7355488</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5220,6 +5220,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5232,22 +5237,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125392499</v>
+        <v>125393627</v>
       </c>
       <c r="B49" t="n">
-        <v>92710</v>
+        <v>78378</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5255,21 +5260,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5279,10 +5284,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>814055</v>
+        <v>813993</v>
       </c>
       <c r="R49" t="n">
-        <v>7355488</v>
+        <v>7355850</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5317,11 +5322,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5334,44 +5334,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125394416</v>
+        <v>125393619</v>
       </c>
       <c r="B50" t="n">
-        <v>56843</v>
+        <v>78731</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>814013</v>
+        <v>814069</v>
       </c>
       <c r="R50" t="n">
-        <v>7355681</v>
+        <v>7355541</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5419,11 +5419,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5436,44 +5431,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125393619</v>
+        <v>125394416</v>
       </c>
       <c r="B51" t="n">
-        <v>78727</v>
+        <v>56843</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5483,10 +5478,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>814069</v>
+        <v>814013</v>
       </c>
       <c r="R51" t="n">
-        <v>7355541</v>
+        <v>7355681</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5521,6 +5516,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5533,22 +5533,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125392592</v>
+        <v>125401314</v>
       </c>
       <c r="B52" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5580,10 +5580,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>813924</v>
+        <v>813899</v>
       </c>
       <c r="R52" t="n">
-        <v>7355940</v>
+        <v>7355975</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5630,44 +5630,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125393606</v>
+        <v>125392502</v>
       </c>
       <c r="B53" t="n">
-        <v>79586</v>
+        <v>91493</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>813976</v>
+        <v>813982</v>
       </c>
       <c r="R53" t="n">
-        <v>7355749</v>
+        <v>7355407</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5727,44 +5727,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125392498</v>
+        <v>125393606</v>
       </c>
       <c r="B54" t="n">
-        <v>78992</v>
+        <v>79590</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>814002</v>
+        <v>813976</v>
       </c>
       <c r="R54" t="n">
-        <v>7355412</v>
+        <v>7355749</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5824,44 +5824,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125393622</v>
+        <v>125392498</v>
       </c>
       <c r="B55" t="n">
-        <v>78726</v>
+        <v>78996</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>814058</v>
+        <v>814002</v>
       </c>
       <c r="R55" t="n">
-        <v>7355641</v>
+        <v>7355412</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5921,44 +5921,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125392502</v>
+        <v>125393622</v>
       </c>
       <c r="B56" t="n">
-        <v>91489</v>
+        <v>78730</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>813982</v>
+        <v>814058</v>
       </c>
       <c r="R56" t="n">
-        <v>7355407</v>
+        <v>7355641</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6018,22 +6018,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125401314</v>
+        <v>125392592</v>
       </c>
       <c r="B57" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6065,10 +6065,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>813899</v>
+        <v>813924</v>
       </c>
       <c r="R57" t="n">
-        <v>7355975</v>
+        <v>7355940</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6115,22 +6115,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125392508</v>
+        <v>125393615</v>
       </c>
       <c r="B58" t="n">
-        <v>77917</v>
+        <v>78731</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6138,21 +6138,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>814001</v>
+        <v>814053</v>
       </c>
       <c r="R58" t="n">
-        <v>7355442</v>
+        <v>7355646</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6212,22 +6212,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125393613</v>
+        <v>125392507</v>
       </c>
       <c r="B59" t="n">
-        <v>78992</v>
+        <v>92522</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6235,21 +6235,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>813953</v>
+        <v>814049</v>
       </c>
       <c r="R59" t="n">
-        <v>7355711</v>
+        <v>7355489</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6309,44 +6309,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125393602</v>
+        <v>125393613</v>
       </c>
       <c r="B60" t="n">
-        <v>79586</v>
+        <v>78996</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>814085</v>
+        <v>813953</v>
       </c>
       <c r="R60" t="n">
-        <v>7355609</v>
+        <v>7355711</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6418,32 +6418,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125392507</v>
+        <v>125393602</v>
       </c>
       <c r="B61" t="n">
-        <v>92518</v>
+        <v>79590</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>814049</v>
+        <v>814085</v>
       </c>
       <c r="R61" t="n">
-        <v>7355489</v>
+        <v>7355609</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6503,12 +6503,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
         <v>125392274</v>
       </c>
       <c r="B62" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6612,10 +6612,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125393615</v>
+        <v>125392508</v>
       </c>
       <c r="B63" t="n">
-        <v>78727</v>
+        <v>77921</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6623,21 +6623,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6647,10 +6647,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>814053</v>
+        <v>814001</v>
       </c>
       <c r="R63" t="n">
-        <v>7355646</v>
+        <v>7355442</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6697,12 +6697,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -6712,7 +6712,7 @@
         <v>125401311</v>
       </c>
       <c r="B64" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>125401312</v>
       </c>
       <c r="B65" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>125403783</v>
       </c>
       <c r="B66" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>125401297</v>
       </c>
       <c r="B67" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7097,10 +7097,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125392497</v>
+        <v>125393620</v>
       </c>
       <c r="B68" t="n">
-        <v>92510</v>
+        <v>80947</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7108,21 +7108,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4361</v>
+        <v>1049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>814027</v>
+        <v>813875</v>
       </c>
       <c r="R68" t="n">
-        <v>7355486</v>
+        <v>7355877</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7182,44 +7182,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125394419</v>
+        <v>125392497</v>
       </c>
       <c r="B69" t="n">
-        <v>92518</v>
+        <v>92514</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>813962</v>
+        <v>814027</v>
       </c>
       <c r="R69" t="n">
-        <v>7355721</v>
+        <v>7355486</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7279,44 +7279,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125393603</v>
+        <v>125394419</v>
       </c>
       <c r="B70" t="n">
-        <v>79586</v>
+        <v>92522</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>813848</v>
+        <v>813962</v>
       </c>
       <c r="R70" t="n">
-        <v>7355853</v>
+        <v>7355721</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7376,44 +7376,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125401319</v>
+        <v>125393603</v>
       </c>
       <c r="B71" t="n">
-        <v>92518</v>
+        <v>79590</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7423,13 +7423,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>813998</v>
+        <v>813848</v>
       </c>
       <c r="R71" t="n">
-        <v>7355850</v>
+        <v>7355853</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7473,22 +7473,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125401299</v>
+        <v>125401319</v>
       </c>
       <c r="B72" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7520,13 +7520,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>814052</v>
+        <v>813998</v>
       </c>
       <c r="R72" t="n">
-        <v>7355644</v>
+        <v>7355850</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7570,44 +7570,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125393620</v>
+        <v>125401299</v>
       </c>
       <c r="B73" t="n">
-        <v>80943</v>
+        <v>92522</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>813875</v>
+        <v>814052</v>
       </c>
       <c r="R73" t="n">
-        <v>7355877</v>
+        <v>7355644</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7667,22 +7667,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125392501</v>
+        <v>125392494</v>
       </c>
       <c r="B74" t="n">
-        <v>91849</v>
+        <v>90270</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7690,21 +7690,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5454</v>
+        <v>1962</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>814052</v>
+        <v>814004</v>
       </c>
       <c r="R74" t="n">
-        <v>7355484</v>
+        <v>7355434</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7776,10 +7776,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125393607</v>
+        <v>125392501</v>
       </c>
       <c r="B75" t="n">
-        <v>79586</v>
+        <v>91853</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7787,21 +7787,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>5454</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>813971</v>
+        <v>814052</v>
       </c>
       <c r="R75" t="n">
-        <v>7355703</v>
+        <v>7355484</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7861,44 +7861,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125401296</v>
+        <v>125393607</v>
       </c>
       <c r="B76" t="n">
-        <v>92518</v>
+        <v>79590</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7908,10 +7908,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>813777</v>
+        <v>813971</v>
       </c>
       <c r="R76" t="n">
-        <v>7355862</v>
+        <v>7355703</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7946,11 +7946,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Häxring</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -7963,44 +7958,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125392494</v>
+        <v>125401296</v>
       </c>
       <c r="B77" t="n">
-        <v>90266</v>
+        <v>92522</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8010,10 +8005,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>814004</v>
+        <v>813777</v>
       </c>
       <c r="R77" t="n">
-        <v>7355434</v>
+        <v>7355862</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8048,6 +8043,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Häxring</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8060,12 +8060,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8075,7 +8075,7 @@
         <v>125392506</v>
       </c>
       <c r="B78" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>125392505</v>
       </c>
       <c r="B79" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8266,32 +8266,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125392267</v>
+        <v>125392496</v>
       </c>
       <c r="B80" t="n">
-        <v>90266</v>
+        <v>56843</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8301,13 +8301,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>814049</v>
+        <v>814003</v>
       </c>
       <c r="R80" t="n">
-        <v>7355602</v>
+        <v>7355454</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8351,22 +8351,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125393623</v>
+        <v>125392267</v>
       </c>
       <c r="B81" t="n">
-        <v>78635</v>
+        <v>90270</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8374,21 +8374,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8398,13 +8398,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>814062</v>
+        <v>814049</v>
       </c>
       <c r="R81" t="n">
-        <v>7355547</v>
+        <v>7355602</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8448,44 +8448,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125392496</v>
+        <v>125393623</v>
       </c>
       <c r="B82" t="n">
-        <v>56843</v>
+        <v>78639</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8495,10 +8495,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>814003</v>
+        <v>814062</v>
       </c>
       <c r="R82" t="n">
-        <v>7355454</v>
+        <v>7355547</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8545,44 +8545,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125401323</v>
+        <v>125393621</v>
       </c>
       <c r="B83" t="n">
-        <v>92518</v>
+        <v>78730</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8592,13 +8592,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>813969</v>
+        <v>813934</v>
       </c>
       <c r="R83" t="n">
-        <v>7355700</v>
+        <v>7355844</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8642,44 +8642,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125393621</v>
+        <v>125401323</v>
       </c>
       <c r="B84" t="n">
-        <v>78726</v>
+        <v>92522</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8689,13 +8689,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>813934</v>
+        <v>813969</v>
       </c>
       <c r="R84" t="n">
-        <v>7355844</v>
+        <v>7355700</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8739,12 +8739,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -8754,7 +8754,7 @@
         <v>125433171</v>
       </c>
       <c r="B85" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>125417991</v>
       </c>
       <c r="B87" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>125433174</v>
       </c>
       <c r="B88" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>125433172</v>
       </c>
       <c r="B89" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         <v>125433173</v>
       </c>
       <c r="B91" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>125433170</v>
       </c>
       <c r="B92" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>125395032</v>
       </c>
       <c r="B94" t="n">
-        <v>91150</v>
+        <v>91154</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>125395033</v>
       </c>
       <c r="B95" t="n">
-        <v>91489</v>
+        <v>91493</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125393605</v>
+        <v>125401321</v>
       </c>
       <c r="B2" t="n">
-        <v>79590</v>
+        <v>92522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>813983</v>
+        <v>813851</v>
       </c>
       <c r="R2" t="n">
-        <v>7355808</v>
+        <v>7355951</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125401321</v>
+        <v>125393605</v>
       </c>
       <c r="B4" t="n">
-        <v>92522</v>
+        <v>79590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>813851</v>
+        <v>813983</v>
       </c>
       <c r="R4" t="n">
-        <v>7355951</v>
+        <v>7355808</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125393624</v>
+        <v>125392591</v>
       </c>
       <c r="B11" t="n">
-        <v>92522</v>
+        <v>79590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>813879</v>
+        <v>813924</v>
       </c>
       <c r="R11" t="n">
-        <v>7355876</v>
+        <v>7355940</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125392591</v>
+        <v>125393626</v>
       </c>
       <c r="B12" t="n">
-        <v>79590</v>
+        <v>78378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,13 +1680,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>813924</v>
+        <v>813874</v>
       </c>
       <c r="R12" t="n">
-        <v>7355940</v>
+        <v>7355877</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1730,22 +1730,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125393626</v>
+        <v>125393608</v>
       </c>
       <c r="B13" t="n">
-        <v>78378</v>
+        <v>79590</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>813874</v>
+        <v>814054</v>
       </c>
       <c r="R13" t="n">
-        <v>7355877</v>
+        <v>7355641</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125393608</v>
+        <v>125393628</v>
       </c>
       <c r="B14" t="n">
-        <v>79590</v>
+        <v>78378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>814054</v>
+        <v>813979</v>
       </c>
       <c r="R14" t="n">
-        <v>7355641</v>
+        <v>7355768</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125393628</v>
+        <v>125393611</v>
       </c>
       <c r="B15" t="n">
-        <v>78378</v>
+        <v>79561</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>813979</v>
+        <v>814063</v>
       </c>
       <c r="R15" t="n">
-        <v>7355768</v>
+        <v>7355649</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125393611</v>
+        <v>125393624</v>
       </c>
       <c r="B16" t="n">
-        <v>79561</v>
+        <v>92522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>814063</v>
+        <v>813879</v>
       </c>
       <c r="R16" t="n">
-        <v>7355649</v>
+        <v>7355876</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125392594</v>
+        <v>125393618</v>
       </c>
       <c r="B17" t="n">
-        <v>92522</v>
+        <v>78731</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>814057</v>
+        <v>813976</v>
       </c>
       <c r="R17" t="n">
-        <v>7355682</v>
+        <v>7355749</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2215,19 +2215,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125392504</v>
+        <v>125392594</v>
       </c>
       <c r="B18" t="n">
         <v>92522</v>
@@ -2262,13 +2262,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>813963</v>
+        <v>814057</v>
       </c>
       <c r="R18" t="n">
-        <v>7355408</v>
+        <v>7355682</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2312,19 +2312,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125392275</v>
+        <v>125392504</v>
       </c>
       <c r="B19" t="n">
         <v>92522</v>
@@ -2359,13 +2359,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>814068</v>
+        <v>813963</v>
       </c>
       <c r="R19" t="n">
-        <v>7355802</v>
+        <v>7355408</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2409,44 +2409,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125393618</v>
+        <v>125392275</v>
       </c>
       <c r="B20" t="n">
-        <v>78731</v>
+        <v>92522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,13 +2456,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>813976</v>
+        <v>814068</v>
       </c>
       <c r="R20" t="n">
-        <v>7355749</v>
+        <v>7355802</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2506,12 +2506,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125392272</v>
+        <v>125393610</v>
       </c>
       <c r="B23" t="n">
-        <v>91393</v>
+        <v>79561</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>814011</v>
+        <v>813948</v>
       </c>
       <c r="R23" t="n">
-        <v>7355730</v>
+        <v>7355861</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2797,44 +2797,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125394417</v>
+        <v>125393617</v>
       </c>
       <c r="B24" t="n">
-        <v>92522</v>
+        <v>78731</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>813952</v>
+        <v>813999</v>
       </c>
       <c r="R24" t="n">
-        <v>7355835</v>
+        <v>7355845</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2894,44 +2894,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125392495</v>
+        <v>125392272</v>
       </c>
       <c r="B25" t="n">
-        <v>56843</v>
+        <v>91393</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>814057</v>
+        <v>814011</v>
       </c>
       <c r="R25" t="n">
-        <v>7355446</v>
+        <v>7355730</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2991,44 +2991,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125393610</v>
+        <v>125394417</v>
       </c>
       <c r="B26" t="n">
-        <v>79561</v>
+        <v>92522</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>813948</v>
+        <v>813952</v>
       </c>
       <c r="R26" t="n">
-        <v>7355861</v>
+        <v>7355835</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3088,44 +3088,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125393617</v>
+        <v>125392495</v>
       </c>
       <c r="B27" t="n">
-        <v>78731</v>
+        <v>56843</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>813999</v>
+        <v>814057</v>
       </c>
       <c r="R27" t="n">
-        <v>7355845</v>
+        <v>7355446</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3185,12 +3185,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125403784</v>
+        <v>125392595</v>
       </c>
       <c r="B30" t="n">
         <v>92522</v>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>813985</v>
+        <v>813850</v>
       </c>
       <c r="R30" t="n">
-        <v>7355756</v>
+        <v>7355937</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3476,19 +3476,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125392595</v>
+        <v>125392596</v>
       </c>
       <c r="B31" t="n">
         <v>92522</v>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>813850</v>
+        <v>813911</v>
       </c>
       <c r="R31" t="n">
-        <v>7355937</v>
+        <v>7355874</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125392596</v>
+        <v>125403784</v>
       </c>
       <c r="B32" t="n">
         <v>92522</v>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>813911</v>
+        <v>813985</v>
       </c>
       <c r="R32" t="n">
-        <v>7355874</v>
+        <v>7355756</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3670,12 +3670,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -5045,32 +5045,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125401313</v>
+        <v>125392499</v>
       </c>
       <c r="B47" t="n">
-        <v>56843</v>
+        <v>92714</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5080,13 +5080,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>813998</v>
+        <v>814055</v>
       </c>
       <c r="R47" t="n">
-        <v>7355672</v>
+        <v>7355488</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5135,22 +5135,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125392499</v>
+        <v>125393627</v>
       </c>
       <c r="B48" t="n">
-        <v>92714</v>
+        <v>78378</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5158,21 +5158,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>814055</v>
+        <v>813993</v>
       </c>
       <c r="R48" t="n">
-        <v>7355488</v>
+        <v>7355850</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5220,11 +5220,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5237,44 +5232,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125393627</v>
+        <v>125394416</v>
       </c>
       <c r="B49" t="n">
-        <v>78378</v>
+        <v>56843</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,10 +5279,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>813993</v>
+        <v>814013</v>
       </c>
       <c r="R49" t="n">
-        <v>7355850</v>
+        <v>7355681</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5322,6 +5317,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5334,44 +5334,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125393619</v>
+        <v>125401313</v>
       </c>
       <c r="B50" t="n">
-        <v>78731</v>
+        <v>56843</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,13 +5381,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>814069</v>
+        <v>813998</v>
       </c>
       <c r="R50" t="n">
-        <v>7355541</v>
+        <v>7355672</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5417,6 +5417,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5431,44 +5436,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125394416</v>
+        <v>125393619</v>
       </c>
       <c r="B51" t="n">
-        <v>56843</v>
+        <v>78731</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5478,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>814013</v>
+        <v>814069</v>
       </c>
       <c r="R51" t="n">
-        <v>7355681</v>
+        <v>7355541</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5516,11 +5521,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5533,12 +5533,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6127,32 +6127,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125393615</v>
+        <v>125392507</v>
       </c>
       <c r="B58" t="n">
-        <v>78731</v>
+        <v>92522</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>814053</v>
+        <v>814049</v>
       </c>
       <c r="R58" t="n">
-        <v>7355646</v>
+        <v>7355489</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6212,22 +6212,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125392507</v>
+        <v>125393613</v>
       </c>
       <c r="B59" t="n">
-        <v>92522</v>
+        <v>78996</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6235,21 +6235,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>814049</v>
+        <v>813953</v>
       </c>
       <c r="R59" t="n">
-        <v>7355489</v>
+        <v>7355711</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6309,44 +6309,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125393613</v>
+        <v>125393602</v>
       </c>
       <c r="B60" t="n">
-        <v>78996</v>
+        <v>79590</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>813953</v>
+        <v>814085</v>
       </c>
       <c r="R60" t="n">
-        <v>7355711</v>
+        <v>7355609</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6418,10 +6418,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125393602</v>
+        <v>125392274</v>
       </c>
       <c r="B61" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6429,21 +6429,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6453,13 +6453,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>814085</v>
+        <v>814062</v>
       </c>
       <c r="R61" t="n">
-        <v>7355609</v>
+        <v>7355640</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6503,22 +6503,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125392274</v>
+        <v>125392508</v>
       </c>
       <c r="B62" t="n">
-        <v>78972</v>
+        <v>77921</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6526,21 +6526,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6550,13 +6550,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>814062</v>
+        <v>814001</v>
       </c>
       <c r="R62" t="n">
-        <v>7355640</v>
+        <v>7355442</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6600,22 +6600,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125392508</v>
+        <v>125393615</v>
       </c>
       <c r="B63" t="n">
-        <v>77921</v>
+        <v>78731</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6623,21 +6623,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6647,10 +6647,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>814001</v>
+        <v>814053</v>
       </c>
       <c r="R63" t="n">
-        <v>7355442</v>
+        <v>7355646</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6697,12 +6697,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125401321</v>
+        <v>125393605</v>
       </c>
       <c r="B2" t="n">
-        <v>92522</v>
+        <v>79590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>813851</v>
+        <v>813983</v>
       </c>
       <c r="R2" t="n">
-        <v>7355951</v>
+        <v>7355808</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125393605</v>
+        <v>125401321</v>
       </c>
       <c r="B4" t="n">
-        <v>79590</v>
+        <v>92522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>813983</v>
+        <v>813851</v>
       </c>
       <c r="R4" t="n">
-        <v>7355808</v>
+        <v>7355951</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125401315</v>
+        <v>125401288</v>
       </c>
       <c r="B8" t="n">
-        <v>78731</v>
+        <v>91154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>813936</v>
+        <v>813970</v>
       </c>
       <c r="R8" t="n">
-        <v>7355848</v>
+        <v>7355705</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,44 +1342,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125401288</v>
+        <v>125401289</v>
       </c>
       <c r="B9" t="n">
-        <v>91154</v>
+        <v>91197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>813970</v>
+        <v>813966</v>
       </c>
       <c r="R9" t="n">
-        <v>7355705</v>
+        <v>7355769</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125401289</v>
+        <v>125401315</v>
       </c>
       <c r="B10" t="n">
-        <v>91197</v>
+        <v>78731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>813966</v>
+        <v>813936</v>
       </c>
       <c r="R10" t="n">
-        <v>7355769</v>
+        <v>7355848</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125392591</v>
+        <v>125393611</v>
       </c>
       <c r="B11" t="n">
-        <v>79590</v>
+        <v>79561</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>813924</v>
+        <v>814063</v>
       </c>
       <c r="R11" t="n">
-        <v>7355940</v>
+        <v>7355649</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,44 +1633,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125393626</v>
+        <v>125393624</v>
       </c>
       <c r="B12" t="n">
-        <v>78378</v>
+        <v>92522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>813874</v>
+        <v>813879</v>
       </c>
       <c r="R12" t="n">
-        <v>7355877</v>
+        <v>7355876</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125393608</v>
+        <v>125392591</v>
       </c>
       <c r="B13" t="n">
         <v>79590</v>
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>814054</v>
+        <v>813924</v>
       </c>
       <c r="R13" t="n">
-        <v>7355641</v>
+        <v>7355940</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,19 +1827,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125393628</v>
+        <v>125393626</v>
       </c>
       <c r="B14" t="n">
         <v>78378</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>813979</v>
+        <v>813874</v>
       </c>
       <c r="R14" t="n">
-        <v>7355768</v>
+        <v>7355877</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125393611</v>
+        <v>125393608</v>
       </c>
       <c r="B15" t="n">
-        <v>79561</v>
+        <v>79590</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>814063</v>
+        <v>814054</v>
       </c>
       <c r="R15" t="n">
-        <v>7355649</v>
+        <v>7355641</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125393624</v>
+        <v>125393628</v>
       </c>
       <c r="B16" t="n">
-        <v>92522</v>
+        <v>78378</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>813879</v>
+        <v>813979</v>
       </c>
       <c r="R16" t="n">
-        <v>7355876</v>
+        <v>7355768</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125393618</v>
+        <v>125392594</v>
       </c>
       <c r="B17" t="n">
-        <v>78731</v>
+        <v>92522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>813976</v>
+        <v>814057</v>
       </c>
       <c r="R17" t="n">
-        <v>7355749</v>
+        <v>7355682</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2215,19 +2215,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125392594</v>
+        <v>125392504</v>
       </c>
       <c r="B18" t="n">
         <v>92522</v>
@@ -2262,13 +2262,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>814057</v>
+        <v>813963</v>
       </c>
       <c r="R18" t="n">
-        <v>7355682</v>
+        <v>7355408</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2312,19 +2312,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125392504</v>
+        <v>125392275</v>
       </c>
       <c r="B19" t="n">
         <v>92522</v>
@@ -2359,13 +2359,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>813963</v>
+        <v>814068</v>
       </c>
       <c r="R19" t="n">
-        <v>7355408</v>
+        <v>7355802</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2409,44 +2409,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125392275</v>
+        <v>125393618</v>
       </c>
       <c r="B20" t="n">
-        <v>92522</v>
+        <v>78731</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,13 +2456,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>814068</v>
+        <v>813976</v>
       </c>
       <c r="R20" t="n">
-        <v>7355802</v>
+        <v>7355749</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2506,44 +2506,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125403785</v>
+        <v>125401301</v>
       </c>
       <c r="B21" t="n">
-        <v>92522</v>
+        <v>92516</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,13 +2553,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>814010</v>
+        <v>814046</v>
       </c>
       <c r="R21" t="n">
-        <v>7355734</v>
+        <v>7355641</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2603,44 +2603,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125401301</v>
+        <v>125403785</v>
       </c>
       <c r="B22" t="n">
-        <v>92516</v>
+        <v>92522</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,13 +2650,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>814046</v>
+        <v>814010</v>
       </c>
       <c r="R22" t="n">
-        <v>7355641</v>
+        <v>7355734</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2700,44 +2700,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125393610</v>
+        <v>125392272</v>
       </c>
       <c r="B23" t="n">
-        <v>79561</v>
+        <v>91393</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>813948</v>
+        <v>814011</v>
       </c>
       <c r="R23" t="n">
-        <v>7355861</v>
+        <v>7355730</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2797,44 +2797,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125393617</v>
+        <v>125394417</v>
       </c>
       <c r="B24" t="n">
-        <v>78731</v>
+        <v>92522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>813999</v>
+        <v>813952</v>
       </c>
       <c r="R24" t="n">
-        <v>7355845</v>
+        <v>7355835</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2894,44 +2894,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125392272</v>
+        <v>125392495</v>
       </c>
       <c r="B25" t="n">
-        <v>91393</v>
+        <v>56843</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1503</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>814011</v>
+        <v>814057</v>
       </c>
       <c r="R25" t="n">
-        <v>7355730</v>
+        <v>7355446</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2991,44 +2991,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125394417</v>
+        <v>125401310</v>
       </c>
       <c r="B26" t="n">
-        <v>92522</v>
+        <v>79590</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,13 +3038,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>813952</v>
+        <v>814093</v>
       </c>
       <c r="R26" t="n">
-        <v>7355835</v>
+        <v>7355601</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3088,44 +3088,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125392495</v>
+        <v>125393610</v>
       </c>
       <c r="B27" t="n">
-        <v>56843</v>
+        <v>79561</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>814057</v>
+        <v>813948</v>
       </c>
       <c r="R27" t="n">
-        <v>7355446</v>
+        <v>7355861</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3185,22 +3185,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125401310</v>
+        <v>125393617</v>
       </c>
       <c r="B28" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>814093</v>
+        <v>813999</v>
       </c>
       <c r="R28" t="n">
-        <v>7355601</v>
+        <v>7355845</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3282,12 +3282,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125401303</v>
+        <v>125392268</v>
       </c>
       <c r="B33" t="n">
-        <v>78378</v>
+        <v>92714</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3693,21 +3693,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,13 +3717,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>813955</v>
+        <v>814049</v>
       </c>
       <c r="R33" t="n">
-        <v>7355863</v>
+        <v>7355786</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3767,22 +3767,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125401292</v>
+        <v>125392597</v>
       </c>
       <c r="B34" t="n">
-        <v>56843</v>
+        <v>92522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3790,21 +3790,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3814,13 +3814,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>813980</v>
+        <v>814123</v>
       </c>
       <c r="R34" t="n">
-        <v>7355837</v>
+        <v>7355495</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3850,11 +3850,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3869,44 +3864,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125401322</v>
+        <v>125401303</v>
       </c>
       <c r="B35" t="n">
-        <v>92522</v>
+        <v>78378</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,13 +3911,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>813963</v>
+        <v>813955</v>
       </c>
       <c r="R35" t="n">
-        <v>7355778</v>
+        <v>7355863</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3966,19 +3961,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125392597</v>
+        <v>125401322</v>
       </c>
       <c r="B36" t="n">
         <v>92522</v>
@@ -4013,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>814123</v>
+        <v>813963</v>
       </c>
       <c r="R36" t="n">
-        <v>7355495</v>
+        <v>7355778</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4063,44 +4058,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125392268</v>
+        <v>125401292</v>
       </c>
       <c r="B37" t="n">
-        <v>92714</v>
+        <v>56843</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4110,13 +4105,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>814049</v>
+        <v>813980</v>
       </c>
       <c r="R37" t="n">
-        <v>7355786</v>
+        <v>7355837</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4146,6 +4141,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4160,12 +4160,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125393614</v>
+        <v>125394420</v>
       </c>
       <c r="B39" t="n">
-        <v>78996</v>
+        <v>92522</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4280,21 +4280,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4304,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>814021</v>
+        <v>813977</v>
       </c>
       <c r="R39" t="n">
-        <v>7355670</v>
+        <v>7355690</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4354,22 +4354,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125392590</v>
+        <v>125392503</v>
       </c>
       <c r="B40" t="n">
-        <v>91197</v>
+        <v>92522</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4377,21 +4377,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4401,13 +4401,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>813970</v>
+        <v>814058</v>
       </c>
       <c r="R40" t="n">
-        <v>7355771</v>
+        <v>7355447</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4451,44 +4451,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125393609</v>
+        <v>125393614</v>
       </c>
       <c r="B41" t="n">
-        <v>79590</v>
+        <v>78996</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>814066</v>
+        <v>814021</v>
       </c>
       <c r="R41" t="n">
-        <v>7355537</v>
+        <v>7355670</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4560,10 +4560,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125394420</v>
+        <v>125392590</v>
       </c>
       <c r="B42" t="n">
-        <v>92522</v>
+        <v>91197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4571,21 +4571,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>813977</v>
+        <v>813970</v>
       </c>
       <c r="R42" t="n">
-        <v>7355690</v>
+        <v>7355771</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4645,44 +4645,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125392503</v>
+        <v>125393609</v>
       </c>
       <c r="B43" t="n">
-        <v>92522</v>
+        <v>79590</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>814058</v>
+        <v>814066</v>
       </c>
       <c r="R43" t="n">
-        <v>7355447</v>
+        <v>7355537</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4742,22 +4742,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125393629</v>
+        <v>125401324</v>
       </c>
       <c r="B44" t="n">
-        <v>78378</v>
+        <v>92516</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4765,21 +4765,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4789,13 +4789,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>814063</v>
+        <v>813960</v>
       </c>
       <c r="R44" t="n">
-        <v>7355649</v>
+        <v>7355731</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4839,44 +4839,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125401324</v>
+        <v>125401298</v>
       </c>
       <c r="B45" t="n">
-        <v>92516</v>
+        <v>92522</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4886,13 +4886,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>813960</v>
+        <v>813922</v>
       </c>
       <c r="R45" t="n">
-        <v>7355731</v>
+        <v>7355853</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4936,44 +4936,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125401298</v>
+        <v>125393629</v>
       </c>
       <c r="B46" t="n">
-        <v>92522</v>
+        <v>78378</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>813922</v>
+        <v>814063</v>
       </c>
       <c r="R46" t="n">
-        <v>7355853</v>
+        <v>7355649</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5033,12 +5033,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5147,32 +5147,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125393627</v>
+        <v>125394416</v>
       </c>
       <c r="B48" t="n">
-        <v>78378</v>
+        <v>56843</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>813993</v>
+        <v>814013</v>
       </c>
       <c r="R48" t="n">
-        <v>7355850</v>
+        <v>7355681</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5220,6 +5220,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5232,19 +5237,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125394416</v>
+        <v>125401313</v>
       </c>
       <c r="B49" t="n">
         <v>56843</v>
@@ -5279,13 +5284,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>814013</v>
+        <v>813998</v>
       </c>
       <c r="R49" t="n">
-        <v>7355681</v>
+        <v>7355672</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5334,44 +5339,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125401313</v>
+        <v>125393619</v>
       </c>
       <c r="B50" t="n">
-        <v>56843</v>
+        <v>78731</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5381,13 +5386,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>813998</v>
+        <v>814069</v>
       </c>
       <c r="R50" t="n">
-        <v>7355672</v>
+        <v>7355541</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5417,11 +5422,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5436,22 +5436,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125393619</v>
+        <v>125393627</v>
       </c>
       <c r="B51" t="n">
-        <v>78731</v>
+        <v>78378</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>814069</v>
+        <v>813993</v>
       </c>
       <c r="R51" t="n">
-        <v>7355541</v>
+        <v>7355850</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5642,32 +5642,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125392502</v>
+        <v>125393606</v>
       </c>
       <c r="B53" t="n">
-        <v>91493</v>
+        <v>79590</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>813982</v>
+        <v>813976</v>
       </c>
       <c r="R53" t="n">
-        <v>7355407</v>
+        <v>7355749</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5727,44 +5727,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125393606</v>
+        <v>125392498</v>
       </c>
       <c r="B54" t="n">
-        <v>79590</v>
+        <v>78996</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>813976</v>
+        <v>814002</v>
       </c>
       <c r="R54" t="n">
-        <v>7355749</v>
+        <v>7355412</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5824,44 +5824,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125392498</v>
+        <v>125393622</v>
       </c>
       <c r="B55" t="n">
-        <v>78996</v>
+        <v>78730</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>814002</v>
+        <v>814058</v>
       </c>
       <c r="R55" t="n">
-        <v>7355412</v>
+        <v>7355641</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5921,44 +5921,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125393622</v>
+        <v>125392502</v>
       </c>
       <c r="B56" t="n">
-        <v>78730</v>
+        <v>91493</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>814058</v>
+        <v>813982</v>
       </c>
       <c r="R56" t="n">
-        <v>7355641</v>
+        <v>7355407</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6018,12 +6018,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6224,32 +6224,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125393613</v>
+        <v>125392508</v>
       </c>
       <c r="B59" t="n">
-        <v>78996</v>
+        <v>77921</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6434</v>
+        <v>6487</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>813953</v>
+        <v>814001</v>
       </c>
       <c r="R59" t="n">
-        <v>7355711</v>
+        <v>7355442</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6309,44 +6309,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125393602</v>
+        <v>125393613</v>
       </c>
       <c r="B60" t="n">
-        <v>79590</v>
+        <v>78996</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>814085</v>
+        <v>813953</v>
       </c>
       <c r="R60" t="n">
-        <v>7355609</v>
+        <v>7355711</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6418,10 +6418,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125392274</v>
+        <v>125393602</v>
       </c>
       <c r="B61" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6429,21 +6429,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6453,13 +6453,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>814062</v>
+        <v>814085</v>
       </c>
       <c r="R61" t="n">
-        <v>7355640</v>
+        <v>7355609</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6503,22 +6503,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125392508</v>
+        <v>125392274</v>
       </c>
       <c r="B62" t="n">
-        <v>77921</v>
+        <v>78972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6526,21 +6526,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6550,13 +6550,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>814001</v>
+        <v>814062</v>
       </c>
       <c r="R62" t="n">
-        <v>7355442</v>
+        <v>7355640</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6600,12 +6600,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6709,7 +6709,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125401311</v>
+        <v>125401312</v>
       </c>
       <c r="B64" t="n">
         <v>79590</v>
@@ -6744,10 +6744,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>813899</v>
+        <v>813943</v>
       </c>
       <c r="R64" t="n">
-        <v>7355971</v>
+        <v>7355850</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6806,7 +6806,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125401312</v>
+        <v>125401311</v>
       </c>
       <c r="B65" t="n">
         <v>79590</v>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>813943</v>
+        <v>813899</v>
       </c>
       <c r="R65" t="n">
-        <v>7355850</v>
+        <v>7355971</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6903,7 +6903,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125403783</v>
+        <v>125401297</v>
       </c>
       <c r="B66" t="n">
         <v>92522</v>
@@ -6938,13 +6938,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>813951</v>
+        <v>813885</v>
       </c>
       <c r="R66" t="n">
-        <v>7355737</v>
+        <v>7355896</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6988,19 +6988,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125401297</v>
+        <v>125403783</v>
       </c>
       <c r="B67" t="n">
         <v>92522</v>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>813885</v>
+        <v>813951</v>
       </c>
       <c r="R67" t="n">
-        <v>7355896</v>
+        <v>7355737</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7085,22 +7085,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125393620</v>
+        <v>125392497</v>
       </c>
       <c r="B68" t="n">
-        <v>80947</v>
+        <v>92514</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7108,21 +7108,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1049</v>
+        <v>4361</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>813875</v>
+        <v>814027</v>
       </c>
       <c r="R68" t="n">
-        <v>7355877</v>
+        <v>7355486</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7182,44 +7182,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125392497</v>
+        <v>125394419</v>
       </c>
       <c r="B69" t="n">
-        <v>92514</v>
+        <v>92522</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>814027</v>
+        <v>813962</v>
       </c>
       <c r="R69" t="n">
-        <v>7355486</v>
+        <v>7355721</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7279,44 +7279,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125394419</v>
+        <v>125393603</v>
       </c>
       <c r="B70" t="n">
-        <v>92522</v>
+        <v>79590</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7326,10 +7326,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>813962</v>
+        <v>813848</v>
       </c>
       <c r="R70" t="n">
-        <v>7355721</v>
+        <v>7355853</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7376,22 +7376,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125393603</v>
+        <v>125393620</v>
       </c>
       <c r="B71" t="n">
-        <v>79590</v>
+        <v>80947</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7399,21 +7399,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7423,10 +7423,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>813848</v>
+        <v>813875</v>
       </c>
       <c r="R71" t="n">
-        <v>7355853</v>
+        <v>7355877</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7485,7 +7485,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125401319</v>
+        <v>125401299</v>
       </c>
       <c r="B72" t="n">
         <v>92522</v>
@@ -7520,13 +7520,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>813998</v>
+        <v>814052</v>
       </c>
       <c r="R72" t="n">
-        <v>7355850</v>
+        <v>7355644</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7570,19 +7570,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125401299</v>
+        <v>125401319</v>
       </c>
       <c r="B73" t="n">
         <v>92522</v>
@@ -7617,13 +7617,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>814052</v>
+        <v>813998</v>
       </c>
       <c r="R73" t="n">
-        <v>7355644</v>
+        <v>7355850</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7667,44 +7667,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125392494</v>
+        <v>125401296</v>
       </c>
       <c r="B74" t="n">
-        <v>90270</v>
+        <v>92522</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>814004</v>
+        <v>813777</v>
       </c>
       <c r="R74" t="n">
-        <v>7355434</v>
+        <v>7355862</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7752,6 +7752,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Häxring</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -7764,22 +7769,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125392501</v>
+        <v>125392494</v>
       </c>
       <c r="B75" t="n">
-        <v>91853</v>
+        <v>90270</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7787,21 +7792,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5454</v>
+        <v>1962</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7811,10 +7816,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>814052</v>
+        <v>814004</v>
       </c>
       <c r="R75" t="n">
-        <v>7355484</v>
+        <v>7355434</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7873,10 +7878,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125393607</v>
+        <v>125392501</v>
       </c>
       <c r="B76" t="n">
-        <v>79590</v>
+        <v>91853</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7884,21 +7889,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>5454</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7908,10 +7913,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>813971</v>
+        <v>814052</v>
       </c>
       <c r="R76" t="n">
-        <v>7355703</v>
+        <v>7355484</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7958,44 +7963,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125401296</v>
+        <v>125393607</v>
       </c>
       <c r="B77" t="n">
-        <v>92522</v>
+        <v>79590</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8005,10 +8010,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>813777</v>
+        <v>813971</v>
       </c>
       <c r="R77" t="n">
-        <v>7355862</v>
+        <v>7355703</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8043,11 +8048,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Häxring</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8060,12 +8060,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8266,32 +8266,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125392496</v>
+        <v>125393623</v>
       </c>
       <c r="B80" t="n">
-        <v>56843</v>
+        <v>78639</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8301,10 +8301,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>814003</v>
+        <v>814062</v>
       </c>
       <c r="R80" t="n">
-        <v>7355454</v>
+        <v>7355547</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8351,12 +8351,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8460,32 +8460,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125393623</v>
+        <v>125392496</v>
       </c>
       <c r="B82" t="n">
-        <v>78639</v>
+        <v>56843</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8495,10 +8495,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>814062</v>
+        <v>814003</v>
       </c>
       <c r="R82" t="n">
-        <v>7355547</v>
+        <v>7355454</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8545,12 +8545,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125401288</v>
+        <v>125401289</v>
       </c>
       <c r="B8" t="n">
-        <v>91154</v>
+        <v>91197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>813970</v>
+        <v>813966</v>
       </c>
       <c r="R8" t="n">
-        <v>7355705</v>
+        <v>7355769</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125401289</v>
+        <v>125401288</v>
       </c>
       <c r="B9" t="n">
-        <v>91197</v>
+        <v>91154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>813966</v>
+        <v>813970</v>
       </c>
       <c r="R9" t="n">
-        <v>7355769</v>
+        <v>7355705</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125392594</v>
+        <v>125401301</v>
       </c>
       <c r="B17" t="n">
-        <v>92522</v>
+        <v>92516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>814057</v>
+        <v>814046</v>
       </c>
       <c r="R17" t="n">
-        <v>7355682</v>
+        <v>7355641</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2215,19 +2215,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125392504</v>
+        <v>125403785</v>
       </c>
       <c r="B18" t="n">
         <v>92522</v>
@@ -2262,13 +2262,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>813963</v>
+        <v>814010</v>
       </c>
       <c r="R18" t="n">
-        <v>7355408</v>
+        <v>7355734</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2312,19 +2312,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125392275</v>
+        <v>125392594</v>
       </c>
       <c r="B19" t="n">
         <v>92522</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>814068</v>
+        <v>814057</v>
       </c>
       <c r="R19" t="n">
-        <v>7355802</v>
+        <v>7355682</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2409,44 +2409,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125393618</v>
+        <v>125392504</v>
       </c>
       <c r="B20" t="n">
-        <v>78731</v>
+        <v>92522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>813976</v>
+        <v>813963</v>
       </c>
       <c r="R20" t="n">
-        <v>7355749</v>
+        <v>7355408</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2506,44 +2506,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125401301</v>
+        <v>125392275</v>
       </c>
       <c r="B21" t="n">
-        <v>92516</v>
+        <v>92522</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,13 +2553,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>814046</v>
+        <v>814068</v>
       </c>
       <c r="R21" t="n">
-        <v>7355641</v>
+        <v>7355802</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2603,44 +2603,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125403785</v>
+        <v>125393618</v>
       </c>
       <c r="B22" t="n">
-        <v>92522</v>
+        <v>78731</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,13 +2650,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>814010</v>
+        <v>813976</v>
       </c>
       <c r="R22" t="n">
-        <v>7355734</v>
+        <v>7355749</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2700,12 +2700,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125394417</v>
+        <v>125392495</v>
       </c>
       <c r="B24" t="n">
-        <v>92522</v>
+        <v>56843</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>813952</v>
+        <v>814057</v>
       </c>
       <c r="R24" t="n">
-        <v>7355835</v>
+        <v>7355446</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2894,22 +2894,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125392495</v>
+        <v>125394417</v>
       </c>
       <c r="B25" t="n">
-        <v>56843</v>
+        <v>92522</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>814057</v>
+        <v>813952</v>
       </c>
       <c r="R25" t="n">
-        <v>7355446</v>
+        <v>7355835</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2991,22 +2991,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125401310</v>
+        <v>125393610</v>
       </c>
       <c r="B26" t="n">
-        <v>79590</v>
+        <v>79561</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,13 +3038,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>814093</v>
+        <v>813948</v>
       </c>
       <c r="R26" t="n">
-        <v>7355601</v>
+        <v>7355861</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3088,22 +3088,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125393610</v>
+        <v>125393617</v>
       </c>
       <c r="B27" t="n">
-        <v>79561</v>
+        <v>78731</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,21 +3111,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>813948</v>
+        <v>813999</v>
       </c>
       <c r="R27" t="n">
-        <v>7355861</v>
+        <v>7355845</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125393617</v>
+        <v>125401310</v>
       </c>
       <c r="B28" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>813999</v>
+        <v>814093</v>
       </c>
       <c r="R28" t="n">
-        <v>7355845</v>
+        <v>7355601</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3282,44 +3282,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125401325</v>
+        <v>125392595</v>
       </c>
       <c r="B29" t="n">
-        <v>78378</v>
+        <v>92522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>814093</v>
+        <v>813850</v>
       </c>
       <c r="R29" t="n">
-        <v>7355602</v>
+        <v>7355937</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3379,19 +3379,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125392595</v>
+        <v>125392596</v>
       </c>
       <c r="B30" t="n">
         <v>92522</v>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>813850</v>
+        <v>813911</v>
       </c>
       <c r="R30" t="n">
-        <v>7355937</v>
+        <v>7355874</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3488,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125392596</v>
+        <v>125401325</v>
       </c>
       <c r="B31" t="n">
-        <v>92522</v>
+        <v>78378</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>813911</v>
+        <v>814093</v>
       </c>
       <c r="R31" t="n">
-        <v>7355874</v>
+        <v>7355602</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3573,12 +3573,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -5045,10 +5045,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125392499</v>
+        <v>125393619</v>
       </c>
       <c r="B47" t="n">
-        <v>92714</v>
+        <v>78731</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5056,21 +5056,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>814055</v>
+        <v>814069</v>
       </c>
       <c r="R47" t="n">
-        <v>7355488</v>
+        <v>7355541</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5118,11 +5118,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5135,44 +5130,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125394416</v>
+        <v>125392499</v>
       </c>
       <c r="B48" t="n">
-        <v>56843</v>
+        <v>92714</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5182,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>814013</v>
+        <v>814055</v>
       </c>
       <c r="R48" t="n">
-        <v>7355681</v>
+        <v>7355488</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5222,7 +5217,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5237,44 +5232,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elsa Rensfeldt</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125401313</v>
+        <v>125393627</v>
       </c>
       <c r="B49" t="n">
-        <v>56843</v>
+        <v>78378</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,13 +5279,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>813998</v>
+        <v>813993</v>
       </c>
       <c r="R49" t="n">
-        <v>7355672</v>
+        <v>7355850</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5320,11 +5315,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-25</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5339,44 +5329,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125393619</v>
+        <v>125394416</v>
       </c>
       <c r="B50" t="n">
-        <v>78731</v>
+        <v>56843</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5386,10 +5376,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>814069</v>
+        <v>814013</v>
       </c>
       <c r="R50" t="n">
-        <v>7355541</v>
+        <v>7355681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5424,6 +5414,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5436,44 +5431,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elsa Rensfeldt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125393627</v>
+        <v>125401313</v>
       </c>
       <c r="B51" t="n">
-        <v>78378</v>
+        <v>56843</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5483,13 +5478,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>813993</v>
+        <v>813998</v>
       </c>
       <c r="R51" t="n">
-        <v>7355850</v>
+        <v>7355672</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5519,6 +5514,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5533,22 +5533,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125401314</v>
+        <v>125393606</v>
       </c>
       <c r="B52" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5556,21 +5556,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>813899</v>
+        <v>813976</v>
       </c>
       <c r="R52" t="n">
-        <v>7355975</v>
+        <v>7355749</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5630,44 +5630,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125393606</v>
+        <v>125392498</v>
       </c>
       <c r="B53" t="n">
-        <v>79590</v>
+        <v>78996</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>813976</v>
+        <v>814002</v>
       </c>
       <c r="R53" t="n">
-        <v>7355749</v>
+        <v>7355412</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5727,44 +5727,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125392498</v>
+        <v>125393622</v>
       </c>
       <c r="B54" t="n">
-        <v>78996</v>
+        <v>78730</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>814002</v>
+        <v>814058</v>
       </c>
       <c r="R54" t="n">
-        <v>7355412</v>
+        <v>7355641</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5824,22 +5824,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125393622</v>
+        <v>125392592</v>
       </c>
       <c r="B55" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,21 +5847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,13 +5871,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>814058</v>
+        <v>813924</v>
       </c>
       <c r="R55" t="n">
-        <v>7355641</v>
+        <v>7355940</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5921,12 +5921,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125392592</v>
+        <v>125401314</v>
       </c>
       <c r="B57" t="n">
         <v>78731</v>
@@ -6065,10 +6065,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>813924</v>
+        <v>813899</v>
       </c>
       <c r="R57" t="n">
-        <v>7355940</v>
+        <v>7355975</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6115,12 +6115,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7679,32 +7679,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125401296</v>
+        <v>125392494</v>
       </c>
       <c r="B74" t="n">
-        <v>92522</v>
+        <v>90270</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>813777</v>
+        <v>814004</v>
       </c>
       <c r="R74" t="n">
-        <v>7355862</v>
+        <v>7355434</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7752,11 +7752,6 @@
           <t>2025-05-25</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Häxring</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -7769,22 +7764,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125392494</v>
+        <v>125392501</v>
       </c>
       <c r="B75" t="n">
-        <v>90270</v>
+        <v>91853</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7792,21 +7787,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1962</v>
+        <v>5454</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7816,10 +7811,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>814004</v>
+        <v>814052</v>
       </c>
       <c r="R75" t="n">
-        <v>7355434</v>
+        <v>7355484</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7878,10 +7873,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125392501</v>
+        <v>125393607</v>
       </c>
       <c r="B76" t="n">
-        <v>91853</v>
+        <v>79590</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7889,21 +7884,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5454</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7913,10 +7908,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>814052</v>
+        <v>813971</v>
       </c>
       <c r="R76" t="n">
-        <v>7355484</v>
+        <v>7355703</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7963,44 +7958,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125393607</v>
+        <v>125401296</v>
       </c>
       <c r="B77" t="n">
-        <v>79590</v>
+        <v>92522</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8010,10 +8005,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>813971</v>
+        <v>813777</v>
       </c>
       <c r="R77" t="n">
-        <v>7355703</v>
+        <v>7355862</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8048,6 +8043,11 @@
           <t>2025-05-25</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Häxring</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8060,12 +8060,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8557,32 +8557,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125393621</v>
+        <v>125401323</v>
       </c>
       <c r="B83" t="n">
-        <v>78730</v>
+        <v>92522</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8592,13 +8592,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>813934</v>
+        <v>813969</v>
       </c>
       <c r="R83" t="n">
-        <v>7355844</v>
+        <v>7355700</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8642,44 +8642,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125401323</v>
+        <v>125393621</v>
       </c>
       <c r="B84" t="n">
-        <v>92522</v>
+        <v>78730</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8689,13 +8689,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>813969</v>
+        <v>813934</v>
       </c>
       <c r="R84" t="n">
-        <v>7355700</v>
+        <v>7355844</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8739,12 +8739,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -9658,7 +9658,7 @@
         <v>125395032</v>
       </c>
       <c r="B94" t="n">
-        <v>91154</v>
+        <v>91156</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>125395033</v>
       </c>
       <c r="B95" t="n">
-        <v>91493</v>
+        <v>91495</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -2812,7 +2812,7 @@
         <v>125392495</v>
       </c>
       <c r="B24" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>125401292</v>
       </c>
       <c r="B37" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>125394416</v>
       </c>
       <c r="B50" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>125401313</v>
       </c>
       <c r="B51" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>125392496</v>
       </c>
       <c r="B82" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>125417990</v>
       </c>
       <c r="B86" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>125417988</v>
       </c>
       <c r="B90" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>125417989</v>
       </c>
       <c r="B93" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -2812,7 +2812,7 @@
         <v>125392495</v>
       </c>
       <c r="B24" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>125401292</v>
       </c>
       <c r="B37" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>125394416</v>
       </c>
       <c r="B50" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>125401313</v>
       </c>
       <c r="B51" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>125392496</v>
       </c>
       <c r="B82" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>125417990</v>
       </c>
       <c r="B86" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>125417988</v>
       </c>
       <c r="B90" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>125417989</v>
       </c>
       <c r="B93" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -2812,7 +2812,7 @@
         <v>125392495</v>
       </c>
       <c r="B24" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>125401292</v>
       </c>
       <c r="B37" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>125394416</v>
       </c>
       <c r="B50" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>125401313</v>
       </c>
       <c r="B51" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>125392496</v>
       </c>
       <c r="B82" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>125417990</v>
       </c>
       <c r="B86" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>125417988</v>
       </c>
       <c r="B90" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>125417989</v>
       </c>
       <c r="B93" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 51840-2024 artfynd.xlsx
+++ b/artfynd/A 51840-2024 artfynd.xlsx
@@ -2812,7 +2812,7 @@
         <v>125392495</v>
       </c>
       <c r="B24" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>125401292</v>
       </c>
       <c r="B37" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>125394416</v>
       </c>
       <c r="B50" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         <v>125401313</v>
       </c>
       <c r="B51" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>125392496</v>
       </c>
       <c r="B82" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>125417990</v>
       </c>
       <c r="B86" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>125417988</v>
       </c>
       <c r="B90" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>125417989</v>
       </c>
       <c r="B93" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
